--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-12 10:14</t>
+          <t>2026-09-13 10:59</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>404</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>450</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>339</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>423</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>1616</v>
+        <v>1701</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-13 10:59</t>
+          <t>2026-09-14 13:05</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>425</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>466</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>354</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>456</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>1701</v>
+        <v>1829</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-14 13:05</t>
+          <t>2026-09-15 11:33</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>464</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>504</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>371</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>490</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>1829</v>
+        <v>1973</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-15 11:33</t>
+          <t>2026-09-16 11:29</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>496</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>558</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>401</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>518</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>1973</v>
+        <v>2132</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-16 11:29</t>
+          <t>2026-09-17 11:33</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>528</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>617</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>442</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>545</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2132</v>
+        <v>2260</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-17 11:33</t>
+          <t>2026-09-18 10:58</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>557</v>
+        <v>593</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>656</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>478</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>569</v>
+        <v>579</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2260</v>
+        <v>2350</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-18 10:58</t>
+          <t>2026-09-19 10:35</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>593</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>688</v>
+        <v>731</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>490</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>579</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2350</v>
+        <v>2468</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C299" t="n">
         <v>2024</v>
       </c>
@@ -5903,7 +5907,11 @@
       <c r="E299" t="n">
         <v>354</v>
       </c>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5911,7 +5919,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C300" t="n">
         <v>2024</v>
       </c>
@@ -5921,7 +5933,11 @@
       <c r="E300" t="n">
         <v>154</v>
       </c>
-      <c r="F300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5929,7 +5945,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C301" t="n">
         <v>2024</v>
       </c>
@@ -5939,7 +5959,11 @@
       <c r="E301" t="n">
         <v>158</v>
       </c>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5947,7 +5971,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C302" t="n">
         <v>2024</v>
       </c>
@@ -5957,7 +5985,11 @@
       <c r="E302" t="n">
         <v>356</v>
       </c>
-      <c r="F302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5965,7 +5997,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C303" t="n">
         <v>2024</v>
       </c>
@@ -5975,7 +6011,11 @@
       <c r="E303" t="n">
         <v>553</v>
       </c>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5983,7 +6023,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C304" t="n">
         <v>2024</v>
       </c>
@@ -5993,7 +6037,11 @@
       <c r="E304" t="n">
         <v>399</v>
       </c>
-      <c r="F304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6001,7 +6049,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C305" t="n">
         <v>2024</v>
       </c>
@@ -6011,7 +6063,11 @@
       <c r="E305" t="n">
         <v>132</v>
       </c>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6019,7 +6075,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C306" t="n">
         <v>2024</v>
       </c>
@@ -6029,7 +6089,11 @@
       <c r="E306" t="n">
         <v>349</v>
       </c>
-      <c r="F306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6037,7 +6101,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C307" t="n">
         <v>2024</v>
       </c>
@@ -6047,7 +6115,11 @@
       <c r="E307" t="n">
         <v>353</v>
       </c>
-      <c r="F307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6055,7 +6127,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C308" t="n">
         <v>2024</v>
       </c>
@@ -6065,7 +6141,11 @@
       <c r="E308" t="n">
         <v>288</v>
       </c>
-      <c r="F308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6073,7 +6153,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C309" t="n">
         <v>2024</v>
       </c>
@@ -6083,7 +6167,11 @@
       <c r="E309" t="n">
         <v>235</v>
       </c>
-      <c r="F309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6091,7 +6179,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C310" t="n">
         <v>2024</v>
       </c>
@@ -6101,7 +6193,11 @@
       <c r="E310" t="n">
         <v>390</v>
       </c>
-      <c r="F310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6109,7 +6205,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C311" t="n">
         <v>2025</v>
       </c>
@@ -6119,7 +6219,11 @@
       <c r="E311" t="n">
         <v>565</v>
       </c>
-      <c r="F311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6127,7 +6231,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C312" t="n">
         <v>2025</v>
       </c>
@@ -6137,7 +6245,11 @@
       <c r="E312" t="n">
         <v>425</v>
       </c>
-      <c r="F312" t="inlineStr"/>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6145,7 +6257,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C313" t="n">
         <v>2025</v>
       </c>
@@ -6155,7 +6271,11 @@
       <c r="E313" t="n">
         <v>396</v>
       </c>
-      <c r="F313" t="inlineStr"/>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6163,7 +6283,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C314" t="n">
         <v>2025</v>
       </c>
@@ -6173,7 +6297,11 @@
       <c r="E314" t="n">
         <v>327</v>
       </c>
-      <c r="F314" t="inlineStr"/>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6181,7 +6309,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C315" t="n">
         <v>2025</v>
       </c>
@@ -6191,7 +6323,11 @@
       <c r="E315" t="n">
         <v>367</v>
       </c>
-      <c r="F315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6199,7 +6335,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C316" t="n">
         <v>2025</v>
       </c>
@@ -6209,7 +6349,11 @@
       <c r="E316" t="n">
         <v>281</v>
       </c>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6217,7 +6361,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C317" t="n">
         <v>2025</v>
       </c>
@@ -6227,7 +6375,11 @@
       <c r="E317" t="n">
         <v>321</v>
       </c>
-      <c r="F317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6235,7 +6387,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C318" t="n">
         <v>2025</v>
       </c>
@@ -6245,7 +6401,11 @@
       <c r="E318" t="n">
         <v>301</v>
       </c>
-      <c r="F318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6253,7 +6413,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C319" t="n">
         <v>2025</v>
       </c>
@@ -6263,7 +6427,11 @@
       <c r="E319" t="n">
         <v>420</v>
       </c>
-      <c r="F319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6271,7 +6439,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C320" t="n">
         <v>2025</v>
       </c>
@@ -6281,7 +6453,11 @@
       <c r="E320" t="n">
         <v>355</v>
       </c>
-      <c r="F320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6289,7 +6465,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C321" t="n">
         <v>2025</v>
       </c>
@@ -6299,7 +6479,11 @@
       <c r="E321" t="n">
         <v>311</v>
       </c>
-      <c r="F321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6307,7 +6491,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C322" t="n">
         <v>2025</v>
       </c>
@@ -6317,7 +6505,11 @@
       <c r="E322" t="n">
         <v>167</v>
       </c>
-      <c r="F322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6325,7 +6517,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C323" t="n">
         <v>2026</v>
       </c>
@@ -6335,7 +6531,11 @@
       <c r="E323" t="n">
         <v>346</v>
       </c>
-      <c r="F323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6343,7 +6543,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C324" t="n">
         <v>2026</v>
       </c>
@@ -6353,7 +6557,11 @@
       <c r="E324" t="n">
         <v>215</v>
       </c>
-      <c r="F324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6361,7 +6569,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C325" t="n">
         <v>2026</v>
       </c>
@@ -6371,7 +6583,11 @@
       <c r="E325" t="n">
         <v>236</v>
       </c>
-      <c r="F325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6379,7 +6595,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C326" t="n">
         <v>2026</v>
       </c>
@@ -6389,7 +6609,11 @@
       <c r="E326" t="n">
         <v>222</v>
       </c>
-      <c r="F326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6397,7 +6621,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C327" t="n">
         <v>2026</v>
       </c>
@@ -6407,7 +6635,11 @@
       <c r="E327" t="n">
         <v>215</v>
       </c>
-      <c r="F327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6415,7 +6647,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C328" t="n">
         <v>2026</v>
       </c>
@@ -6425,7 +6661,11 @@
       <c r="E328" t="n">
         <v>212</v>
       </c>
-      <c r="F328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6433,7 +6673,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C329" t="n">
         <v>2026</v>
       </c>
@@ -6443,7 +6687,11 @@
       <c r="E329" t="n">
         <v>247</v>
       </c>
-      <c r="F329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6451,7 +6699,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C330" t="n">
         <v>2026</v>
       </c>
@@ -6461,7 +6713,11 @@
       <c r="E330" t="n">
         <v>250</v>
       </c>
-      <c r="F330" t="inlineStr"/>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6485,7 +6741,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6751,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C332" t="n">
         <v>2024</v>
       </c>
@@ -6505,7 +6765,11 @@
       <c r="E332" t="n">
         <v>111</v>
       </c>
-      <c r="F332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6513,7 +6777,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C333" t="n">
         <v>2024</v>
       </c>
@@ -6523,7 +6791,11 @@
       <c r="E333" t="n">
         <v>217</v>
       </c>
-      <c r="F333" t="inlineStr"/>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6531,7 +6803,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C334" t="n">
         <v>2024</v>
       </c>
@@ -6541,7 +6817,11 @@
       <c r="E334" t="n">
         <v>173</v>
       </c>
-      <c r="F334" t="inlineStr"/>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6549,7 +6829,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C335" t="n">
         <v>2024</v>
       </c>
@@ -6559,7 +6843,11 @@
       <c r="E335" t="n">
         <v>157</v>
       </c>
-      <c r="F335" t="inlineStr"/>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6567,7 +6855,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C336" t="n">
         <v>2024</v>
       </c>
@@ -6577,7 +6869,11 @@
       <c r="E336" t="n">
         <v>178</v>
       </c>
-      <c r="F336" t="inlineStr"/>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6585,7 +6881,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C337" t="n">
         <v>2024</v>
       </c>
@@ -6595,7 +6895,11 @@
       <c r="E337" t="n">
         <v>181</v>
       </c>
-      <c r="F337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6603,7 +6907,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C338" t="n">
         <v>2024</v>
       </c>
@@ -6613,7 +6921,11 @@
       <c r="E338" t="n">
         <v>169</v>
       </c>
-      <c r="F338" t="inlineStr"/>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6621,7 +6933,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C339" t="n">
         <v>2024</v>
       </c>
@@ -6631,7 +6947,11 @@
       <c r="E339" t="n">
         <v>183</v>
       </c>
-      <c r="F339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6639,7 +6959,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C340" t="n">
         <v>2024</v>
       </c>
@@ -6649,7 +6973,11 @@
       <c r="E340" t="n">
         <v>212</v>
       </c>
-      <c r="F340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6657,7 +6985,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C341" t="n">
         <v>2024</v>
       </c>
@@ -6667,7 +6999,11 @@
       <c r="E341" t="n">
         <v>177</v>
       </c>
-      <c r="F341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6675,7 +7011,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C342" t="n">
         <v>2024</v>
       </c>
@@ -6685,7 +7025,11 @@
       <c r="E342" t="n">
         <v>141</v>
       </c>
-      <c r="F342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6693,7 +7037,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C343" t="n">
         <v>2024</v>
       </c>
@@ -6703,7 +7051,11 @@
       <c r="E343" t="n">
         <v>181</v>
       </c>
-      <c r="F343" t="inlineStr"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6711,7 +7063,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C344" t="n">
         <v>2025</v>
       </c>
@@ -6721,7 +7077,11 @@
       <c r="E344" t="n">
         <v>362</v>
       </c>
-      <c r="F344" t="inlineStr"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6729,7 +7089,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C345" t="n">
         <v>2025</v>
       </c>
@@ -6739,7 +7103,11 @@
       <c r="E345" t="n">
         <v>233</v>
       </c>
-      <c r="F345" t="inlineStr"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -6747,7 +7115,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C346" t="n">
         <v>2025</v>
       </c>
@@ -6757,7 +7129,11 @@
       <c r="E346" t="n">
         <v>290</v>
       </c>
-      <c r="F346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -6765,7 +7141,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C347" t="n">
         <v>2025</v>
       </c>
@@ -6775,7 +7155,11 @@
       <c r="E347" t="n">
         <v>339</v>
       </c>
-      <c r="F347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6783,7 +7167,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C348" t="n">
         <v>2025</v>
       </c>
@@ -6793,7 +7181,11 @@
       <c r="E348" t="n">
         <v>337</v>
       </c>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6801,7 +7193,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C349" t="n">
         <v>2025</v>
       </c>
@@ -6811,7 +7207,11 @@
       <c r="E349" t="n">
         <v>304</v>
       </c>
-      <c r="F349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6819,7 +7219,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C350" t="n">
         <v>2025</v>
       </c>
@@ -6829,7 +7233,11 @@
       <c r="E350" t="n">
         <v>309</v>
       </c>
-      <c r="F350" t="inlineStr"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6837,7 +7245,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C351" t="n">
         <v>2025</v>
       </c>
@@ -6847,7 +7259,11 @@
       <c r="E351" t="n">
         <v>331</v>
       </c>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6855,7 +7271,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C352" t="n">
         <v>2025</v>
       </c>
@@ -6865,7 +7285,11 @@
       <c r="E352" t="n">
         <v>328</v>
       </c>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6873,7 +7297,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C353" t="n">
         <v>2025</v>
       </c>
@@ -6883,7 +7311,11 @@
       <c r="E353" t="n">
         <v>326</v>
       </c>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6891,7 +7323,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C354" t="n">
         <v>2025</v>
       </c>
@@ -6901,7 +7337,11 @@
       <c r="E354" t="n">
         <v>298</v>
       </c>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6909,7 +7349,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C355" t="n">
         <v>2025</v>
       </c>
@@ -6919,7 +7363,11 @@
       <c r="E355" t="n">
         <v>227</v>
       </c>
-      <c r="F355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6927,7 +7375,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C356" t="n">
         <v>2026</v>
       </c>
@@ -6937,7 +7389,11 @@
       <c r="E356" t="n">
         <v>363</v>
       </c>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6945,7 +7401,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C357" t="n">
         <v>2026</v>
       </c>
@@ -6955,7 +7415,11 @@
       <c r="E357" t="n">
         <v>252</v>
       </c>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6963,7 +7427,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C358" t="n">
         <v>2026</v>
       </c>
@@ -6973,7 +7441,11 @@
       <c r="E358" t="n">
         <v>289</v>
       </c>
-      <c r="F358" t="inlineStr"/>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6981,7 +7453,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C359" t="n">
         <v>2026</v>
       </c>
@@ -6991,7 +7467,11 @@
       <c r="E359" t="n">
         <v>272</v>
       </c>
-      <c r="F359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6999,7 +7479,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C360" t="n">
         <v>2026</v>
       </c>
@@ -7009,7 +7493,11 @@
       <c r="E360" t="n">
         <v>255</v>
       </c>
-      <c r="F360" t="inlineStr"/>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -7017,7 +7505,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C361" t="n">
         <v>2026</v>
       </c>
@@ -7027,7 +7519,11 @@
       <c r="E361" t="n">
         <v>198</v>
       </c>
-      <c r="F361" t="inlineStr"/>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -7035,7 +7531,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C362" t="n">
         <v>2026</v>
       </c>
@@ -7045,7 +7545,11 @@
       <c r="E362" t="n">
         <v>278</v>
       </c>
-      <c r="F362" t="inlineStr"/>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -7053,7 +7557,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C363" t="n">
         <v>2026</v>
       </c>
@@ -7063,7 +7571,11 @@
       <c r="E363" t="n">
         <v>278</v>
       </c>
-      <c r="F363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:48</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -7087,7 +7599,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -7689,7 +8201,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8799,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -8889,11 +9401,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -9491,11 +10003,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10609,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -10695,11 +11207,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11813,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -11899,11 +12411,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -12501,11 +13013,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13615,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -13709,7 +14221,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14819,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -14909,11 +15421,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-19 10:35</t>
+          <t>2026-09-20 10:48</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15754,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>622</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3">
@@ -15252,103 +15764,103 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>571</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>704</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="AH3" t="n">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15966,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>511</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +16072,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>604</v>
+        <v>626</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +16178,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2468</v>
+        <v>2530</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -5893,11 +5893,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B299" t="inlineStr"/>
       <c r="C299" t="n">
         <v>2024</v>
       </c>
@@ -5907,11 +5903,7 @@
       <c r="E299" t="n">
         <v>354</v>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5919,11 +5911,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
         <v>2024</v>
       </c>
@@ -5933,11 +5921,7 @@
       <c r="E300" t="n">
         <v>154</v>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5945,11 +5929,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
         <v>2024</v>
       </c>
@@ -5959,11 +5939,7 @@
       <c r="E301" t="n">
         <v>158</v>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5971,11 +5947,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
         <v>2024</v>
       </c>
@@ -5985,11 +5957,7 @@
       <c r="E302" t="n">
         <v>356</v>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5997,11 +5965,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>2024</v>
       </c>
@@ -6011,11 +5975,7 @@
       <c r="E303" t="n">
         <v>553</v>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6023,11 +5983,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="n">
         <v>2024</v>
       </c>
@@ -6037,11 +5993,7 @@
       <c r="E304" t="n">
         <v>399</v>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6049,11 +6001,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B305" t="inlineStr"/>
       <c r="C305" t="n">
         <v>2024</v>
       </c>
@@ -6063,11 +6011,7 @@
       <c r="E305" t="n">
         <v>132</v>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6075,11 +6019,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B306" t="inlineStr"/>
       <c r="C306" t="n">
         <v>2024</v>
       </c>
@@ -6089,11 +6029,7 @@
       <c r="E306" t="n">
         <v>349</v>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6101,11 +6037,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
         <v>2024</v>
       </c>
@@ -6115,11 +6047,7 @@
       <c r="E307" t="n">
         <v>353</v>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6127,11 +6055,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
         <v>2024</v>
       </c>
@@ -6141,11 +6065,7 @@
       <c r="E308" t="n">
         <v>288</v>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6153,11 +6073,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="n">
         <v>2024</v>
       </c>
@@ -6167,11 +6083,7 @@
       <c r="E309" t="n">
         <v>235</v>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6179,11 +6091,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
         <v>2024</v>
       </c>
@@ -6193,11 +6101,7 @@
       <c r="E310" t="n">
         <v>390</v>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6205,11 +6109,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B311" t="inlineStr"/>
       <c r="C311" t="n">
         <v>2025</v>
       </c>
@@ -6219,11 +6119,7 @@
       <c r="E311" t="n">
         <v>565</v>
       </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6231,11 +6127,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
         <v>2025</v>
       </c>
@@ -6245,11 +6137,7 @@
       <c r="E312" t="n">
         <v>425</v>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6257,11 +6145,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
         <v>2025</v>
       </c>
@@ -6271,11 +6155,7 @@
       <c r="E313" t="n">
         <v>396</v>
       </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6283,11 +6163,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
         <v>2025</v>
       </c>
@@ -6297,11 +6173,7 @@
       <c r="E314" t="n">
         <v>327</v>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6309,11 +6181,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B315" t="inlineStr"/>
       <c r="C315" t="n">
         <v>2025</v>
       </c>
@@ -6323,11 +6191,7 @@
       <c r="E315" t="n">
         <v>367</v>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6335,11 +6199,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
         <v>2025</v>
       </c>
@@ -6349,11 +6209,7 @@
       <c r="E316" t="n">
         <v>281</v>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6361,11 +6217,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
         <v>2025</v>
       </c>
@@ -6375,11 +6227,7 @@
       <c r="E317" t="n">
         <v>321</v>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6387,11 +6235,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
         <v>2025</v>
       </c>
@@ -6401,11 +6245,7 @@
       <c r="E318" t="n">
         <v>301</v>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6413,11 +6253,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B319" t="inlineStr"/>
       <c r="C319" t="n">
         <v>2025</v>
       </c>
@@ -6427,11 +6263,7 @@
       <c r="E319" t="n">
         <v>420</v>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6439,11 +6271,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
         <v>2025</v>
       </c>
@@ -6453,11 +6281,7 @@
       <c r="E320" t="n">
         <v>355</v>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6465,11 +6289,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>2025</v>
       </c>
@@ -6479,11 +6299,7 @@
       <c r="E321" t="n">
         <v>311</v>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6491,11 +6307,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B322" t="inlineStr"/>
       <c r="C322" t="n">
         <v>2025</v>
       </c>
@@ -6505,11 +6317,7 @@
       <c r="E322" t="n">
         <v>167</v>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6517,11 +6325,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B323" t="inlineStr"/>
       <c r="C323" t="n">
         <v>2026</v>
       </c>
@@ -6531,11 +6335,7 @@
       <c r="E323" t="n">
         <v>346</v>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6543,11 +6343,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
         <v>2026</v>
       </c>
@@ -6557,11 +6353,7 @@
       <c r="E324" t="n">
         <v>215</v>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6569,11 +6361,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
         <v>2026</v>
       </c>
@@ -6583,11 +6371,7 @@
       <c r="E325" t="n">
         <v>236</v>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6595,11 +6379,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
         <v>2026</v>
       </c>
@@ -6609,11 +6389,7 @@
       <c r="E326" t="n">
         <v>222</v>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6621,11 +6397,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B327" t="inlineStr"/>
       <c r="C327" t="n">
         <v>2026</v>
       </c>
@@ -6635,11 +6407,7 @@
       <c r="E327" t="n">
         <v>215</v>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6647,11 +6415,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B328" t="inlineStr"/>
       <c r="C328" t="n">
         <v>2026</v>
       </c>
@@ -6661,11 +6425,7 @@
       <c r="E328" t="n">
         <v>212</v>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6673,11 +6433,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
         <v>2026</v>
       </c>
@@ -6687,11 +6443,7 @@
       <c r="E329" t="n">
         <v>247</v>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6699,11 +6451,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B330" t="inlineStr"/>
       <c r="C330" t="n">
         <v>2026</v>
       </c>
@@ -6713,11 +6461,7 @@
       <c r="E330" t="n">
         <v>250</v>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6737,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -6751,11 +6495,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B332" t="inlineStr"/>
       <c r="C332" t="n">
         <v>2024</v>
       </c>
@@ -6765,11 +6505,7 @@
       <c r="E332" t="n">
         <v>111</v>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6777,11 +6513,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
         <v>2024</v>
       </c>
@@ -6791,11 +6523,7 @@
       <c r="E333" t="n">
         <v>217</v>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6803,11 +6531,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
         <v>2024</v>
       </c>
@@ -6817,11 +6541,7 @@
       <c r="E334" t="n">
         <v>173</v>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6829,11 +6549,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B335" t="inlineStr"/>
       <c r="C335" t="n">
         <v>2024</v>
       </c>
@@ -6843,11 +6559,7 @@
       <c r="E335" t="n">
         <v>157</v>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6855,11 +6567,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
         <v>2024</v>
       </c>
@@ -6869,11 +6577,7 @@
       <c r="E336" t="n">
         <v>178</v>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6881,11 +6585,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
         <v>2024</v>
       </c>
@@ -6895,11 +6595,7 @@
       <c r="E337" t="n">
         <v>181</v>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6907,11 +6603,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B338" t="inlineStr"/>
       <c r="C338" t="n">
         <v>2024</v>
       </c>
@@ -6921,11 +6613,7 @@
       <c r="E338" t="n">
         <v>169</v>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6933,11 +6621,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
         <v>2024</v>
       </c>
@@ -6947,11 +6631,7 @@
       <c r="E339" t="n">
         <v>183</v>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6959,11 +6639,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
         <v>2024</v>
       </c>
@@ -6973,11 +6649,7 @@
       <c r="E340" t="n">
         <v>212</v>
       </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6985,11 +6657,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
         <v>2024</v>
       </c>
@@ -6999,11 +6667,7 @@
       <c r="E341" t="n">
         <v>177</v>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7011,11 +6675,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
         <v>2024</v>
       </c>
@@ -7025,11 +6685,7 @@
       <c r="E342" t="n">
         <v>141</v>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7037,11 +6693,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
         <v>2024</v>
       </c>
@@ -7051,11 +6703,7 @@
       <c r="E343" t="n">
         <v>181</v>
       </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7063,11 +6711,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
         <v>2025</v>
       </c>
@@ -7077,11 +6721,7 @@
       <c r="E344" t="n">
         <v>362</v>
       </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7089,11 +6729,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
         <v>2025</v>
       </c>
@@ -7103,11 +6739,7 @@
       <c r="E345" t="n">
         <v>233</v>
       </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7115,11 +6747,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
         <v>2025</v>
       </c>
@@ -7129,11 +6757,7 @@
       <c r="E346" t="n">
         <v>290</v>
       </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7141,11 +6765,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="n">
         <v>2025</v>
       </c>
@@ -7155,11 +6775,7 @@
       <c r="E347" t="n">
         <v>339</v>
       </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7167,11 +6783,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
         <v>2025</v>
       </c>
@@ -7181,11 +6793,7 @@
       <c r="E348" t="n">
         <v>337</v>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7193,11 +6801,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="n">
         <v>2025</v>
       </c>
@@ -7207,11 +6811,7 @@
       <c r="E349" t="n">
         <v>304</v>
       </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7219,11 +6819,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
         <v>2025</v>
       </c>
@@ -7233,11 +6829,7 @@
       <c r="E350" t="n">
         <v>309</v>
       </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7245,11 +6837,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
         <v>2025</v>
       </c>
@@ -7259,11 +6847,7 @@
       <c r="E351" t="n">
         <v>331</v>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7271,11 +6855,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
         <v>2025</v>
       </c>
@@ -7285,11 +6865,7 @@
       <c r="E352" t="n">
         <v>328</v>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -7297,11 +6873,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>2025</v>
       </c>
@@ -7311,11 +6883,7 @@
       <c r="E353" t="n">
         <v>326</v>
       </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -7323,11 +6891,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>2025</v>
       </c>
@@ -7337,11 +6901,7 @@
       <c r="E354" t="n">
         <v>298</v>
       </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -7349,11 +6909,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
         <v>2025</v>
       </c>
@@ -7363,11 +6919,7 @@
       <c r="E355" t="n">
         <v>227</v>
       </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -7375,11 +6927,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
         <v>2026</v>
       </c>
@@ -7389,11 +6937,7 @@
       <c r="E356" t="n">
         <v>363</v>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7401,11 +6945,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
         <v>2026</v>
       </c>
@@ -7415,11 +6955,7 @@
       <c r="E357" t="n">
         <v>252</v>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -7427,11 +6963,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
         <v>2026</v>
       </c>
@@ -7441,11 +6973,7 @@
       <c r="E358" t="n">
         <v>289</v>
       </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -7453,11 +6981,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
         <v>2026</v>
       </c>
@@ -7467,11 +6991,7 @@
       <c r="E359" t="n">
         <v>272</v>
       </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -7479,11 +6999,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
         <v>2026</v>
       </c>
@@ -7493,11 +7009,7 @@
       <c r="E360" t="n">
         <v>255</v>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -7505,11 +7017,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B361" t="inlineStr"/>
       <c r="C361" t="n">
         <v>2026</v>
       </c>
@@ -7519,11 +7027,7 @@
       <c r="E361" t="n">
         <v>198</v>
       </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -7531,11 +7035,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B362" t="inlineStr"/>
       <c r="C362" t="n">
         <v>2026</v>
       </c>
@@ -7545,11 +7045,7 @@
       <c r="E362" t="n">
         <v>278</v>
       </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -7557,11 +7053,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
         <v>2026</v>
       </c>
@@ -7571,11 +7063,7 @@
       <c r="E363" t="n">
         <v>278</v>
       </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:48</t>
-        </is>
-      </c>
+      <c r="F363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -7595,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -8197,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -8799,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -9401,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -10003,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -10605,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -11211,7 +10699,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11301,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -12411,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -13013,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -13615,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -14217,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -14819,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -15425,7 +14913,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-20 10:48</t>
+          <t>2026-09-21 13:07</t>
         </is>
       </c>
     </row>
@@ -15754,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>639</v>
+        <v>665</v>
       </c>
     </row>
     <row r="3">
@@ -15764,103 +15252,103 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>731</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>532</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>571</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>927</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>585</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>735</v>
+        <v>771</v>
       </c>
     </row>
     <row r="4">
@@ -15966,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>530</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5">
@@ -16072,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>626</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6">
@@ -16178,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2530</v>
+        <v>2634</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C299" t="n">
         <v>2024</v>
       </c>
@@ -5903,7 +5907,11 @@
       <c r="E299" t="n">
         <v>354</v>
       </c>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5911,7 +5919,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C300" t="n">
         <v>2024</v>
       </c>
@@ -5921,7 +5933,11 @@
       <c r="E300" t="n">
         <v>154</v>
       </c>
-      <c r="F300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5929,7 +5945,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C301" t="n">
         <v>2024</v>
       </c>
@@ -5939,7 +5959,11 @@
       <c r="E301" t="n">
         <v>158</v>
       </c>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5947,7 +5971,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C302" t="n">
         <v>2024</v>
       </c>
@@ -5957,7 +5985,11 @@
       <c r="E302" t="n">
         <v>356</v>
       </c>
-      <c r="F302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5965,7 +5997,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C303" t="n">
         <v>2024</v>
       </c>
@@ -5975,7 +6011,11 @@
       <c r="E303" t="n">
         <v>553</v>
       </c>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5983,7 +6023,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C304" t="n">
         <v>2024</v>
       </c>
@@ -5993,7 +6037,11 @@
       <c r="E304" t="n">
         <v>399</v>
       </c>
-      <c r="F304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6001,7 +6049,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C305" t="n">
         <v>2024</v>
       </c>
@@ -6011,7 +6063,11 @@
       <c r="E305" t="n">
         <v>132</v>
       </c>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6019,7 +6075,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C306" t="n">
         <v>2024</v>
       </c>
@@ -6029,7 +6089,11 @@
       <c r="E306" t="n">
         <v>349</v>
       </c>
-      <c r="F306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6037,7 +6101,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C307" t="n">
         <v>2024</v>
       </c>
@@ -6047,7 +6115,11 @@
       <c r="E307" t="n">
         <v>353</v>
       </c>
-      <c r="F307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6055,7 +6127,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C308" t="n">
         <v>2024</v>
       </c>
@@ -6065,7 +6141,11 @@
       <c r="E308" t="n">
         <v>288</v>
       </c>
-      <c r="F308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6073,7 +6153,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C309" t="n">
         <v>2024</v>
       </c>
@@ -6083,7 +6167,11 @@
       <c r="E309" t="n">
         <v>235</v>
       </c>
-      <c r="F309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6091,7 +6179,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C310" t="n">
         <v>2024</v>
       </c>
@@ -6101,7 +6193,11 @@
       <c r="E310" t="n">
         <v>390</v>
       </c>
-      <c r="F310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6109,7 +6205,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C311" t="n">
         <v>2025</v>
       </c>
@@ -6119,7 +6219,11 @@
       <c r="E311" t="n">
         <v>565</v>
       </c>
-      <c r="F311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6127,7 +6231,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C312" t="n">
         <v>2025</v>
       </c>
@@ -6137,7 +6245,11 @@
       <c r="E312" t="n">
         <v>425</v>
       </c>
-      <c r="F312" t="inlineStr"/>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6145,7 +6257,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C313" t="n">
         <v>2025</v>
       </c>
@@ -6155,7 +6271,11 @@
       <c r="E313" t="n">
         <v>396</v>
       </c>
-      <c r="F313" t="inlineStr"/>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6163,7 +6283,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C314" t="n">
         <v>2025</v>
       </c>
@@ -6173,7 +6297,11 @@
       <c r="E314" t="n">
         <v>327</v>
       </c>
-      <c r="F314" t="inlineStr"/>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6181,7 +6309,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C315" t="n">
         <v>2025</v>
       </c>
@@ -6191,7 +6323,11 @@
       <c r="E315" t="n">
         <v>367</v>
       </c>
-      <c r="F315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6199,7 +6335,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C316" t="n">
         <v>2025</v>
       </c>
@@ -6209,7 +6349,11 @@
       <c r="E316" t="n">
         <v>281</v>
       </c>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6217,7 +6361,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C317" t="n">
         <v>2025</v>
       </c>
@@ -6227,7 +6375,11 @@
       <c r="E317" t="n">
         <v>321</v>
       </c>
-      <c r="F317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6235,7 +6387,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C318" t="n">
         <v>2025</v>
       </c>
@@ -6245,7 +6401,11 @@
       <c r="E318" t="n">
         <v>301</v>
       </c>
-      <c r="F318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6253,7 +6413,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C319" t="n">
         <v>2025</v>
       </c>
@@ -6263,7 +6427,11 @@
       <c r="E319" t="n">
         <v>420</v>
       </c>
-      <c r="F319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6271,7 +6439,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C320" t="n">
         <v>2025</v>
       </c>
@@ -6281,7 +6453,11 @@
       <c r="E320" t="n">
         <v>355</v>
       </c>
-      <c r="F320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6289,7 +6465,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C321" t="n">
         <v>2025</v>
       </c>
@@ -6299,7 +6479,11 @@
       <c r="E321" t="n">
         <v>311</v>
       </c>
-      <c r="F321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6307,7 +6491,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C322" t="n">
         <v>2025</v>
       </c>
@@ -6317,7 +6505,11 @@
       <c r="E322" t="n">
         <v>167</v>
       </c>
-      <c r="F322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6325,7 +6517,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C323" t="n">
         <v>2026</v>
       </c>
@@ -6335,7 +6531,11 @@
       <c r="E323" t="n">
         <v>346</v>
       </c>
-      <c r="F323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6343,7 +6543,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C324" t="n">
         <v>2026</v>
       </c>
@@ -6353,7 +6557,11 @@
       <c r="E324" t="n">
         <v>215</v>
       </c>
-      <c r="F324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6361,7 +6569,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C325" t="n">
         <v>2026</v>
       </c>
@@ -6371,7 +6583,11 @@
       <c r="E325" t="n">
         <v>236</v>
       </c>
-      <c r="F325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6379,7 +6595,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C326" t="n">
         <v>2026</v>
       </c>
@@ -6389,7 +6609,11 @@
       <c r="E326" t="n">
         <v>222</v>
       </c>
-      <c r="F326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6397,7 +6621,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C327" t="n">
         <v>2026</v>
       </c>
@@ -6407,7 +6635,11 @@
       <c r="E327" t="n">
         <v>215</v>
       </c>
-      <c r="F327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6415,7 +6647,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C328" t="n">
         <v>2026</v>
       </c>
@@ -6425,7 +6661,11 @@
       <c r="E328" t="n">
         <v>212</v>
       </c>
-      <c r="F328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6433,7 +6673,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C329" t="n">
         <v>2026</v>
       </c>
@@ -6443,7 +6687,11 @@
       <c r="E329" t="n">
         <v>247</v>
       </c>
-      <c r="F329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6451,7 +6699,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C330" t="n">
         <v>2026</v>
       </c>
@@ -6461,7 +6713,11 @@
       <c r="E330" t="n">
         <v>250</v>
       </c>
-      <c r="F330" t="inlineStr"/>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6485,7 +6741,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6751,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C332" t="n">
         <v>2024</v>
       </c>
@@ -6505,7 +6765,11 @@
       <c r="E332" t="n">
         <v>111</v>
       </c>
-      <c r="F332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6513,7 +6777,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C333" t="n">
         <v>2024</v>
       </c>
@@ -6523,7 +6791,11 @@
       <c r="E333" t="n">
         <v>217</v>
       </c>
-      <c r="F333" t="inlineStr"/>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6531,7 +6803,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C334" t="n">
         <v>2024</v>
       </c>
@@ -6541,7 +6817,11 @@
       <c r="E334" t="n">
         <v>173</v>
       </c>
-      <c r="F334" t="inlineStr"/>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6549,7 +6829,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C335" t="n">
         <v>2024</v>
       </c>
@@ -6559,7 +6843,11 @@
       <c r="E335" t="n">
         <v>157</v>
       </c>
-      <c r="F335" t="inlineStr"/>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6567,7 +6855,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C336" t="n">
         <v>2024</v>
       </c>
@@ -6577,7 +6869,11 @@
       <c r="E336" t="n">
         <v>178</v>
       </c>
-      <c r="F336" t="inlineStr"/>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6585,7 +6881,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C337" t="n">
         <v>2024</v>
       </c>
@@ -6595,7 +6895,11 @@
       <c r="E337" t="n">
         <v>181</v>
       </c>
-      <c r="F337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6603,7 +6907,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C338" t="n">
         <v>2024</v>
       </c>
@@ -6613,7 +6921,11 @@
       <c r="E338" t="n">
         <v>169</v>
       </c>
-      <c r="F338" t="inlineStr"/>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6621,7 +6933,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C339" t="n">
         <v>2024</v>
       </c>
@@ -6631,7 +6947,11 @@
       <c r="E339" t="n">
         <v>183</v>
       </c>
-      <c r="F339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6639,7 +6959,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C340" t="n">
         <v>2024</v>
       </c>
@@ -6649,7 +6973,11 @@
       <c r="E340" t="n">
         <v>212</v>
       </c>
-      <c r="F340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6657,7 +6985,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C341" t="n">
         <v>2024</v>
       </c>
@@ -6667,7 +6999,11 @@
       <c r="E341" t="n">
         <v>177</v>
       </c>
-      <c r="F341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6675,7 +7011,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C342" t="n">
         <v>2024</v>
       </c>
@@ -6685,7 +7025,11 @@
       <c r="E342" t="n">
         <v>141</v>
       </c>
-      <c r="F342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6693,7 +7037,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C343" t="n">
         <v>2024</v>
       </c>
@@ -6703,7 +7051,11 @@
       <c r="E343" t="n">
         <v>181</v>
       </c>
-      <c r="F343" t="inlineStr"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6711,7 +7063,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C344" t="n">
         <v>2025</v>
       </c>
@@ -6721,7 +7077,11 @@
       <c r="E344" t="n">
         <v>362</v>
       </c>
-      <c r="F344" t="inlineStr"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6729,7 +7089,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C345" t="n">
         <v>2025</v>
       </c>
@@ -6739,7 +7103,11 @@
       <c r="E345" t="n">
         <v>233</v>
       </c>
-      <c r="F345" t="inlineStr"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -6747,7 +7115,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C346" t="n">
         <v>2025</v>
       </c>
@@ -6757,7 +7129,11 @@
       <c r="E346" t="n">
         <v>290</v>
       </c>
-      <c r="F346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -6765,7 +7141,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C347" t="n">
         <v>2025</v>
       </c>
@@ -6775,7 +7155,11 @@
       <c r="E347" t="n">
         <v>339</v>
       </c>
-      <c r="F347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6783,7 +7167,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C348" t="n">
         <v>2025</v>
       </c>
@@ -6793,7 +7181,11 @@
       <c r="E348" t="n">
         <v>337</v>
       </c>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6801,7 +7193,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C349" t="n">
         <v>2025</v>
       </c>
@@ -6811,7 +7207,11 @@
       <c r="E349" t="n">
         <v>304</v>
       </c>
-      <c r="F349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6819,7 +7219,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C350" t="n">
         <v>2025</v>
       </c>
@@ -6829,7 +7233,11 @@
       <c r="E350" t="n">
         <v>309</v>
       </c>
-      <c r="F350" t="inlineStr"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6837,7 +7245,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C351" t="n">
         <v>2025</v>
       </c>
@@ -6847,7 +7259,11 @@
       <c r="E351" t="n">
         <v>331</v>
       </c>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6855,7 +7271,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C352" t="n">
         <v>2025</v>
       </c>
@@ -6865,7 +7285,11 @@
       <c r="E352" t="n">
         <v>328</v>
       </c>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6873,7 +7297,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C353" t="n">
         <v>2025</v>
       </c>
@@ -6883,7 +7311,11 @@
       <c r="E353" t="n">
         <v>326</v>
       </c>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6891,7 +7323,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C354" t="n">
         <v>2025</v>
       </c>
@@ -6901,7 +7337,11 @@
       <c r="E354" t="n">
         <v>298</v>
       </c>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6909,7 +7349,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C355" t="n">
         <v>2025</v>
       </c>
@@ -6919,7 +7363,11 @@
       <c r="E355" t="n">
         <v>227</v>
       </c>
-      <c r="F355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6927,7 +7375,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C356" t="n">
         <v>2026</v>
       </c>
@@ -6937,7 +7389,11 @@
       <c r="E356" t="n">
         <v>363</v>
       </c>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6945,7 +7401,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C357" t="n">
         <v>2026</v>
       </c>
@@ -6955,7 +7415,11 @@
       <c r="E357" t="n">
         <v>252</v>
       </c>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6963,7 +7427,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C358" t="n">
         <v>2026</v>
       </c>
@@ -6973,7 +7441,11 @@
       <c r="E358" t="n">
         <v>289</v>
       </c>
-      <c r="F358" t="inlineStr"/>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6981,7 +7453,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C359" t="n">
         <v>2026</v>
       </c>
@@ -6991,7 +7467,11 @@
       <c r="E359" t="n">
         <v>272</v>
       </c>
-      <c r="F359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6999,7 +7479,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C360" t="n">
         <v>2026</v>
       </c>
@@ -7009,7 +7493,11 @@
       <c r="E360" t="n">
         <v>255</v>
       </c>
-      <c r="F360" t="inlineStr"/>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -7017,7 +7505,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C361" t="n">
         <v>2026</v>
       </c>
@@ -7027,7 +7519,11 @@
       <c r="E361" t="n">
         <v>198</v>
       </c>
-      <c r="F361" t="inlineStr"/>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -7035,7 +7531,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C362" t="n">
         <v>2026</v>
       </c>
@@ -7045,7 +7545,11 @@
       <c r="E362" t="n">
         <v>278</v>
       </c>
-      <c r="F362" t="inlineStr"/>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -7053,7 +7557,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C363" t="n">
         <v>2026</v>
       </c>
@@ -7063,7 +7571,11 @@
       <c r="E363" t="n">
         <v>278</v>
       </c>
-      <c r="F363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:17</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -7087,7 +7599,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -7685,11 +8197,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8799,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -8889,11 +9401,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -9491,11 +10003,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10605,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -10695,11 +11207,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11809,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -11899,11 +12411,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -12501,11 +13013,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13615,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -13705,11 +14217,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14819,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -14913,7 +15425,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-21 13:07</t>
+          <t>2026-09-22 11:17</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15754,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>665</v>
+        <v>694</v>
       </c>
     </row>
     <row r="3">
@@ -15252,103 +15764,103 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>571</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>704</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="AH3" t="n">
-        <v>771</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15966,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>547</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +16072,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>651</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +16178,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2634</v>
+        <v>2740</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -5893,11 +5893,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B299" t="inlineStr"/>
       <c r="C299" t="n">
         <v>2024</v>
       </c>
@@ -5907,11 +5903,7 @@
       <c r="E299" t="n">
         <v>354</v>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5919,11 +5911,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
         <v>2024</v>
       </c>
@@ -5933,11 +5921,7 @@
       <c r="E300" t="n">
         <v>154</v>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5945,11 +5929,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
         <v>2024</v>
       </c>
@@ -5959,11 +5939,7 @@
       <c r="E301" t="n">
         <v>158</v>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5971,11 +5947,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
         <v>2024</v>
       </c>
@@ -5985,11 +5957,7 @@
       <c r="E302" t="n">
         <v>356</v>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5997,11 +5965,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>2024</v>
       </c>
@@ -6011,11 +5975,7 @@
       <c r="E303" t="n">
         <v>553</v>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6023,11 +5983,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="n">
         <v>2024</v>
       </c>
@@ -6037,11 +5993,7 @@
       <c r="E304" t="n">
         <v>399</v>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6049,11 +6001,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B305" t="inlineStr"/>
       <c r="C305" t="n">
         <v>2024</v>
       </c>
@@ -6063,11 +6011,7 @@
       <c r="E305" t="n">
         <v>132</v>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6075,11 +6019,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B306" t="inlineStr"/>
       <c r="C306" t="n">
         <v>2024</v>
       </c>
@@ -6089,11 +6029,7 @@
       <c r="E306" t="n">
         <v>349</v>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6101,11 +6037,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
         <v>2024</v>
       </c>
@@ -6115,11 +6047,7 @@
       <c r="E307" t="n">
         <v>353</v>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6127,11 +6055,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
         <v>2024</v>
       </c>
@@ -6141,11 +6065,7 @@
       <c r="E308" t="n">
         <v>288</v>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6153,11 +6073,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="n">
         <v>2024</v>
       </c>
@@ -6167,11 +6083,7 @@
       <c r="E309" t="n">
         <v>235</v>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6179,11 +6091,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
         <v>2024</v>
       </c>
@@ -6193,11 +6101,7 @@
       <c r="E310" t="n">
         <v>390</v>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6205,11 +6109,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B311" t="inlineStr"/>
       <c r="C311" t="n">
         <v>2025</v>
       </c>
@@ -6219,11 +6119,7 @@
       <c r="E311" t="n">
         <v>565</v>
       </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6231,11 +6127,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
         <v>2025</v>
       </c>
@@ -6245,11 +6137,7 @@
       <c r="E312" t="n">
         <v>425</v>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6257,11 +6145,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
         <v>2025</v>
       </c>
@@ -6271,11 +6155,7 @@
       <c r="E313" t="n">
         <v>396</v>
       </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6283,11 +6163,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
         <v>2025</v>
       </c>
@@ -6297,11 +6173,7 @@
       <c r="E314" t="n">
         <v>327</v>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6309,11 +6181,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B315" t="inlineStr"/>
       <c r="C315" t="n">
         <v>2025</v>
       </c>
@@ -6323,11 +6191,7 @@
       <c r="E315" t="n">
         <v>367</v>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6335,11 +6199,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
         <v>2025</v>
       </c>
@@ -6349,11 +6209,7 @@
       <c r="E316" t="n">
         <v>281</v>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6361,11 +6217,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
         <v>2025</v>
       </c>
@@ -6375,11 +6227,7 @@
       <c r="E317" t="n">
         <v>321</v>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6387,11 +6235,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
         <v>2025</v>
       </c>
@@ -6401,11 +6245,7 @@
       <c r="E318" t="n">
         <v>301</v>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6413,11 +6253,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B319" t="inlineStr"/>
       <c r="C319" t="n">
         <v>2025</v>
       </c>
@@ -6427,11 +6263,7 @@
       <c r="E319" t="n">
         <v>420</v>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6439,11 +6271,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
         <v>2025</v>
       </c>
@@ -6453,11 +6281,7 @@
       <c r="E320" t="n">
         <v>355</v>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6465,11 +6289,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>2025</v>
       </c>
@@ -6479,11 +6299,7 @@
       <c r="E321" t="n">
         <v>311</v>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6491,11 +6307,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B322" t="inlineStr"/>
       <c r="C322" t="n">
         <v>2025</v>
       </c>
@@ -6505,11 +6317,7 @@
       <c r="E322" t="n">
         <v>167</v>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6517,11 +6325,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B323" t="inlineStr"/>
       <c r="C323" t="n">
         <v>2026</v>
       </c>
@@ -6531,11 +6335,7 @@
       <c r="E323" t="n">
         <v>346</v>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6543,11 +6343,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
         <v>2026</v>
       </c>
@@ -6557,11 +6353,7 @@
       <c r="E324" t="n">
         <v>215</v>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6569,11 +6361,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
         <v>2026</v>
       </c>
@@ -6583,11 +6371,7 @@
       <c r="E325" t="n">
         <v>236</v>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6595,11 +6379,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
         <v>2026</v>
       </c>
@@ -6609,11 +6389,7 @@
       <c r="E326" t="n">
         <v>222</v>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6621,11 +6397,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B327" t="inlineStr"/>
       <c r="C327" t="n">
         <v>2026</v>
       </c>
@@ -6635,11 +6407,7 @@
       <c r="E327" t="n">
         <v>215</v>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6647,11 +6415,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B328" t="inlineStr"/>
       <c r="C328" t="n">
         <v>2026</v>
       </c>
@@ -6661,11 +6425,7 @@
       <c r="E328" t="n">
         <v>212</v>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6673,11 +6433,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
         <v>2026</v>
       </c>
@@ -6687,11 +6443,7 @@
       <c r="E329" t="n">
         <v>247</v>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6699,11 +6451,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B330" t="inlineStr"/>
       <c r="C330" t="n">
         <v>2026</v>
       </c>
@@ -6713,11 +6461,7 @@
       <c r="E330" t="n">
         <v>250</v>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6737,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -6751,11 +6495,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B332" t="inlineStr"/>
       <c r="C332" t="n">
         <v>2024</v>
       </c>
@@ -6765,11 +6505,7 @@
       <c r="E332" t="n">
         <v>111</v>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6777,11 +6513,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
         <v>2024</v>
       </c>
@@ -6791,11 +6523,7 @@
       <c r="E333" t="n">
         <v>217</v>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6803,11 +6531,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
         <v>2024</v>
       </c>
@@ -6817,11 +6541,7 @@
       <c r="E334" t="n">
         <v>173</v>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6829,11 +6549,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B335" t="inlineStr"/>
       <c r="C335" t="n">
         <v>2024</v>
       </c>
@@ -6843,11 +6559,7 @@
       <c r="E335" t="n">
         <v>157</v>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6855,11 +6567,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
         <v>2024</v>
       </c>
@@ -6869,11 +6577,7 @@
       <c r="E336" t="n">
         <v>178</v>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6881,11 +6585,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
         <v>2024</v>
       </c>
@@ -6895,11 +6595,7 @@
       <c r="E337" t="n">
         <v>181</v>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6907,11 +6603,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B338" t="inlineStr"/>
       <c r="C338" t="n">
         <v>2024</v>
       </c>
@@ -6921,11 +6613,7 @@
       <c r="E338" t="n">
         <v>169</v>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6933,11 +6621,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
         <v>2024</v>
       </c>
@@ -6947,11 +6631,7 @@
       <c r="E339" t="n">
         <v>183</v>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6959,11 +6639,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
         <v>2024</v>
       </c>
@@ -6973,11 +6649,7 @@
       <c r="E340" t="n">
         <v>212</v>
       </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6985,11 +6657,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
         <v>2024</v>
       </c>
@@ -6999,11 +6667,7 @@
       <c r="E341" t="n">
         <v>177</v>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7011,11 +6675,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
         <v>2024</v>
       </c>
@@ -7025,11 +6685,7 @@
       <c r="E342" t="n">
         <v>141</v>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7037,11 +6693,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
         <v>2024</v>
       </c>
@@ -7051,11 +6703,7 @@
       <c r="E343" t="n">
         <v>181</v>
       </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7063,11 +6711,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
         <v>2025</v>
       </c>
@@ -7077,11 +6721,7 @@
       <c r="E344" t="n">
         <v>362</v>
       </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7089,11 +6729,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
         <v>2025</v>
       </c>
@@ -7103,11 +6739,7 @@
       <c r="E345" t="n">
         <v>233</v>
       </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7115,11 +6747,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
         <v>2025</v>
       </c>
@@ -7129,11 +6757,7 @@
       <c r="E346" t="n">
         <v>290</v>
       </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7141,11 +6765,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="n">
         <v>2025</v>
       </c>
@@ -7155,11 +6775,7 @@
       <c r="E347" t="n">
         <v>339</v>
       </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7167,11 +6783,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
         <v>2025</v>
       </c>
@@ -7181,11 +6793,7 @@
       <c r="E348" t="n">
         <v>337</v>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7193,11 +6801,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="n">
         <v>2025</v>
       </c>
@@ -7207,11 +6811,7 @@
       <c r="E349" t="n">
         <v>304</v>
       </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7219,11 +6819,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
         <v>2025</v>
       </c>
@@ -7233,11 +6829,7 @@
       <c r="E350" t="n">
         <v>309</v>
       </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7245,11 +6837,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
         <v>2025</v>
       </c>
@@ -7259,11 +6847,7 @@
       <c r="E351" t="n">
         <v>331</v>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7271,11 +6855,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
         <v>2025</v>
       </c>
@@ -7285,11 +6865,7 @@
       <c r="E352" t="n">
         <v>328</v>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -7297,11 +6873,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>2025</v>
       </c>
@@ -7311,11 +6883,7 @@
       <c r="E353" t="n">
         <v>326</v>
       </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -7323,11 +6891,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>2025</v>
       </c>
@@ -7337,11 +6901,7 @@
       <c r="E354" t="n">
         <v>298</v>
       </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -7349,11 +6909,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
         <v>2025</v>
       </c>
@@ -7363,11 +6919,7 @@
       <c r="E355" t="n">
         <v>227</v>
       </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -7375,11 +6927,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
         <v>2026</v>
       </c>
@@ -7389,11 +6937,7 @@
       <c r="E356" t="n">
         <v>363</v>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7401,11 +6945,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
         <v>2026</v>
       </c>
@@ -7415,11 +6955,7 @@
       <c r="E357" t="n">
         <v>252</v>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -7427,11 +6963,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
         <v>2026</v>
       </c>
@@ -7441,11 +6973,7 @@
       <c r="E358" t="n">
         <v>289</v>
       </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -7453,11 +6981,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
         <v>2026</v>
       </c>
@@ -7467,11 +6991,7 @@
       <c r="E359" t="n">
         <v>272</v>
       </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -7479,11 +6999,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
         <v>2026</v>
       </c>
@@ -7493,11 +7009,7 @@
       <c r="E360" t="n">
         <v>255</v>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -7505,11 +7017,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B361" t="inlineStr"/>
       <c r="C361" t="n">
         <v>2026</v>
       </c>
@@ -7519,11 +7027,7 @@
       <c r="E361" t="n">
         <v>198</v>
       </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -7531,11 +7035,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B362" t="inlineStr"/>
       <c r="C362" t="n">
         <v>2026</v>
       </c>
@@ -7545,11 +7045,7 @@
       <c r="E362" t="n">
         <v>278</v>
       </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -7557,11 +7053,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
         <v>2026</v>
       </c>
@@ -7571,11 +7063,7 @@
       <c r="E363" t="n">
         <v>278</v>
       </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:17</t>
-        </is>
-      </c>
+      <c r="F363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -7595,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -8197,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -8799,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -9401,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -10003,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -10605,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -11207,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -11809,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -12415,7 +11903,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -13013,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -13615,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -14217,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -14819,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -15425,7 +14913,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-22 11:17</t>
+          <t>2026-09-23 11:33</t>
         </is>
       </c>
     </row>
@@ -15754,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>694</v>
+        <v>720</v>
       </c>
     </row>
     <row r="3">
@@ -15764,103 +15252,103 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>731</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>532</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>571</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>927</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>585</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>798</v>
+        <v>851</v>
       </c>
     </row>
     <row r="4">
@@ -15966,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>570</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5">
@@ -16072,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>678</v>
+        <v>691</v>
       </c>
     </row>
     <row r="6">
@@ -16178,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2740</v>
+        <v>2861</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-23 11:33</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>851</v>
+        <v>890</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>599</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>691</v>
+        <v>710</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2861</v>
+        <v>2980</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -14913,7 +14913,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-25 11:53</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>750</v>
+        <v>772</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>890</v>
+        <v>929</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>630</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>710</v>
+        <v>735</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>2980</v>
+        <v>3088</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-25 11:53</t>
+          <t>2026-09-26 10:57</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>772</v>
+        <v>783</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>929</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>652</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>735</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>3088</v>
+        <v>3180</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-26 10:57</t>
+          <t>2026-09-27 11:53</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>783</v>
+        <v>803</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>959</v>
+        <v>976</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>666</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>772</v>
+        <v>791</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>3180</v>
+        <v>3244</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-27 11:53</t>
+          <t>2026-09-28 14:52</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>803</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>976</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>674</v>
+        <v>688</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>791</v>
+        <v>811</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>3244</v>
+        <v>3322</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C134" t="n">
         <v>2024</v>
       </c>
@@ -2893,7 +2897,11 @@
       <c r="E134" t="n">
         <v>258</v>
       </c>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2901,7 +2909,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C135" t="n">
         <v>2024</v>
       </c>
@@ -2911,7 +2923,11 @@
       <c r="E135" t="n">
         <v>131</v>
       </c>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2919,7 +2935,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C136" t="n">
         <v>2024</v>
       </c>
@@ -2929,7 +2949,11 @@
       <c r="E136" t="n">
         <v>94</v>
       </c>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2937,7 +2961,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C137" t="n">
         <v>2024</v>
       </c>
@@ -2947,7 +2975,11 @@
       <c r="E137" t="n">
         <v>57</v>
       </c>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2955,7 +2987,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C138" t="n">
         <v>2024</v>
       </c>
@@ -2965,7 +3001,11 @@
       <c r="E138" t="n">
         <v>83</v>
       </c>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2973,7 +3013,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C139" t="n">
         <v>2024</v>
       </c>
@@ -2983,7 +3027,11 @@
       <c r="E139" t="n">
         <v>86</v>
       </c>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2991,7 +3039,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C140" t="n">
         <v>2024</v>
       </c>
@@ -3001,7 +3053,11 @@
       <c r="E140" t="n">
         <v>68</v>
       </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3009,7 +3065,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C141" t="n">
         <v>2024</v>
       </c>
@@ -3019,7 +3079,11 @@
       <c r="E141" t="n">
         <v>115</v>
       </c>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3027,7 +3091,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C142" t="n">
         <v>2024</v>
       </c>
@@ -3037,7 +3105,11 @@
       <c r="E142" t="n">
         <v>102</v>
       </c>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3045,7 +3117,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C143" t="n">
         <v>2024</v>
       </c>
@@ -3055,7 +3131,11 @@
       <c r="E143" t="n">
         <v>100</v>
       </c>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3063,7 +3143,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C144" t="n">
         <v>2024</v>
       </c>
@@ -3073,7 +3157,11 @@
       <c r="E144" t="n">
         <v>62</v>
       </c>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3081,7 +3169,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C145" t="n">
         <v>2024</v>
       </c>
@@ -3091,7 +3183,11 @@
       <c r="E145" t="n">
         <v>129</v>
       </c>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3099,7 +3195,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C146" t="n">
         <v>2025</v>
       </c>
@@ -3109,7 +3209,11 @@
       <c r="E146" t="n">
         <v>232</v>
       </c>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3117,7 +3221,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C147" t="n">
         <v>2025</v>
       </c>
@@ -3127,7 +3235,11 @@
       <c r="E147" t="n">
         <v>159</v>
       </c>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3135,7 +3247,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C148" t="n">
         <v>2025</v>
       </c>
@@ -3145,7 +3261,11 @@
       <c r="E148" t="n">
         <v>138</v>
       </c>
-      <c r="F148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3153,7 +3273,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C149" t="n">
         <v>2025</v>
       </c>
@@ -3163,7 +3287,11 @@
       <c r="E149" t="n">
         <v>121</v>
       </c>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3171,7 +3299,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C150" t="n">
         <v>2025</v>
       </c>
@@ -3181,7 +3313,11 @@
       <c r="E150" t="n">
         <v>99</v>
       </c>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3189,7 +3325,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C151" t="n">
         <v>2025</v>
       </c>
@@ -3199,7 +3339,11 @@
       <c r="E151" t="n">
         <v>93</v>
       </c>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3207,7 +3351,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C152" t="n">
         <v>2025</v>
       </c>
@@ -3217,7 +3365,11 @@
       <c r="E152" t="n">
         <v>124</v>
       </c>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3225,7 +3377,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C153" t="n">
         <v>2025</v>
       </c>
@@ -3235,7 +3391,11 @@
       <c r="E153" t="n">
         <v>142</v>
       </c>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3243,7 +3403,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C154" t="n">
         <v>2025</v>
       </c>
@@ -3253,7 +3417,11 @@
       <c r="E154" t="n">
         <v>138</v>
       </c>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3261,7 +3429,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C155" t="n">
         <v>2025</v>
       </c>
@@ -3271,7 +3443,11 @@
       <c r="E155" t="n">
         <v>125</v>
       </c>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3279,7 +3455,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C156" t="n">
         <v>2025</v>
       </c>
@@ -3289,7 +3469,11 @@
       <c r="E156" t="n">
         <v>109</v>
       </c>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3297,7 +3481,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C157" t="n">
         <v>2025</v>
       </c>
@@ -3307,7 +3495,11 @@
       <c r="E157" t="n">
         <v>78</v>
       </c>
-      <c r="F157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3315,7 +3507,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C158" t="n">
         <v>2026</v>
       </c>
@@ -3325,7 +3521,11 @@
       <c r="E158" t="n">
         <v>180</v>
       </c>
-      <c r="F158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3333,7 +3533,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C159" t="n">
         <v>2026</v>
       </c>
@@ -3343,7 +3547,11 @@
       <c r="E159" t="n">
         <v>103</v>
       </c>
-      <c r="F159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3351,7 +3559,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C160" t="n">
         <v>2026</v>
       </c>
@@ -3361,7 +3573,11 @@
       <c r="E160" t="n">
         <v>83</v>
       </c>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3369,7 +3585,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C161" t="n">
         <v>2026</v>
       </c>
@@ -3379,7 +3599,11 @@
       <c r="E161" t="n">
         <v>83</v>
       </c>
-      <c r="F161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3387,7 +3611,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C162" t="n">
         <v>2026</v>
       </c>
@@ -3397,7 +3625,11 @@
       <c r="E162" t="n">
         <v>86</v>
       </c>
-      <c r="F162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3405,7 +3637,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C163" t="n">
         <v>2026</v>
       </c>
@@ -3415,7 +3651,11 @@
       <c r="E163" t="n">
         <v>74</v>
       </c>
-      <c r="F163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3423,7 +3663,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C164" t="n">
         <v>2026</v>
       </c>
@@ -3433,7 +3677,11 @@
       <c r="E164" t="n">
         <v>104</v>
       </c>
-      <c r="F164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3441,7 +3689,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C165" t="n">
         <v>2026</v>
       </c>
@@ -3451,7 +3703,11 @@
       <c r="E165" t="n">
         <v>83</v>
       </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3475,7 +3731,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4329,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4931,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4945,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C233" t="n">
         <v>2024</v>
       </c>
@@ -4699,7 +4959,11 @@
       <c r="E233" t="n">
         <v>203</v>
       </c>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4707,7 +4971,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C234" t="n">
         <v>2024</v>
       </c>
@@ -4717,7 +4985,11 @@
       <c r="E234" t="n">
         <v>147</v>
       </c>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4725,7 +4997,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C235" t="n">
         <v>2024</v>
       </c>
@@ -4735,7 +5011,11 @@
       <c r="E235" t="n">
         <v>122</v>
       </c>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4743,7 +5023,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C236" t="n">
         <v>2024</v>
       </c>
@@ -4753,7 +5037,11 @@
       <c r="E236" t="n">
         <v>129</v>
       </c>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4761,7 +5049,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C237" t="n">
         <v>2024</v>
       </c>
@@ -4771,7 +5063,11 @@
       <c r="E237" t="n">
         <v>116</v>
       </c>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4779,7 +5075,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C238" t="n">
         <v>2024</v>
       </c>
@@ -4789,7 +5089,11 @@
       <c r="E238" t="n">
         <v>110</v>
       </c>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4797,7 +5101,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C239" t="n">
         <v>2024</v>
       </c>
@@ -4807,7 +5115,11 @@
       <c r="E239" t="n">
         <v>138</v>
       </c>
-      <c r="F239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4815,7 +5127,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C240" t="n">
         <v>2024</v>
       </c>
@@ -4825,7 +5141,11 @@
       <c r="E240" t="n">
         <v>117</v>
       </c>
-      <c r="F240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4833,7 +5153,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C241" t="n">
         <v>2024</v>
       </c>
@@ -4843,7 +5167,11 @@
       <c r="E241" t="n">
         <v>122</v>
       </c>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4851,7 +5179,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C242" t="n">
         <v>2024</v>
       </c>
@@ -4861,7 +5193,11 @@
       <c r="E242" t="n">
         <v>102</v>
       </c>
-      <c r="F242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4869,7 +5205,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C243" t="n">
         <v>2024</v>
       </c>
@@ -4879,7 +5219,11 @@
       <c r="E243" t="n">
         <v>73</v>
       </c>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4887,7 +5231,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C244" t="n">
         <v>2024</v>
       </c>
@@ -4897,7 +5245,11 @@
       <c r="E244" t="n">
         <v>141</v>
       </c>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4905,7 +5257,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C245" t="n">
         <v>2025</v>
       </c>
@@ -4915,7 +5271,11 @@
       <c r="E245" t="n">
         <v>256</v>
       </c>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4923,7 +5283,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C246" t="n">
         <v>2025</v>
       </c>
@@ -4933,7 +5297,11 @@
       <c r="E246" t="n">
         <v>154</v>
       </c>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4941,7 +5309,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C247" t="n">
         <v>2025</v>
       </c>
@@ -4951,7 +5323,11 @@
       <c r="E247" t="n">
         <v>152</v>
       </c>
-      <c r="F247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4959,7 +5335,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C248" t="n">
         <v>2025</v>
       </c>
@@ -4969,7 +5349,11 @@
       <c r="E248" t="n">
         <v>101</v>
       </c>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4977,7 +5361,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C249" t="n">
         <v>2025</v>
       </c>
@@ -4987,7 +5375,11 @@
       <c r="E249" t="n">
         <v>143</v>
       </c>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4995,7 +5387,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C250" t="n">
         <v>2025</v>
       </c>
@@ -5005,7 +5401,11 @@
       <c r="E250" t="n">
         <v>121</v>
       </c>
-      <c r="F250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5013,7 +5413,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C251" t="n">
         <v>2025</v>
       </c>
@@ -5023,7 +5427,11 @@
       <c r="E251" t="n">
         <v>119</v>
       </c>
-      <c r="F251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5031,7 +5439,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C252" t="n">
         <v>2025</v>
       </c>
@@ -5041,7 +5453,11 @@
       <c r="E252" t="n">
         <v>129</v>
       </c>
-      <c r="F252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5049,7 +5465,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C253" t="n">
         <v>2025</v>
       </c>
@@ -5059,7 +5479,11 @@
       <c r="E253" t="n">
         <v>119</v>
       </c>
-      <c r="F253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5067,7 +5491,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C254" t="n">
         <v>2025</v>
       </c>
@@ -5077,7 +5505,11 @@
       <c r="E254" t="n">
         <v>115</v>
       </c>
-      <c r="F254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5085,7 +5517,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C255" t="n">
         <v>2025</v>
       </c>
@@ -5095,7 +5531,11 @@
       <c r="E255" t="n">
         <v>94</v>
       </c>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5103,7 +5543,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C256" t="n">
         <v>2025</v>
       </c>
@@ -5113,7 +5557,11 @@
       <c r="E256" t="n">
         <v>92</v>
       </c>
-      <c r="F256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5121,7 +5569,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C257" t="n">
         <v>2026</v>
       </c>
@@ -5131,7 +5583,11 @@
       <c r="E257" t="n">
         <v>165</v>
       </c>
-      <c r="F257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5139,7 +5595,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C258" t="n">
         <v>2026</v>
       </c>
@@ -5149,7 +5609,11 @@
       <c r="E258" t="n">
         <v>86</v>
       </c>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5157,7 +5621,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C259" t="n">
         <v>2026</v>
       </c>
@@ -5167,7 +5635,11 @@
       <c r="E259" t="n">
         <v>108</v>
       </c>
-      <c r="F259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5175,7 +5647,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C260" t="n">
         <v>2026</v>
       </c>
@@ -5185,7 +5661,11 @@
       <c r="E260" t="n">
         <v>115</v>
       </c>
-      <c r="F260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5193,7 +5673,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C261" t="n">
         <v>2026</v>
       </c>
@@ -5203,7 +5687,11 @@
       <c r="E261" t="n">
         <v>82</v>
       </c>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5211,7 +5699,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C262" t="n">
         <v>2026</v>
       </c>
@@ -5221,7 +5713,11 @@
       <c r="E262" t="n">
         <v>84</v>
       </c>
-      <c r="F262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5229,7 +5725,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C263" t="n">
         <v>2026</v>
       </c>
@@ -5239,7 +5739,11 @@
       <c r="E263" t="n">
         <v>108</v>
       </c>
-      <c r="F263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5247,7 +5751,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C264" t="n">
         <v>2026</v>
       </c>
@@ -5257,7 +5765,11 @@
       <c r="E264" t="n">
         <v>103</v>
       </c>
-      <c r="F264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5281,7 +5793,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -5879,11 +6391,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -5893,7 +6405,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C299" t="n">
         <v>2024</v>
       </c>
@@ -5903,7 +6419,11 @@
       <c r="E299" t="n">
         <v>354</v>
       </c>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5911,7 +6431,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C300" t="n">
         <v>2024</v>
       </c>
@@ -5921,7 +6445,11 @@
       <c r="E300" t="n">
         <v>154</v>
       </c>
-      <c r="F300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5929,7 +6457,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C301" t="n">
         <v>2024</v>
       </c>
@@ -5939,7 +6471,11 @@
       <c r="E301" t="n">
         <v>158</v>
       </c>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5947,7 +6483,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C302" t="n">
         <v>2024</v>
       </c>
@@ -5957,7 +6497,11 @@
       <c r="E302" t="n">
         <v>356</v>
       </c>
-      <c r="F302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5965,7 +6509,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C303" t="n">
         <v>2024</v>
       </c>
@@ -5975,7 +6523,11 @@
       <c r="E303" t="n">
         <v>553</v>
       </c>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5983,7 +6535,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C304" t="n">
         <v>2024</v>
       </c>
@@ -5993,7 +6549,11 @@
       <c r="E304" t="n">
         <v>399</v>
       </c>
-      <c r="F304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6001,7 +6561,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C305" t="n">
         <v>2024</v>
       </c>
@@ -6011,7 +6575,11 @@
       <c r="E305" t="n">
         <v>132</v>
       </c>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6019,7 +6587,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C306" t="n">
         <v>2024</v>
       </c>
@@ -6029,7 +6601,11 @@
       <c r="E306" t="n">
         <v>349</v>
       </c>
-      <c r="F306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6037,7 +6613,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C307" t="n">
         <v>2024</v>
       </c>
@@ -6047,7 +6627,11 @@
       <c r="E307" t="n">
         <v>353</v>
       </c>
-      <c r="F307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6055,7 +6639,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C308" t="n">
         <v>2024</v>
       </c>
@@ -6065,7 +6653,11 @@
       <c r="E308" t="n">
         <v>288</v>
       </c>
-      <c r="F308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6073,7 +6665,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C309" t="n">
         <v>2024</v>
       </c>
@@ -6083,7 +6679,11 @@
       <c r="E309" t="n">
         <v>235</v>
       </c>
-      <c r="F309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6091,7 +6691,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C310" t="n">
         <v>2024</v>
       </c>
@@ -6101,7 +6705,11 @@
       <c r="E310" t="n">
         <v>390</v>
       </c>
-      <c r="F310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6109,7 +6717,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C311" t="n">
         <v>2025</v>
       </c>
@@ -6119,7 +6731,11 @@
       <c r="E311" t="n">
         <v>565</v>
       </c>
-      <c r="F311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6127,7 +6743,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C312" t="n">
         <v>2025</v>
       </c>
@@ -6137,7 +6757,11 @@
       <c r="E312" t="n">
         <v>425</v>
       </c>
-      <c r="F312" t="inlineStr"/>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6145,7 +6769,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C313" t="n">
         <v>2025</v>
       </c>
@@ -6155,7 +6783,11 @@
       <c r="E313" t="n">
         <v>396</v>
       </c>
-      <c r="F313" t="inlineStr"/>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6163,7 +6795,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C314" t="n">
         <v>2025</v>
       </c>
@@ -6173,7 +6809,11 @@
       <c r="E314" t="n">
         <v>327</v>
       </c>
-      <c r="F314" t="inlineStr"/>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6181,7 +6821,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C315" t="n">
         <v>2025</v>
       </c>
@@ -6191,7 +6835,11 @@
       <c r="E315" t="n">
         <v>367</v>
       </c>
-      <c r="F315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6199,7 +6847,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C316" t="n">
         <v>2025</v>
       </c>
@@ -6209,7 +6861,11 @@
       <c r="E316" t="n">
         <v>281</v>
       </c>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6217,7 +6873,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C317" t="n">
         <v>2025</v>
       </c>
@@ -6227,7 +6887,11 @@
       <c r="E317" t="n">
         <v>321</v>
       </c>
-      <c r="F317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6235,7 +6899,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C318" t="n">
         <v>2025</v>
       </c>
@@ -6245,7 +6913,11 @@
       <c r="E318" t="n">
         <v>301</v>
       </c>
-      <c r="F318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6253,7 +6925,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C319" t="n">
         <v>2025</v>
       </c>
@@ -6263,7 +6939,11 @@
       <c r="E319" t="n">
         <v>420</v>
       </c>
-      <c r="F319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6271,7 +6951,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C320" t="n">
         <v>2025</v>
       </c>
@@ -6281,7 +6965,11 @@
       <c r="E320" t="n">
         <v>355</v>
       </c>
-      <c r="F320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6289,7 +6977,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C321" t="n">
         <v>2025</v>
       </c>
@@ -6299,7 +6991,11 @@
       <c r="E321" t="n">
         <v>311</v>
       </c>
-      <c r="F321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6307,7 +7003,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C322" t="n">
         <v>2025</v>
       </c>
@@ -6317,7 +7017,11 @@
       <c r="E322" t="n">
         <v>167</v>
       </c>
-      <c r="F322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6325,7 +7029,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C323" t="n">
         <v>2026</v>
       </c>
@@ -6335,7 +7043,11 @@
       <c r="E323" t="n">
         <v>346</v>
       </c>
-      <c r="F323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6343,7 +7055,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C324" t="n">
         <v>2026</v>
       </c>
@@ -6353,7 +7069,11 @@
       <c r="E324" t="n">
         <v>215</v>
       </c>
-      <c r="F324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6361,7 +7081,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C325" t="n">
         <v>2026</v>
       </c>
@@ -6371,7 +7095,11 @@
       <c r="E325" t="n">
         <v>236</v>
       </c>
-      <c r="F325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6379,7 +7107,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C326" t="n">
         <v>2026</v>
       </c>
@@ -6389,7 +7121,11 @@
       <c r="E326" t="n">
         <v>222</v>
       </c>
-      <c r="F326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6397,7 +7133,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C327" t="n">
         <v>2026</v>
       </c>
@@ -6407,7 +7147,11 @@
       <c r="E327" t="n">
         <v>215</v>
       </c>
-      <c r="F327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6415,7 +7159,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C328" t="n">
         <v>2026</v>
       </c>
@@ -6425,7 +7173,11 @@
       <c r="E328" t="n">
         <v>212</v>
       </c>
-      <c r="F328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6433,7 +7185,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C329" t="n">
         <v>2026</v>
       </c>
@@ -6443,7 +7199,11 @@
       <c r="E329" t="n">
         <v>247</v>
       </c>
-      <c r="F329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6451,7 +7211,11 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C330" t="n">
         <v>2026</v>
       </c>
@@ -6461,7 +7225,11 @@
       <c r="E330" t="n">
         <v>250</v>
       </c>
-      <c r="F330" t="inlineStr"/>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6485,7 +7253,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -6495,7 +7263,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C332" t="n">
         <v>2024</v>
       </c>
@@ -6505,7 +7277,11 @@
       <c r="E332" t="n">
         <v>111</v>
       </c>
-      <c r="F332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6513,7 +7289,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C333" t="n">
         <v>2024</v>
       </c>
@@ -6523,7 +7303,11 @@
       <c r="E333" t="n">
         <v>217</v>
       </c>
-      <c r="F333" t="inlineStr"/>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6531,7 +7315,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C334" t="n">
         <v>2024</v>
       </c>
@@ -6541,7 +7329,11 @@
       <c r="E334" t="n">
         <v>173</v>
       </c>
-      <c r="F334" t="inlineStr"/>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6549,7 +7341,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C335" t="n">
         <v>2024</v>
       </c>
@@ -6559,7 +7355,11 @@
       <c r="E335" t="n">
         <v>157</v>
       </c>
-      <c r="F335" t="inlineStr"/>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6567,7 +7367,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C336" t="n">
         <v>2024</v>
       </c>
@@ -6577,7 +7381,11 @@
       <c r="E336" t="n">
         <v>178</v>
       </c>
-      <c r="F336" t="inlineStr"/>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6585,7 +7393,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C337" t="n">
         <v>2024</v>
       </c>
@@ -6595,7 +7407,11 @@
       <c r="E337" t="n">
         <v>181</v>
       </c>
-      <c r="F337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6603,7 +7419,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C338" t="n">
         <v>2024</v>
       </c>
@@ -6613,7 +7433,11 @@
       <c r="E338" t="n">
         <v>169</v>
       </c>
-      <c r="F338" t="inlineStr"/>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6621,7 +7445,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C339" t="n">
         <v>2024</v>
       </c>
@@ -6631,7 +7459,11 @@
       <c r="E339" t="n">
         <v>183</v>
       </c>
-      <c r="F339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6639,7 +7471,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C340" t="n">
         <v>2024</v>
       </c>
@@ -6649,7 +7485,11 @@
       <c r="E340" t="n">
         <v>212</v>
       </c>
-      <c r="F340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6657,7 +7497,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C341" t="n">
         <v>2024</v>
       </c>
@@ -6667,7 +7511,11 @@
       <c r="E341" t="n">
         <v>177</v>
       </c>
-      <c r="F341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6675,7 +7523,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C342" t="n">
         <v>2024</v>
       </c>
@@ -6685,7 +7537,11 @@
       <c r="E342" t="n">
         <v>141</v>
       </c>
-      <c r="F342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6693,7 +7549,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C343" t="n">
         <v>2024</v>
       </c>
@@ -6703,7 +7563,11 @@
       <c r="E343" t="n">
         <v>181</v>
       </c>
-      <c r="F343" t="inlineStr"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6711,7 +7575,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C344" t="n">
         <v>2025</v>
       </c>
@@ -6721,7 +7589,11 @@
       <c r="E344" t="n">
         <v>362</v>
       </c>
-      <c r="F344" t="inlineStr"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6729,7 +7601,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C345" t="n">
         <v>2025</v>
       </c>
@@ -6739,7 +7615,11 @@
       <c r="E345" t="n">
         <v>233</v>
       </c>
-      <c r="F345" t="inlineStr"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -6747,7 +7627,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C346" t="n">
         <v>2025</v>
       </c>
@@ -6757,7 +7641,11 @@
       <c r="E346" t="n">
         <v>290</v>
       </c>
-      <c r="F346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -6765,7 +7653,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C347" t="n">
         <v>2025</v>
       </c>
@@ -6775,7 +7667,11 @@
       <c r="E347" t="n">
         <v>339</v>
       </c>
-      <c r="F347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6783,7 +7679,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C348" t="n">
         <v>2025</v>
       </c>
@@ -6793,7 +7693,11 @@
       <c r="E348" t="n">
         <v>337</v>
       </c>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6801,7 +7705,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C349" t="n">
         <v>2025</v>
       </c>
@@ -6811,7 +7719,11 @@
       <c r="E349" t="n">
         <v>304</v>
       </c>
-      <c r="F349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6819,7 +7731,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C350" t="n">
         <v>2025</v>
       </c>
@@ -6829,7 +7745,11 @@
       <c r="E350" t="n">
         <v>309</v>
       </c>
-      <c r="F350" t="inlineStr"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6837,7 +7757,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C351" t="n">
         <v>2025</v>
       </c>
@@ -6847,7 +7771,11 @@
       <c r="E351" t="n">
         <v>331</v>
       </c>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6855,7 +7783,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C352" t="n">
         <v>2025</v>
       </c>
@@ -6865,7 +7797,11 @@
       <c r="E352" t="n">
         <v>328</v>
       </c>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6873,7 +7809,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C353" t="n">
         <v>2025</v>
       </c>
@@ -6883,7 +7823,11 @@
       <c r="E353" t="n">
         <v>326</v>
       </c>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6891,7 +7835,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C354" t="n">
         <v>2025</v>
       </c>
@@ -6901,7 +7849,11 @@
       <c r="E354" t="n">
         <v>298</v>
       </c>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6909,7 +7861,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C355" t="n">
         <v>2025</v>
       </c>
@@ -6919,7 +7875,11 @@
       <c r="E355" t="n">
         <v>227</v>
       </c>
-      <c r="F355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6927,7 +7887,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C356" t="n">
         <v>2026</v>
       </c>
@@ -6937,7 +7901,11 @@
       <c r="E356" t="n">
         <v>363</v>
       </c>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6945,7 +7913,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C357" t="n">
         <v>2026</v>
       </c>
@@ -6955,7 +7927,11 @@
       <c r="E357" t="n">
         <v>252</v>
       </c>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6963,7 +7939,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C358" t="n">
         <v>2026</v>
       </c>
@@ -6973,7 +7953,11 @@
       <c r="E358" t="n">
         <v>289</v>
       </c>
-      <c r="F358" t="inlineStr"/>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6981,7 +7965,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C359" t="n">
         <v>2026</v>
       </c>
@@ -6991,7 +7979,11 @@
       <c r="E359" t="n">
         <v>272</v>
       </c>
-      <c r="F359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6999,7 +7991,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C360" t="n">
         <v>2026</v>
       </c>
@@ -7009,7 +8005,11 @@
       <c r="E360" t="n">
         <v>255</v>
       </c>
-      <c r="F360" t="inlineStr"/>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -7017,7 +8017,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C361" t="n">
         <v>2026</v>
       </c>
@@ -7027,7 +8031,11 @@
       <c r="E361" t="n">
         <v>198</v>
       </c>
-      <c r="F361" t="inlineStr"/>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -7035,7 +8043,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C362" t="n">
         <v>2026</v>
       </c>
@@ -7045,7 +8057,11 @@
       <c r="E362" t="n">
         <v>278</v>
       </c>
-      <c r="F362" t="inlineStr"/>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -7053,7 +8069,11 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C363" t="n">
         <v>2026</v>
       </c>
@@ -7063,7 +8083,11 @@
       <c r="E363" t="n">
         <v>278</v>
       </c>
-      <c r="F363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -7087,7 +8111,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -7685,11 +8709,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -7699,7 +8723,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C398" t="n">
         <v>2024</v>
       </c>
@@ -7709,7 +8737,11 @@
       <c r="E398" t="n">
         <v>199</v>
       </c>
-      <c r="F398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -7717,7 +8749,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C399" t="n">
         <v>2024</v>
       </c>
@@ -7727,7 +8763,11 @@
       <c r="E399" t="n">
         <v>136</v>
       </c>
-      <c r="F399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -7735,7 +8775,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C400" t="n">
         <v>2024</v>
       </c>
@@ -7745,7 +8789,11 @@
       <c r="E400" t="n">
         <v>148</v>
       </c>
-      <c r="F400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -7753,7 +8801,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C401" t="n">
         <v>2024</v>
       </c>
@@ -7763,7 +8815,11 @@
       <c r="E401" t="n">
         <v>108</v>
       </c>
-      <c r="F401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -7771,7 +8827,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C402" t="n">
         <v>2024</v>
       </c>
@@ -7781,7 +8841,11 @@
       <c r="E402" t="n">
         <v>135</v>
       </c>
-      <c r="F402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -7789,7 +8853,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C403" t="n">
         <v>2024</v>
       </c>
@@ -7799,7 +8867,11 @@
       <c r="E403" t="n">
         <v>142</v>
       </c>
-      <c r="F403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -7807,7 +8879,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C404" t="n">
         <v>2024</v>
       </c>
@@ -7817,7 +8893,11 @@
       <c r="E404" t="n">
         <v>63</v>
       </c>
-      <c r="F404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -7825,7 +8905,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C405" t="n">
         <v>2024</v>
       </c>
@@ -7835,7 +8919,11 @@
       <c r="E405" t="n">
         <v>179</v>
       </c>
-      <c r="F405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -7843,7 +8931,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C406" t="n">
         <v>2024</v>
       </c>
@@ -7853,7 +8945,11 @@
       <c r="E406" t="n">
         <v>198</v>
       </c>
-      <c r="F406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -7861,7 +8957,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C407" t="n">
         <v>2024</v>
       </c>
@@ -7871,7 +8971,11 @@
       <c r="E407" t="n">
         <v>126</v>
       </c>
-      <c r="F407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -7879,7 +8983,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C408" t="n">
         <v>2024</v>
       </c>
@@ -7889,7 +8997,11 @@
       <c r="E408" t="n">
         <v>143</v>
       </c>
-      <c r="F408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -7897,7 +9009,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C409" t="n">
         <v>2024</v>
       </c>
@@ -7907,7 +9023,11 @@
       <c r="E409" t="n">
         <v>180</v>
       </c>
-      <c r="F409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -7915,7 +9035,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr"/>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C410" t="n">
         <v>2025</v>
       </c>
@@ -7925,7 +9049,11 @@
       <c r="E410" t="n">
         <v>301</v>
       </c>
-      <c r="F410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -7933,7 +9061,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C411" t="n">
         <v>2025</v>
       </c>
@@ -7943,7 +9075,11 @@
       <c r="E411" t="n">
         <v>225</v>
       </c>
-      <c r="F411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -7951,7 +9087,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C412" t="n">
         <v>2025</v>
       </c>
@@ -7961,7 +9101,11 @@
       <c r="E412" t="n">
         <v>185</v>
       </c>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -7969,7 +9113,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C413" t="n">
         <v>2025</v>
       </c>
@@ -7979,7 +9127,11 @@
       <c r="E413" t="n">
         <v>173</v>
       </c>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -7987,7 +9139,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr"/>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C414" t="n">
         <v>2025</v>
       </c>
@@ -7997,7 +9153,11 @@
       <c r="E414" t="n">
         <v>235</v>
       </c>
-      <c r="F414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -8005,7 +9165,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C415" t="n">
         <v>2025</v>
       </c>
@@ -8015,7 +9179,11 @@
       <c r="E415" t="n">
         <v>176</v>
       </c>
-      <c r="F415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -8023,7 +9191,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr"/>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C416" t="n">
         <v>2025</v>
       </c>
@@ -8033,7 +9205,11 @@
       <c r="E416" t="n">
         <v>229</v>
       </c>
-      <c r="F416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -8041,7 +9217,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C417" t="n">
         <v>2025</v>
       </c>
@@ -8051,7 +9231,11 @@
       <c r="E417" t="n">
         <v>248</v>
       </c>
-      <c r="F417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -8059,7 +9243,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr"/>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C418" t="n">
         <v>2025</v>
       </c>
@@ -8069,7 +9257,11 @@
       <c r="E418" t="n">
         <v>214</v>
       </c>
-      <c r="F418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -8077,7 +9269,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr"/>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C419" t="n">
         <v>2025</v>
       </c>
@@ -8087,7 +9283,11 @@
       <c r="E419" t="n">
         <v>194</v>
       </c>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -8095,7 +9295,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr"/>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C420" t="n">
         <v>2025</v>
       </c>
@@ -8105,7 +9309,11 @@
       <c r="E420" t="n">
         <v>185</v>
       </c>
-      <c r="F420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -8113,7 +9321,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C421" t="n">
         <v>2025</v>
       </c>
@@ -8123,7 +9335,11 @@
       <c r="E421" t="n">
         <v>146</v>
       </c>
-      <c r="F421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -8131,7 +9347,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr"/>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C422" t="n">
         <v>2026</v>
       </c>
@@ -8141,7 +9361,11 @@
       <c r="E422" t="n">
         <v>229</v>
       </c>
-      <c r="F422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -8149,7 +9373,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr"/>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C423" t="n">
         <v>2026</v>
       </c>
@@ -8159,7 +9387,11 @@
       <c r="E423" t="n">
         <v>126</v>
       </c>
-      <c r="F423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -8167,7 +9399,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr"/>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C424" t="n">
         <v>2026</v>
       </c>
@@ -8177,7 +9413,11 @@
       <c r="E424" t="n">
         <v>156</v>
       </c>
-      <c r="F424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -8185,7 +9425,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr"/>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C425" t="n">
         <v>2026</v>
       </c>
@@ -8195,7 +9439,11 @@
       <c r="E425" t="n">
         <v>168</v>
       </c>
-      <c r="F425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -8203,7 +9451,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr"/>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C426" t="n">
         <v>2026</v>
       </c>
@@ -8213,7 +9465,11 @@
       <c r="E426" t="n">
         <v>132</v>
       </c>
-      <c r="F426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -8221,7 +9477,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr"/>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C427" t="n">
         <v>2026</v>
       </c>
@@ -8231,7 +9491,11 @@
       <c r="E427" t="n">
         <v>122</v>
       </c>
-      <c r="F427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -8239,7 +9503,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr"/>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C428" t="n">
         <v>2026</v>
       </c>
@@ -8249,7 +9517,11 @@
       <c r="E428" t="n">
         <v>241</v>
       </c>
-      <c r="F428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -8257,7 +9529,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr"/>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C429" t="n">
         <v>2026</v>
       </c>
@@ -8267,7 +9543,11 @@
       <c r="E429" t="n">
         <v>262</v>
       </c>
-      <c r="F429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -8291,7 +9571,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -8889,11 +10169,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -9491,11 +10771,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -10093,11 +11373,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -10107,7 +11387,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr"/>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C530" t="n">
         <v>2024</v>
       </c>
@@ -10117,7 +11401,11 @@
       <c r="E530" t="n">
         <v>101</v>
       </c>
-      <c r="F530" t="inlineStr"/>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -10125,7 +11413,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B531" t="inlineStr"/>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C531" t="n">
         <v>2024</v>
       </c>
@@ -10135,7 +11427,11 @@
       <c r="E531" t="n">
         <v>58</v>
       </c>
-      <c r="F531" t="inlineStr"/>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -10143,7 +11439,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr"/>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C532" t="n">
         <v>2024</v>
       </c>
@@ -10153,7 +11453,11 @@
       <c r="E532" t="n">
         <v>70</v>
       </c>
-      <c r="F532" t="inlineStr"/>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -10161,7 +11465,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B533" t="inlineStr"/>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C533" t="n">
         <v>2024</v>
       </c>
@@ -10171,7 +11479,11 @@
       <c r="E533" t="n">
         <v>53</v>
       </c>
-      <c r="F533" t="inlineStr"/>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -10179,7 +11491,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B534" t="inlineStr"/>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C534" t="n">
         <v>2024</v>
       </c>
@@ -10189,7 +11505,11 @@
       <c r="E534" t="n">
         <v>49</v>
       </c>
-      <c r="F534" t="inlineStr"/>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -10197,7 +11517,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B535" t="inlineStr"/>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C535" t="n">
         <v>2024</v>
       </c>
@@ -10207,7 +11531,11 @@
       <c r="E535" t="n">
         <v>48</v>
       </c>
-      <c r="F535" t="inlineStr"/>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -10215,7 +11543,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B536" t="inlineStr"/>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C536" t="n">
         <v>2024</v>
       </c>
@@ -10225,7 +11557,11 @@
       <c r="E536" t="n">
         <v>41</v>
       </c>
-      <c r="F536" t="inlineStr"/>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -10233,7 +11569,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B537" t="inlineStr"/>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C537" t="n">
         <v>2024</v>
       </c>
@@ -10243,7 +11583,11 @@
       <c r="E537" t="n">
         <v>76</v>
       </c>
-      <c r="F537" t="inlineStr"/>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -10251,7 +11595,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr"/>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C538" t="n">
         <v>2024</v>
       </c>
@@ -10261,7 +11609,11 @@
       <c r="E538" t="n">
         <v>49</v>
       </c>
-      <c r="F538" t="inlineStr"/>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -10269,7 +11621,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B539" t="inlineStr"/>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C539" t="n">
         <v>2024</v>
       </c>
@@ -10279,7 +11635,11 @@
       <c r="E539" t="n">
         <v>83</v>
       </c>
-      <c r="F539" t="inlineStr"/>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -10287,7 +11647,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B540" t="inlineStr"/>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C540" t="n">
         <v>2024</v>
       </c>
@@ -10297,7 +11661,11 @@
       <c r="E540" t="n">
         <v>54</v>
       </c>
-      <c r="F540" t="inlineStr"/>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -10305,7 +11673,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr"/>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C541" t="n">
         <v>2024</v>
       </c>
@@ -10315,7 +11687,11 @@
       <c r="E541" t="n">
         <v>117</v>
       </c>
-      <c r="F541" t="inlineStr"/>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -10323,7 +11699,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B542" t="inlineStr"/>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C542" t="n">
         <v>2025</v>
       </c>
@@ -10333,7 +11713,11 @@
       <c r="E542" t="n">
         <v>171</v>
       </c>
-      <c r="F542" t="inlineStr"/>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -10341,7 +11725,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B543" t="inlineStr"/>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C543" t="n">
         <v>2025</v>
       </c>
@@ -10351,7 +11739,11 @@
       <c r="E543" t="n">
         <v>85</v>
       </c>
-      <c r="F543" t="inlineStr"/>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -10359,7 +11751,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B544" t="inlineStr"/>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C544" t="n">
         <v>2025</v>
       </c>
@@ -10369,7 +11765,11 @@
       <c r="E544" t="n">
         <v>108</v>
       </c>
-      <c r="F544" t="inlineStr"/>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -10377,7 +11777,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr"/>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C545" t="n">
         <v>2025</v>
       </c>
@@ -10387,7 +11791,11 @@
       <c r="E545" t="n">
         <v>90</v>
       </c>
-      <c r="F545" t="inlineStr"/>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -10395,7 +11803,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B546" t="inlineStr"/>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C546" t="n">
         <v>2025</v>
       </c>
@@ -10405,7 +11817,11 @@
       <c r="E546" t="n">
         <v>87</v>
       </c>
-      <c r="F546" t="inlineStr"/>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -10413,7 +11829,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B547" t="inlineStr"/>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C547" t="n">
         <v>2025</v>
       </c>
@@ -10423,7 +11843,11 @@
       <c r="E547" t="n">
         <v>71</v>
       </c>
-      <c r="F547" t="inlineStr"/>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -10431,7 +11855,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B548" t="inlineStr"/>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C548" t="n">
         <v>2025</v>
       </c>
@@ -10441,7 +11869,11 @@
       <c r="E548" t="n">
         <v>107</v>
       </c>
-      <c r="F548" t="inlineStr"/>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -10449,7 +11881,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B549" t="inlineStr"/>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C549" t="n">
         <v>2025</v>
       </c>
@@ -10459,7 +11895,11 @@
       <c r="E549" t="n">
         <v>85</v>
       </c>
-      <c r="F549" t="inlineStr"/>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -10467,7 +11907,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B550" t="inlineStr"/>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C550" t="n">
         <v>2025</v>
       </c>
@@ -10477,7 +11921,11 @@
       <c r="E550" t="n">
         <v>89</v>
       </c>
-      <c r="F550" t="inlineStr"/>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -10485,7 +11933,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B551" t="inlineStr"/>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C551" t="n">
         <v>2025</v>
       </c>
@@ -10495,7 +11947,11 @@
       <c r="E551" t="n">
         <v>75</v>
       </c>
-      <c r="F551" t="inlineStr"/>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -10503,7 +11959,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B552" t="inlineStr"/>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C552" t="n">
         <v>2025</v>
       </c>
@@ -10513,7 +11973,11 @@
       <c r="E552" t="n">
         <v>58</v>
       </c>
-      <c r="F552" t="inlineStr"/>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -10521,7 +11985,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B553" t="inlineStr"/>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C553" t="n">
         <v>2025</v>
       </c>
@@ -10531,7 +11999,11 @@
       <c r="E553" t="n">
         <v>64</v>
       </c>
-      <c r="F553" t="inlineStr"/>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -10539,7 +12011,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr"/>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C554" t="n">
         <v>2026</v>
       </c>
@@ -10549,7 +12025,11 @@
       <c r="E554" t="n">
         <v>121</v>
       </c>
-      <c r="F554" t="inlineStr"/>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -10557,7 +12037,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr"/>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C555" t="n">
         <v>2026</v>
       </c>
@@ -10567,7 +12051,11 @@
       <c r="E555" t="n">
         <v>84</v>
       </c>
-      <c r="F555" t="inlineStr"/>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -10575,7 +12063,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr"/>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C556" t="n">
         <v>2026</v>
       </c>
@@ -10585,7 +12077,11 @@
       <c r="E556" t="n">
         <v>72</v>
       </c>
-      <c r="F556" t="inlineStr"/>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -10593,7 +12089,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B557" t="inlineStr"/>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C557" t="n">
         <v>2026</v>
       </c>
@@ -10603,7 +12103,11 @@
       <c r="E557" t="n">
         <v>73</v>
       </c>
-      <c r="F557" t="inlineStr"/>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -10611,7 +12115,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr"/>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C558" t="n">
         <v>2026</v>
       </c>
@@ -10621,7 +12129,11 @@
       <c r="E558" t="n">
         <v>87</v>
       </c>
-      <c r="F558" t="inlineStr"/>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -10629,7 +12141,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr"/>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C559" t="n">
         <v>2026</v>
       </c>
@@ -10639,7 +12155,11 @@
       <c r="E559" t="n">
         <v>52</v>
       </c>
-      <c r="F559" t="inlineStr"/>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -10647,7 +12167,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B560" t="inlineStr"/>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C560" t="n">
         <v>2026</v>
       </c>
@@ -10657,7 +12181,11 @@
       <c r="E560" t="n">
         <v>97</v>
       </c>
-      <c r="F560" t="inlineStr"/>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -10665,7 +12193,11 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr"/>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C561" t="n">
         <v>2026</v>
       </c>
@@ -10675,7 +12207,11 @@
       <c r="E561" t="n">
         <v>64</v>
       </c>
-      <c r="F561" t="inlineStr"/>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -10699,7 +12235,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -10709,7 +12245,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr"/>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C563" t="n">
         <v>2024</v>
       </c>
@@ -10719,7 +12259,11 @@
       <c r="E563" t="n">
         <v>255</v>
       </c>
-      <c r="F563" t="inlineStr"/>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -10727,7 +12271,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B564" t="inlineStr"/>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C564" t="n">
         <v>2024</v>
       </c>
@@ -10737,7 +12285,11 @@
       <c r="E564" t="n">
         <v>164</v>
       </c>
-      <c r="F564" t="inlineStr"/>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -10745,7 +12297,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B565" t="inlineStr"/>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C565" t="n">
         <v>2024</v>
       </c>
@@ -10755,7 +12311,11 @@
       <c r="E565" t="n">
         <v>179</v>
       </c>
-      <c r="F565" t="inlineStr"/>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -10763,7 +12323,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B566" t="inlineStr"/>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C566" t="n">
         <v>2024</v>
       </c>
@@ -10773,7 +12337,11 @@
       <c r="E566" t="n">
         <v>132</v>
       </c>
-      <c r="F566" t="inlineStr"/>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -10781,7 +12349,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B567" t="inlineStr"/>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C567" t="n">
         <v>2024</v>
       </c>
@@ -10791,7 +12363,11 @@
       <c r="E567" t="n">
         <v>118</v>
       </c>
-      <c r="F567" t="inlineStr"/>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -10799,7 +12375,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B568" t="inlineStr"/>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C568" t="n">
         <v>2024</v>
       </c>
@@ -10809,7 +12389,11 @@
       <c r="E568" t="n">
         <v>113</v>
       </c>
-      <c r="F568" t="inlineStr"/>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -10817,7 +12401,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B569" t="inlineStr"/>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C569" t="n">
         <v>2024</v>
       </c>
@@ -10827,7 +12415,11 @@
       <c r="E569" t="n">
         <v>57</v>
       </c>
-      <c r="F569" t="inlineStr"/>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -10835,7 +12427,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B570" t="inlineStr"/>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C570" t="n">
         <v>2024</v>
       </c>
@@ -10845,7 +12441,11 @@
       <c r="E570" t="n">
         <v>136</v>
       </c>
-      <c r="F570" t="inlineStr"/>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -10853,7 +12453,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B571" t="inlineStr"/>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C571" t="n">
         <v>2024</v>
       </c>
@@ -10863,7 +12467,11 @@
       <c r="E571" t="n">
         <v>139</v>
       </c>
-      <c r="F571" t="inlineStr"/>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -10871,7 +12479,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B572" t="inlineStr"/>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C572" t="n">
         <v>2024</v>
       </c>
@@ -10881,7 +12493,11 @@
       <c r="E572" t="n">
         <v>146</v>
       </c>
-      <c r="F572" t="inlineStr"/>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -10889,7 +12505,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B573" t="inlineStr"/>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C573" t="n">
         <v>2024</v>
       </c>
@@ -10899,7 +12519,11 @@
       <c r="E573" t="n">
         <v>133</v>
       </c>
-      <c r="F573" t="inlineStr"/>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -10907,7 +12531,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B574" t="inlineStr"/>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C574" t="n">
         <v>2024</v>
       </c>
@@ -10917,7 +12545,11 @@
       <c r="E574" t="n">
         <v>174</v>
       </c>
-      <c r="F574" t="inlineStr"/>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -10925,7 +12557,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B575" t="inlineStr"/>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C575" t="n">
         <v>2025</v>
       </c>
@@ -10935,7 +12571,11 @@
       <c r="E575" t="n">
         <v>271</v>
       </c>
-      <c r="F575" t="inlineStr"/>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -10943,7 +12583,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B576" t="inlineStr"/>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C576" t="n">
         <v>2025</v>
       </c>
@@ -10953,7 +12597,11 @@
       <c r="E576" t="n">
         <v>193</v>
       </c>
-      <c r="F576" t="inlineStr"/>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -10961,7 +12609,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B577" t="inlineStr"/>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C577" t="n">
         <v>2025</v>
       </c>
@@ -10971,7 +12623,11 @@
       <c r="E577" t="n">
         <v>155</v>
       </c>
-      <c r="F577" t="inlineStr"/>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -10979,7 +12635,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B578" t="inlineStr"/>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C578" t="n">
         <v>2025</v>
       </c>
@@ -10989,7 +12649,11 @@
       <c r="E578" t="n">
         <v>135</v>
       </c>
-      <c r="F578" t="inlineStr"/>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -10997,7 +12661,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B579" t="inlineStr"/>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C579" t="n">
         <v>2025</v>
       </c>
@@ -11007,7 +12675,11 @@
       <c r="E579" t="n">
         <v>186</v>
       </c>
-      <c r="F579" t="inlineStr"/>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -11015,7 +12687,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B580" t="inlineStr"/>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C580" t="n">
         <v>2025</v>
       </c>
@@ -11025,7 +12701,11 @@
       <c r="E580" t="n">
         <v>153</v>
       </c>
-      <c r="F580" t="inlineStr"/>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -11033,7 +12713,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B581" t="inlineStr"/>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C581" t="n">
         <v>2025</v>
       </c>
@@ -11043,7 +12727,11 @@
       <c r="E581" t="n">
         <v>157</v>
       </c>
-      <c r="F581" t="inlineStr"/>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -11051,7 +12739,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr"/>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C582" t="n">
         <v>2025</v>
       </c>
@@ -11061,7 +12753,11 @@
       <c r="E582" t="n">
         <v>149</v>
       </c>
-      <c r="F582" t="inlineStr"/>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -11069,7 +12765,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B583" t="inlineStr"/>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C583" t="n">
         <v>2025</v>
       </c>
@@ -11079,7 +12779,11 @@
       <c r="E583" t="n">
         <v>167</v>
       </c>
-      <c r="F583" t="inlineStr"/>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -11087,7 +12791,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B584" t="inlineStr"/>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C584" t="n">
         <v>2025</v>
       </c>
@@ -11097,7 +12805,11 @@
       <c r="E584" t="n">
         <v>146</v>
       </c>
-      <c r="F584" t="inlineStr"/>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -11105,7 +12817,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B585" t="inlineStr"/>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C585" t="n">
         <v>2025</v>
       </c>
@@ -11115,7 +12831,11 @@
       <c r="E585" t="n">
         <v>159</v>
       </c>
-      <c r="F585" t="inlineStr"/>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -11123,7 +12843,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B586" t="inlineStr"/>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C586" t="n">
         <v>2025</v>
       </c>
@@ -11133,7 +12857,11 @@
       <c r="E586" t="n">
         <v>130</v>
       </c>
-      <c r="F586" t="inlineStr"/>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -11141,7 +12869,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B587" t="inlineStr"/>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C587" t="n">
         <v>2026</v>
       </c>
@@ -11151,7 +12883,11 @@
       <c r="E587" t="n">
         <v>221</v>
       </c>
-      <c r="F587" t="inlineStr"/>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -11159,7 +12895,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B588" t="inlineStr"/>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C588" t="n">
         <v>2026</v>
       </c>
@@ -11169,7 +12909,11 @@
       <c r="E588" t="n">
         <v>113</v>
       </c>
-      <c r="F588" t="inlineStr"/>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -11177,7 +12921,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B589" t="inlineStr"/>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C589" t="n">
         <v>2026</v>
       </c>
@@ -11187,7 +12935,11 @@
       <c r="E589" t="n">
         <v>119</v>
       </c>
-      <c r="F589" t="inlineStr"/>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -11195,7 +12947,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B590" t="inlineStr"/>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C590" t="n">
         <v>2026</v>
       </c>
@@ -11205,7 +12961,11 @@
       <c r="E590" t="n">
         <v>117</v>
       </c>
-      <c r="F590" t="inlineStr"/>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -11213,7 +12973,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B591" t="inlineStr"/>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C591" t="n">
         <v>2026</v>
       </c>
@@ -11223,7 +12987,11 @@
       <c r="E591" t="n">
         <v>124</v>
       </c>
-      <c r="F591" t="inlineStr"/>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -11231,7 +12999,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B592" t="inlineStr"/>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C592" t="n">
         <v>2026</v>
       </c>
@@ -11241,7 +13013,11 @@
       <c r="E592" t="n">
         <v>103</v>
       </c>
-      <c r="F592" t="inlineStr"/>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -11249,7 +13025,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B593" t="inlineStr"/>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C593" t="n">
         <v>2026</v>
       </c>
@@ -11259,7 +13039,11 @@
       <c r="E593" t="n">
         <v>175</v>
       </c>
-      <c r="F593" t="inlineStr"/>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -11267,7 +13051,11 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B594" t="inlineStr"/>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C594" t="n">
         <v>2026</v>
       </c>
@@ -11277,7 +13065,11 @@
       <c r="E594" t="n">
         <v>130</v>
       </c>
-      <c r="F594" t="inlineStr"/>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -11301,7 +13093,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -11899,11 +13691,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -12501,11 +14293,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -13103,11 +14895,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -13117,7 +14909,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B695" t="inlineStr"/>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C695" t="n">
         <v>2024</v>
       </c>
@@ -13127,7 +14923,11 @@
       <c r="E695" t="n">
         <v>0</v>
       </c>
-      <c r="F695" t="inlineStr"/>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -13135,7 +14935,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr"/>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C696" t="n">
         <v>2024</v>
       </c>
@@ -13145,7 +14949,11 @@
       <c r="E696" t="n">
         <v>0</v>
       </c>
-      <c r="F696" t="inlineStr"/>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -13153,7 +14961,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B697" t="inlineStr"/>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C697" t="n">
         <v>2024</v>
       </c>
@@ -13163,7 +14975,11 @@
       <c r="E697" t="n">
         <v>0</v>
       </c>
-      <c r="F697" t="inlineStr"/>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -13171,7 +14987,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr"/>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C698" t="n">
         <v>2024</v>
       </c>
@@ -13181,7 +15001,11 @@
       <c r="E698" t="n">
         <v>0</v>
       </c>
-      <c r="F698" t="inlineStr"/>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -13189,7 +15013,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr"/>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C699" t="n">
         <v>2024</v>
       </c>
@@ -13199,7 +15027,11 @@
       <c r="E699" t="n">
         <v>0</v>
       </c>
-      <c r="F699" t="inlineStr"/>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -13207,7 +15039,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr"/>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C700" t="n">
         <v>2024</v>
       </c>
@@ -13217,7 +15053,11 @@
       <c r="E700" t="n">
         <v>0</v>
       </c>
-      <c r="F700" t="inlineStr"/>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -13225,7 +15065,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr"/>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C701" t="n">
         <v>2024</v>
       </c>
@@ -13235,7 +15079,11 @@
       <c r="E701" t="n">
         <v>0</v>
       </c>
-      <c r="F701" t="inlineStr"/>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -13243,7 +15091,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr"/>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C702" t="n">
         <v>2024</v>
       </c>
@@ -13253,7 +15105,11 @@
       <c r="E702" t="n">
         <v>0</v>
       </c>
-      <c r="F702" t="inlineStr"/>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -13261,7 +15117,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C703" t="n">
         <v>2024</v>
       </c>
@@ -13271,7 +15131,11 @@
       <c r="E703" t="n">
         <v>0</v>
       </c>
-      <c r="F703" t="inlineStr"/>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -13279,7 +15143,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr"/>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C704" t="n">
         <v>2024</v>
       </c>
@@ -13289,7 +15157,11 @@
       <c r="E704" t="n">
         <v>0</v>
       </c>
-      <c r="F704" t="inlineStr"/>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -13297,7 +15169,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr"/>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C705" t="n">
         <v>2024</v>
       </c>
@@ -13307,7 +15183,11 @@
       <c r="E705" t="n">
         <v>0</v>
       </c>
-      <c r="F705" t="inlineStr"/>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -13315,7 +15195,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr"/>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C706" t="n">
         <v>2024</v>
       </c>
@@ -13325,7 +15209,11 @@
       <c r="E706" t="n">
         <v>0</v>
       </c>
-      <c r="F706" t="inlineStr"/>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -13333,7 +15221,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr"/>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C707" t="n">
         <v>2025</v>
       </c>
@@ -13343,7 +15235,11 @@
       <c r="E707" t="n">
         <v>0</v>
       </c>
-      <c r="F707" t="inlineStr"/>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -13351,7 +15247,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B708" t="inlineStr"/>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C708" t="n">
         <v>2025</v>
       </c>
@@ -13361,7 +15261,11 @@
       <c r="E708" t="n">
         <v>176</v>
       </c>
-      <c r="F708" t="inlineStr"/>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -13369,7 +15273,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr"/>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C709" t="n">
         <v>2025</v>
       </c>
@@ -13379,7 +15287,11 @@
       <c r="E709" t="n">
         <v>57</v>
       </c>
-      <c r="F709" t="inlineStr"/>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -13387,7 +15299,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B710" t="inlineStr"/>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C710" t="n">
         <v>2025</v>
       </c>
@@ -13397,7 +15313,11 @@
       <c r="E710" t="n">
         <v>55</v>
       </c>
-      <c r="F710" t="inlineStr"/>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -13405,7 +15325,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr"/>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C711" t="n">
         <v>2025</v>
       </c>
@@ -13415,7 +15339,11 @@
       <c r="E711" t="n">
         <v>448</v>
       </c>
-      <c r="F711" t="inlineStr"/>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -13423,7 +15351,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B712" t="inlineStr"/>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C712" t="n">
         <v>2025</v>
       </c>
@@ -13433,7 +15365,11 @@
       <c r="E712" t="n">
         <v>393</v>
       </c>
-      <c r="F712" t="inlineStr"/>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -13441,7 +15377,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr"/>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C713" t="n">
         <v>2025</v>
       </c>
@@ -13451,7 +15391,11 @@
       <c r="E713" t="n">
         <v>472</v>
       </c>
-      <c r="F713" t="inlineStr"/>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -13459,7 +15403,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr"/>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C714" t="n">
         <v>2025</v>
       </c>
@@ -13469,7 +15417,11 @@
       <c r="E714" t="n">
         <v>221</v>
       </c>
-      <c r="F714" t="inlineStr"/>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -13477,7 +15429,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B715" t="inlineStr"/>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C715" t="n">
         <v>2025</v>
       </c>
@@ -13487,7 +15443,11 @@
       <c r="E715" t="n">
         <v>299</v>
       </c>
-      <c r="F715" t="inlineStr"/>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -13495,7 +15455,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B716" t="inlineStr"/>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C716" t="n">
         <v>2025</v>
       </c>
@@ -13505,7 +15469,11 @@
       <c r="E716" t="n">
         <v>271</v>
       </c>
-      <c r="F716" t="inlineStr"/>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -13513,7 +15481,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B717" t="inlineStr"/>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C717" t="n">
         <v>2025</v>
       </c>
@@ -13523,7 +15495,11 @@
       <c r="E717" t="n">
         <v>192</v>
       </c>
-      <c r="F717" t="inlineStr"/>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -13531,7 +15507,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B718" t="inlineStr"/>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C718" t="n">
         <v>2025</v>
       </c>
@@ -13541,7 +15521,11 @@
       <c r="E718" t="n">
         <v>197</v>
       </c>
-      <c r="F718" t="inlineStr"/>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -13549,7 +15533,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B719" t="inlineStr"/>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C719" t="n">
         <v>2026</v>
       </c>
@@ -13559,7 +15547,11 @@
       <c r="E719" t="n">
         <v>278</v>
       </c>
-      <c r="F719" t="inlineStr"/>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -13567,7 +15559,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B720" t="inlineStr"/>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C720" t="n">
         <v>2026</v>
       </c>
@@ -13577,7 +15573,11 @@
       <c r="E720" t="n">
         <v>177</v>
       </c>
-      <c r="F720" t="inlineStr"/>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -13585,7 +15585,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B721" t="inlineStr"/>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C721" t="n">
         <v>2026</v>
       </c>
@@ -13595,7 +15599,11 @@
       <c r="E721" t="n">
         <v>175</v>
       </c>
-      <c r="F721" t="inlineStr"/>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -13603,7 +15611,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr"/>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C722" t="n">
         <v>2026</v>
       </c>
@@ -13613,7 +15625,11 @@
       <c r="E722" t="n">
         <v>190</v>
       </c>
-      <c r="F722" t="inlineStr"/>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -13621,7 +15637,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B723" t="inlineStr"/>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C723" t="n">
         <v>2026</v>
       </c>
@@ -13631,7 +15651,11 @@
       <c r="E723" t="n">
         <v>152</v>
       </c>
-      <c r="F723" t="inlineStr"/>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -13639,7 +15663,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B724" t="inlineStr"/>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C724" t="n">
         <v>2026</v>
       </c>
@@ -13649,7 +15677,11 @@
       <c r="E724" t="n">
         <v>186</v>
       </c>
-      <c r="F724" t="inlineStr"/>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -13657,7 +15689,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B725" t="inlineStr"/>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C725" t="n">
         <v>2026</v>
       </c>
@@ -13667,7 +15703,11 @@
       <c r="E725" t="n">
         <v>211</v>
       </c>
-      <c r="F725" t="inlineStr"/>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -13675,7 +15715,11 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B726" t="inlineStr"/>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C726" t="n">
         <v>2026</v>
       </c>
@@ -13685,7 +15729,11 @@
       <c r="E726" t="n">
         <v>175</v>
       </c>
-      <c r="F726" t="inlineStr"/>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -13709,7 +15757,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -14307,11 +16355,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -14909,11 +16957,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-28 14:52</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
     </row>
@@ -15185,64 +17233,64 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="AH2" t="n">
-        <v>823</v>
+        <v>865</v>
       </c>
     </row>
     <row r="3">
@@ -15252,103 +17300,103 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>935</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1149</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>993</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1073</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1183</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1926</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1315</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1286</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1165</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1355</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1106</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1242</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1243</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1337</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1211</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1105</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1445</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1146</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="4">
@@ -15358,103 +17406,103 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AH4" t="n">
-        <v>688</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +17608,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>811</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +17714,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>3322</v>
+        <v>3408</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -2883,11 +2883,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
         <v>2024</v>
       </c>
@@ -2897,11 +2893,7 @@
       <c r="E134" t="n">
         <v>258</v>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2909,11 +2901,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
         <v>2024</v>
       </c>
@@ -2923,11 +2911,7 @@
       <c r="E135" t="n">
         <v>131</v>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2935,11 +2919,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
         <v>2024</v>
       </c>
@@ -2949,11 +2929,7 @@
       <c r="E136" t="n">
         <v>94</v>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2961,11 +2937,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>2024</v>
       </c>
@@ -2975,11 +2947,7 @@
       <c r="E137" t="n">
         <v>57</v>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2987,11 +2955,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>2024</v>
       </c>
@@ -3001,11 +2965,7 @@
       <c r="E138" t="n">
         <v>83</v>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3013,11 +2973,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>2024</v>
       </c>
@@ -3027,11 +2983,7 @@
       <c r="E139" t="n">
         <v>86</v>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3039,11 +2991,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>2024</v>
       </c>
@@ -3053,11 +3001,7 @@
       <c r="E140" t="n">
         <v>68</v>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3065,11 +3009,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>2024</v>
       </c>
@@ -3079,11 +3019,7 @@
       <c r="E141" t="n">
         <v>115</v>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3091,11 +3027,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>2024</v>
       </c>
@@ -3105,11 +3037,7 @@
       <c r="E142" t="n">
         <v>102</v>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3117,11 +3045,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
         <v>2024</v>
       </c>
@@ -3131,11 +3055,7 @@
       <c r="E143" t="n">
         <v>100</v>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3143,11 +3063,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>2024</v>
       </c>
@@ -3157,11 +3073,7 @@
       <c r="E144" t="n">
         <v>62</v>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3169,11 +3081,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>2024</v>
       </c>
@@ -3183,11 +3091,7 @@
       <c r="E145" t="n">
         <v>129</v>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3195,11 +3099,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>2025</v>
       </c>
@@ -3209,11 +3109,7 @@
       <c r="E146" t="n">
         <v>232</v>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3221,11 +3117,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
         <v>2025</v>
       </c>
@@ -3235,11 +3127,7 @@
       <c r="E147" t="n">
         <v>159</v>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3247,11 +3135,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>2025</v>
       </c>
@@ -3261,11 +3145,7 @@
       <c r="E148" t="n">
         <v>138</v>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3273,11 +3153,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>2025</v>
       </c>
@@ -3287,11 +3163,7 @@
       <c r="E149" t="n">
         <v>121</v>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3299,11 +3171,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>2025</v>
       </c>
@@ -3313,11 +3181,7 @@
       <c r="E150" t="n">
         <v>99</v>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3325,11 +3189,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>2025</v>
       </c>
@@ -3339,11 +3199,7 @@
       <c r="E151" t="n">
         <v>93</v>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3351,11 +3207,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>2025</v>
       </c>
@@ -3365,11 +3217,7 @@
       <c r="E152" t="n">
         <v>124</v>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3377,11 +3225,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
         <v>2025</v>
       </c>
@@ -3391,11 +3235,7 @@
       <c r="E153" t="n">
         <v>142</v>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3403,11 +3243,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
         <v>2025</v>
       </c>
@@ -3417,11 +3253,7 @@
       <c r="E154" t="n">
         <v>138</v>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3429,11 +3261,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
         <v>2025</v>
       </c>
@@ -3443,11 +3271,7 @@
       <c r="E155" t="n">
         <v>125</v>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3455,11 +3279,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
         <v>2025</v>
       </c>
@@ -3469,11 +3289,7 @@
       <c r="E156" t="n">
         <v>109</v>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3481,11 +3297,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
         <v>2025</v>
       </c>
@@ -3495,11 +3307,7 @@
       <c r="E157" t="n">
         <v>78</v>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3507,11 +3315,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
         <v>2026</v>
       </c>
@@ -3521,11 +3325,7 @@
       <c r="E158" t="n">
         <v>180</v>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3533,11 +3333,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
         <v>2026</v>
       </c>
@@ -3547,11 +3343,7 @@
       <c r="E159" t="n">
         <v>103</v>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3559,11 +3351,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
         <v>2026</v>
       </c>
@@ -3573,11 +3361,7 @@
       <c r="E160" t="n">
         <v>83</v>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3585,11 +3369,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
         <v>2026</v>
       </c>
@@ -3599,11 +3379,7 @@
       <c r="E161" t="n">
         <v>83</v>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3611,11 +3387,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
         <v>2026</v>
       </c>
@@ -3625,11 +3397,7 @@
       <c r="E162" t="n">
         <v>86</v>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3637,11 +3405,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
         <v>2026</v>
       </c>
@@ -3651,11 +3415,7 @@
       <c r="E163" t="n">
         <v>74</v>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3663,11 +3423,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
         <v>2026</v>
       </c>
@@ -3677,11 +3433,7 @@
       <c r="E164" t="n">
         <v>104</v>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3689,11 +3441,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
         <v>2026</v>
       </c>
@@ -3703,11 +3451,7 @@
       <c r="E165" t="n">
         <v>83</v>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3727,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -4329,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -4931,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -4945,11 +4689,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
         <v>2024</v>
       </c>
@@ -4959,11 +4699,7 @@
       <c r="E233" t="n">
         <v>203</v>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4971,11 +4707,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
         <v>2024</v>
       </c>
@@ -4985,11 +4717,7 @@
       <c r="E234" t="n">
         <v>147</v>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4997,11 +4725,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
         <v>2024</v>
       </c>
@@ -5011,11 +4735,7 @@
       <c r="E235" t="n">
         <v>122</v>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5023,11 +4743,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
         <v>2024</v>
       </c>
@@ -5037,11 +4753,7 @@
       <c r="E236" t="n">
         <v>129</v>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5049,11 +4761,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
         <v>2024</v>
       </c>
@@ -5063,11 +4771,7 @@
       <c r="E237" t="n">
         <v>116</v>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5075,11 +4779,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
         <v>2024</v>
       </c>
@@ -5089,11 +4789,7 @@
       <c r="E238" t="n">
         <v>110</v>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5101,11 +4797,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
         <v>2024</v>
       </c>
@@ -5115,11 +4807,7 @@
       <c r="E239" t="n">
         <v>138</v>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5127,11 +4815,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
         <v>2024</v>
       </c>
@@ -5141,11 +4825,7 @@
       <c r="E240" t="n">
         <v>117</v>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5153,11 +4833,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
         <v>2024</v>
       </c>
@@ -5167,11 +4843,7 @@
       <c r="E241" t="n">
         <v>122</v>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5179,11 +4851,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
         <v>2024</v>
       </c>
@@ -5193,11 +4861,7 @@
       <c r="E242" t="n">
         <v>102</v>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5205,11 +4869,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="n">
         <v>2024</v>
       </c>
@@ -5219,11 +4879,7 @@
       <c r="E243" t="n">
         <v>73</v>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5231,11 +4887,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
         <v>2024</v>
       </c>
@@ -5245,11 +4897,7 @@
       <c r="E244" t="n">
         <v>141</v>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5257,11 +4905,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
         <v>2025</v>
       </c>
@@ -5271,11 +4915,7 @@
       <c r="E245" t="n">
         <v>256</v>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5283,11 +4923,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
         <v>2025</v>
       </c>
@@ -5297,11 +4933,7 @@
       <c r="E246" t="n">
         <v>154</v>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5309,11 +4941,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
         <v>2025</v>
       </c>
@@ -5323,11 +4951,7 @@
       <c r="E247" t="n">
         <v>152</v>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5335,11 +4959,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
         <v>2025</v>
       </c>
@@ -5349,11 +4969,7 @@
       <c r="E248" t="n">
         <v>101</v>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5361,11 +4977,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
         <v>2025</v>
       </c>
@@ -5375,11 +4987,7 @@
       <c r="E249" t="n">
         <v>143</v>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5387,11 +4995,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
         <v>2025</v>
       </c>
@@ -5401,11 +5005,7 @@
       <c r="E250" t="n">
         <v>121</v>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5413,11 +5013,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="n">
         <v>2025</v>
       </c>
@@ -5427,11 +5023,7 @@
       <c r="E251" t="n">
         <v>119</v>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5439,11 +5031,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
         <v>2025</v>
       </c>
@@ -5453,11 +5041,7 @@
       <c r="E252" t="n">
         <v>129</v>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5465,11 +5049,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="n">
         <v>2025</v>
       </c>
@@ -5479,11 +5059,7 @@
       <c r="E253" t="n">
         <v>119</v>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5491,11 +5067,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="n">
         <v>2025</v>
       </c>
@@ -5505,11 +5077,7 @@
       <c r="E254" t="n">
         <v>115</v>
       </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5517,11 +5085,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
         <v>2025</v>
       </c>
@@ -5531,11 +5095,7 @@
       <c r="E255" t="n">
         <v>94</v>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5543,11 +5103,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
         <v>2025</v>
       </c>
@@ -5557,11 +5113,7 @@
       <c r="E256" t="n">
         <v>92</v>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5569,11 +5121,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B257" t="inlineStr"/>
       <c r="C257" t="n">
         <v>2026</v>
       </c>
@@ -5583,11 +5131,7 @@
       <c r="E257" t="n">
         <v>165</v>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5595,11 +5139,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B258" t="inlineStr"/>
       <c r="C258" t="n">
         <v>2026</v>
       </c>
@@ -5609,11 +5149,7 @@
       <c r="E258" t="n">
         <v>86</v>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5621,11 +5157,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
         <v>2026</v>
       </c>
@@ -5635,11 +5167,7 @@
       <c r="E259" t="n">
         <v>108</v>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5647,11 +5175,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
         <v>2026</v>
       </c>
@@ -5661,11 +5185,7 @@
       <c r="E260" t="n">
         <v>115</v>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5673,11 +5193,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
         <v>2026</v>
       </c>
@@ -5687,11 +5203,7 @@
       <c r="E261" t="n">
         <v>82</v>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5699,11 +5211,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
         <v>2026</v>
       </c>
@@ -5713,11 +5221,7 @@
       <c r="E262" t="n">
         <v>84</v>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5725,11 +5229,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
         <v>2026</v>
       </c>
@@ -5739,11 +5239,7 @@
       <c r="E263" t="n">
         <v>108</v>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5751,11 +5247,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
         <v>2026</v>
       </c>
@@ -5765,11 +5257,7 @@
       <c r="E264" t="n">
         <v>103</v>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5789,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -6391,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -6405,11 +5893,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B299" t="inlineStr"/>
       <c r="C299" t="n">
         <v>2024</v>
       </c>
@@ -6419,11 +5903,7 @@
       <c r="E299" t="n">
         <v>354</v>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6431,11 +5911,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
         <v>2024</v>
       </c>
@@ -6445,11 +5921,7 @@
       <c r="E300" t="n">
         <v>154</v>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6457,11 +5929,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
         <v>2024</v>
       </c>
@@ -6471,11 +5939,7 @@
       <c r="E301" t="n">
         <v>158</v>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6483,11 +5947,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
         <v>2024</v>
       </c>
@@ -6497,11 +5957,7 @@
       <c r="E302" t="n">
         <v>356</v>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6509,11 +5965,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>2024</v>
       </c>
@@ -6523,11 +5975,7 @@
       <c r="E303" t="n">
         <v>553</v>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6535,11 +5983,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="n">
         <v>2024</v>
       </c>
@@ -6549,11 +5993,7 @@
       <c r="E304" t="n">
         <v>399</v>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6561,11 +6001,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B305" t="inlineStr"/>
       <c r="C305" t="n">
         <v>2024</v>
       </c>
@@ -6575,11 +6011,7 @@
       <c r="E305" t="n">
         <v>132</v>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6587,11 +6019,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B306" t="inlineStr"/>
       <c r="C306" t="n">
         <v>2024</v>
       </c>
@@ -6601,11 +6029,7 @@
       <c r="E306" t="n">
         <v>349</v>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6613,11 +6037,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
         <v>2024</v>
       </c>
@@ -6627,11 +6047,7 @@
       <c r="E307" t="n">
         <v>353</v>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6639,11 +6055,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
         <v>2024</v>
       </c>
@@ -6653,11 +6065,7 @@
       <c r="E308" t="n">
         <v>288</v>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6665,11 +6073,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="n">
         <v>2024</v>
       </c>
@@ -6679,11 +6083,7 @@
       <c r="E309" t="n">
         <v>235</v>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6691,11 +6091,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
         <v>2024</v>
       </c>
@@ -6705,11 +6101,7 @@
       <c r="E310" t="n">
         <v>390</v>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6717,11 +6109,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B311" t="inlineStr"/>
       <c r="C311" t="n">
         <v>2025</v>
       </c>
@@ -6731,11 +6119,7 @@
       <c r="E311" t="n">
         <v>565</v>
       </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6743,11 +6127,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
         <v>2025</v>
       </c>
@@ -6757,11 +6137,7 @@
       <c r="E312" t="n">
         <v>425</v>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6769,11 +6145,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
         <v>2025</v>
       </c>
@@ -6783,11 +6155,7 @@
       <c r="E313" t="n">
         <v>396</v>
       </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6795,11 +6163,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
         <v>2025</v>
       </c>
@@ -6809,11 +6173,7 @@
       <c r="E314" t="n">
         <v>327</v>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6821,11 +6181,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B315" t="inlineStr"/>
       <c r="C315" t="n">
         <v>2025</v>
       </c>
@@ -6835,11 +6191,7 @@
       <c r="E315" t="n">
         <v>367</v>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6847,11 +6199,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
         <v>2025</v>
       </c>
@@ -6861,11 +6209,7 @@
       <c r="E316" t="n">
         <v>281</v>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6873,11 +6217,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
         <v>2025</v>
       </c>
@@ -6887,11 +6227,7 @@
       <c r="E317" t="n">
         <v>321</v>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6899,11 +6235,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
         <v>2025</v>
       </c>
@@ -6913,11 +6245,7 @@
       <c r="E318" t="n">
         <v>301</v>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6925,11 +6253,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B319" t="inlineStr"/>
       <c r="C319" t="n">
         <v>2025</v>
       </c>
@@ -6939,11 +6263,7 @@
       <c r="E319" t="n">
         <v>420</v>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6951,11 +6271,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
         <v>2025</v>
       </c>
@@ -6965,11 +6281,7 @@
       <c r="E320" t="n">
         <v>355</v>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6977,11 +6289,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>2025</v>
       </c>
@@ -6991,11 +6299,7 @@
       <c r="E321" t="n">
         <v>311</v>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7003,11 +6307,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B322" t="inlineStr"/>
       <c r="C322" t="n">
         <v>2025</v>
       </c>
@@ -7017,11 +6317,7 @@
       <c r="E322" t="n">
         <v>167</v>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7029,11 +6325,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B323" t="inlineStr"/>
       <c r="C323" t="n">
         <v>2026</v>
       </c>
@@ -7043,11 +6335,7 @@
       <c r="E323" t="n">
         <v>346</v>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7055,11 +6343,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
         <v>2026</v>
       </c>
@@ -7069,11 +6353,7 @@
       <c r="E324" t="n">
         <v>215</v>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7081,11 +6361,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
         <v>2026</v>
       </c>
@@ -7095,11 +6371,7 @@
       <c r="E325" t="n">
         <v>236</v>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7107,11 +6379,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
         <v>2026</v>
       </c>
@@ -7121,11 +6389,7 @@
       <c r="E326" t="n">
         <v>222</v>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7133,11 +6397,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B327" t="inlineStr"/>
       <c r="C327" t="n">
         <v>2026</v>
       </c>
@@ -7147,11 +6407,7 @@
       <c r="E327" t="n">
         <v>215</v>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7159,11 +6415,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B328" t="inlineStr"/>
       <c r="C328" t="n">
         <v>2026</v>
       </c>
@@ -7173,11 +6425,7 @@
       <c r="E328" t="n">
         <v>212</v>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7185,11 +6433,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
         <v>2026</v>
       </c>
@@ -7199,11 +6443,7 @@
       <c r="E329" t="n">
         <v>247</v>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7211,11 +6451,7 @@
           <t>Joquei</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B330" t="inlineStr"/>
       <c r="C330" t="n">
         <v>2026</v>
       </c>
@@ -7225,11 +6461,7 @@
       <c r="E330" t="n">
         <v>250</v>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7249,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -7263,11 +6495,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B332" t="inlineStr"/>
       <c r="C332" t="n">
         <v>2024</v>
       </c>
@@ -7277,11 +6505,7 @@
       <c r="E332" t="n">
         <v>111</v>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7289,11 +6513,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
         <v>2024</v>
       </c>
@@ -7303,11 +6523,7 @@
       <c r="E333" t="n">
         <v>217</v>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7315,11 +6531,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
         <v>2024</v>
       </c>
@@ -7329,11 +6541,7 @@
       <c r="E334" t="n">
         <v>173</v>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7341,11 +6549,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B335" t="inlineStr"/>
       <c r="C335" t="n">
         <v>2024</v>
       </c>
@@ -7355,11 +6559,7 @@
       <c r="E335" t="n">
         <v>157</v>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7367,11 +6567,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
         <v>2024</v>
       </c>
@@ -7381,11 +6577,7 @@
       <c r="E336" t="n">
         <v>178</v>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7393,11 +6585,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
         <v>2024</v>
       </c>
@@ -7407,11 +6595,7 @@
       <c r="E337" t="n">
         <v>181</v>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7419,11 +6603,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B338" t="inlineStr"/>
       <c r="C338" t="n">
         <v>2024</v>
       </c>
@@ -7433,11 +6613,7 @@
       <c r="E338" t="n">
         <v>169</v>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7445,11 +6621,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
         <v>2024</v>
       </c>
@@ -7459,11 +6631,7 @@
       <c r="E339" t="n">
         <v>183</v>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7471,11 +6639,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
         <v>2024</v>
       </c>
@@ -7485,11 +6649,7 @@
       <c r="E340" t="n">
         <v>212</v>
       </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7497,11 +6657,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
         <v>2024</v>
       </c>
@@ -7511,11 +6667,7 @@
       <c r="E341" t="n">
         <v>177</v>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7523,11 +6675,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
         <v>2024</v>
       </c>
@@ -7537,11 +6685,7 @@
       <c r="E342" t="n">
         <v>141</v>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7549,11 +6693,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
         <v>2024</v>
       </c>
@@ -7563,11 +6703,7 @@
       <c r="E343" t="n">
         <v>181</v>
       </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7575,11 +6711,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
         <v>2025</v>
       </c>
@@ -7589,11 +6721,7 @@
       <c r="E344" t="n">
         <v>362</v>
       </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7601,11 +6729,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
         <v>2025</v>
       </c>
@@ -7615,11 +6739,7 @@
       <c r="E345" t="n">
         <v>233</v>
       </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7627,11 +6747,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
         <v>2025</v>
       </c>
@@ -7641,11 +6757,7 @@
       <c r="E346" t="n">
         <v>290</v>
       </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7653,11 +6765,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="n">
         <v>2025</v>
       </c>
@@ -7667,11 +6775,7 @@
       <c r="E347" t="n">
         <v>339</v>
       </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7679,11 +6783,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
         <v>2025</v>
       </c>
@@ -7693,11 +6793,7 @@
       <c r="E348" t="n">
         <v>337</v>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7705,11 +6801,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="n">
         <v>2025</v>
       </c>
@@ -7719,11 +6811,7 @@
       <c r="E349" t="n">
         <v>304</v>
       </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7731,11 +6819,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
         <v>2025</v>
       </c>
@@ -7745,11 +6829,7 @@
       <c r="E350" t="n">
         <v>309</v>
       </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7757,11 +6837,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
         <v>2025</v>
       </c>
@@ -7771,11 +6847,7 @@
       <c r="E351" t="n">
         <v>331</v>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7783,11 +6855,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
         <v>2025</v>
       </c>
@@ -7797,11 +6865,7 @@
       <c r="E352" t="n">
         <v>328</v>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -7809,11 +6873,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>2025</v>
       </c>
@@ -7823,11 +6883,7 @@
       <c r="E353" t="n">
         <v>326</v>
       </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -7835,11 +6891,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>2025</v>
       </c>
@@ -7849,11 +6901,7 @@
       <c r="E354" t="n">
         <v>298</v>
       </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -7861,11 +6909,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
         <v>2025</v>
       </c>
@@ -7875,11 +6919,7 @@
       <c r="E355" t="n">
         <v>227</v>
       </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -7887,11 +6927,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
         <v>2026</v>
       </c>
@@ -7901,11 +6937,7 @@
       <c r="E356" t="n">
         <v>363</v>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7913,11 +6945,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
         <v>2026</v>
       </c>
@@ -7927,11 +6955,7 @@
       <c r="E357" t="n">
         <v>252</v>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -7939,11 +6963,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
         <v>2026</v>
       </c>
@@ -7953,11 +6973,7 @@
       <c r="E358" t="n">
         <v>289</v>
       </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -7965,11 +6981,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
         <v>2026</v>
       </c>
@@ -7979,11 +6991,7 @@
       <c r="E359" t="n">
         <v>272</v>
       </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -7991,11 +6999,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
         <v>2026</v>
       </c>
@@ -8005,11 +7009,7 @@
       <c r="E360" t="n">
         <v>255</v>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8017,11 +7017,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B361" t="inlineStr"/>
       <c r="C361" t="n">
         <v>2026</v>
       </c>
@@ -8031,11 +7027,7 @@
       <c r="E361" t="n">
         <v>198</v>
       </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8043,11 +7035,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B362" t="inlineStr"/>
       <c r="C362" t="n">
         <v>2026</v>
       </c>
@@ -8057,11 +7045,7 @@
       <c r="E362" t="n">
         <v>278</v>
       </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8069,11 +7053,7 @@
           <t>Kennedy</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
         <v>2026</v>
       </c>
@@ -8083,11 +7063,7 @@
       <c r="E363" t="n">
         <v>278</v>
       </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8107,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -8709,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -8723,11 +7699,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B398" t="inlineStr"/>
       <c r="C398" t="n">
         <v>2024</v>
       </c>
@@ -8737,11 +7709,7 @@
       <c r="E398" t="n">
         <v>199</v>
       </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -8749,11 +7717,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B399" t="inlineStr"/>
       <c r="C399" t="n">
         <v>2024</v>
       </c>
@@ -8763,11 +7727,7 @@
       <c r="E399" t="n">
         <v>136</v>
       </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -8775,11 +7735,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B400" t="inlineStr"/>
       <c r="C400" t="n">
         <v>2024</v>
       </c>
@@ -8789,11 +7745,7 @@
       <c r="E400" t="n">
         <v>148</v>
       </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8801,11 +7753,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B401" t="inlineStr"/>
       <c r="C401" t="n">
         <v>2024</v>
       </c>
@@ -8815,11 +7763,7 @@
       <c r="E401" t="n">
         <v>108</v>
       </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -8827,11 +7771,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B402" t="inlineStr"/>
       <c r="C402" t="n">
         <v>2024</v>
       </c>
@@ -8841,11 +7781,7 @@
       <c r="E402" t="n">
         <v>135</v>
       </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -8853,11 +7789,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B403" t="inlineStr"/>
       <c r="C403" t="n">
         <v>2024</v>
       </c>
@@ -8867,11 +7799,7 @@
       <c r="E403" t="n">
         <v>142</v>
       </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -8879,11 +7807,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B404" t="inlineStr"/>
       <c r="C404" t="n">
         <v>2024</v>
       </c>
@@ -8893,11 +7817,7 @@
       <c r="E404" t="n">
         <v>63</v>
       </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -8905,11 +7825,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B405" t="inlineStr"/>
       <c r="C405" t="n">
         <v>2024</v>
       </c>
@@ -8919,11 +7835,7 @@
       <c r="E405" t="n">
         <v>179</v>
       </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -8931,11 +7843,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B406" t="inlineStr"/>
       <c r="C406" t="n">
         <v>2024</v>
       </c>
@@ -8945,11 +7853,7 @@
       <c r="E406" t="n">
         <v>198</v>
       </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -8957,11 +7861,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B407" t="inlineStr"/>
       <c r="C407" t="n">
         <v>2024</v>
       </c>
@@ -8971,11 +7871,7 @@
       <c r="E407" t="n">
         <v>126</v>
       </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -8983,11 +7879,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B408" t="inlineStr"/>
       <c r="C408" t="n">
         <v>2024</v>
       </c>
@@ -8997,11 +7889,7 @@
       <c r="E408" t="n">
         <v>143</v>
       </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9009,11 +7897,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B409" t="inlineStr"/>
       <c r="C409" t="n">
         <v>2024</v>
       </c>
@@ -9023,11 +7907,7 @@
       <c r="E409" t="n">
         <v>180</v>
       </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9035,11 +7915,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B410" t="inlineStr"/>
       <c r="C410" t="n">
         <v>2025</v>
       </c>
@@ -9049,11 +7925,7 @@
       <c r="E410" t="n">
         <v>301</v>
       </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9061,11 +7933,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B411" t="inlineStr"/>
       <c r="C411" t="n">
         <v>2025</v>
       </c>
@@ -9075,11 +7943,7 @@
       <c r="E411" t="n">
         <v>225</v>
       </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9087,11 +7951,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B412" t="inlineStr"/>
       <c r="C412" t="n">
         <v>2025</v>
       </c>
@@ -9101,11 +7961,7 @@
       <c r="E412" t="n">
         <v>185</v>
       </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9113,11 +7969,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B413" t="inlineStr"/>
       <c r="C413" t="n">
         <v>2025</v>
       </c>
@@ -9127,11 +7979,7 @@
       <c r="E413" t="n">
         <v>173</v>
       </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9139,11 +7987,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B414" t="inlineStr"/>
       <c r="C414" t="n">
         <v>2025</v>
       </c>
@@ -9153,11 +7997,7 @@
       <c r="E414" t="n">
         <v>235</v>
       </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9165,11 +8005,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B415" t="inlineStr"/>
       <c r="C415" t="n">
         <v>2025</v>
       </c>
@@ -9179,11 +8015,7 @@
       <c r="E415" t="n">
         <v>176</v>
       </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9191,11 +8023,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B416" t="inlineStr"/>
       <c r="C416" t="n">
         <v>2025</v>
       </c>
@@ -9205,11 +8033,7 @@
       <c r="E416" t="n">
         <v>229</v>
       </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9217,11 +8041,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B417" t="inlineStr"/>
       <c r="C417" t="n">
         <v>2025</v>
       </c>
@@ -9231,11 +8051,7 @@
       <c r="E417" t="n">
         <v>248</v>
       </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9243,11 +8059,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B418" t="inlineStr"/>
       <c r="C418" t="n">
         <v>2025</v>
       </c>
@@ -9257,11 +8069,7 @@
       <c r="E418" t="n">
         <v>214</v>
       </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9269,11 +8077,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B419" t="inlineStr"/>
       <c r="C419" t="n">
         <v>2025</v>
       </c>
@@ -9283,11 +8087,7 @@
       <c r="E419" t="n">
         <v>194</v>
       </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -9295,11 +8095,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B420" t="inlineStr"/>
       <c r="C420" t="n">
         <v>2025</v>
       </c>
@@ -9309,11 +8105,7 @@
       <c r="E420" t="n">
         <v>185</v>
       </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9321,11 +8113,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B421" t="inlineStr"/>
       <c r="C421" t="n">
         <v>2025</v>
       </c>
@@ -9335,11 +8123,7 @@
       <c r="E421" t="n">
         <v>146</v>
       </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9347,11 +8131,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B422" t="inlineStr"/>
       <c r="C422" t="n">
         <v>2026</v>
       </c>
@@ -9361,11 +8141,7 @@
       <c r="E422" t="n">
         <v>229</v>
       </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9373,11 +8149,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B423" t="inlineStr"/>
       <c r="C423" t="n">
         <v>2026</v>
       </c>
@@ -9387,11 +8159,7 @@
       <c r="E423" t="n">
         <v>126</v>
       </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9399,11 +8167,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B424" t="inlineStr"/>
       <c r="C424" t="n">
         <v>2026</v>
       </c>
@@ -9413,11 +8177,7 @@
       <c r="E424" t="n">
         <v>156</v>
       </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9425,11 +8185,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B425" t="inlineStr"/>
       <c r="C425" t="n">
         <v>2026</v>
       </c>
@@ -9439,11 +8195,7 @@
       <c r="E425" t="n">
         <v>168</v>
       </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9451,11 +8203,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B426" t="inlineStr"/>
       <c r="C426" t="n">
         <v>2026</v>
       </c>
@@ -9465,11 +8213,7 @@
       <c r="E426" t="n">
         <v>132</v>
       </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -9477,11 +8221,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B427" t="inlineStr"/>
       <c r="C427" t="n">
         <v>2026</v>
       </c>
@@ -9491,11 +8231,7 @@
       <c r="E427" t="n">
         <v>122</v>
       </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9503,11 +8239,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B428" t="inlineStr"/>
       <c r="C428" t="n">
         <v>2026</v>
       </c>
@@ -9517,11 +8249,7 @@
       <c r="E428" t="n">
         <v>241</v>
       </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -9529,11 +8257,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B429" t="inlineStr"/>
       <c r="C429" t="n">
         <v>2026</v>
       </c>
@@ -9543,11 +8267,7 @@
       <c r="E429" t="n">
         <v>262</v>
       </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9567,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -10169,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -10771,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -11373,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -11387,11 +10107,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B530" t="inlineStr"/>
       <c r="C530" t="n">
         <v>2024</v>
       </c>
@@ -11401,11 +10117,7 @@
       <c r="E530" t="n">
         <v>101</v>
       </c>
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -11413,11 +10125,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B531" t="inlineStr"/>
       <c r="C531" t="n">
         <v>2024</v>
       </c>
@@ -11427,11 +10135,7 @@
       <c r="E531" t="n">
         <v>58</v>
       </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -11439,11 +10143,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B532" t="inlineStr"/>
       <c r="C532" t="n">
         <v>2024</v>
       </c>
@@ -11453,11 +10153,7 @@
       <c r="E532" t="n">
         <v>70</v>
       </c>
-      <c r="F532" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -11465,11 +10161,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B533" t="inlineStr"/>
       <c r="C533" t="n">
         <v>2024</v>
       </c>
@@ -11479,11 +10171,7 @@
       <c r="E533" t="n">
         <v>53</v>
       </c>
-      <c r="F533" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -11491,11 +10179,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B534" t="inlineStr"/>
       <c r="C534" t="n">
         <v>2024</v>
       </c>
@@ -11505,11 +10189,7 @@
       <c r="E534" t="n">
         <v>49</v>
       </c>
-      <c r="F534" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -11517,11 +10197,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B535" t="inlineStr"/>
       <c r="C535" t="n">
         <v>2024</v>
       </c>
@@ -11531,11 +10207,7 @@
       <c r="E535" t="n">
         <v>48</v>
       </c>
-      <c r="F535" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -11543,11 +10215,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B536" t="inlineStr"/>
       <c r="C536" t="n">
         <v>2024</v>
       </c>
@@ -11557,11 +10225,7 @@
       <c r="E536" t="n">
         <v>41</v>
       </c>
-      <c r="F536" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -11569,11 +10233,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B537" t="inlineStr"/>
       <c r="C537" t="n">
         <v>2024</v>
       </c>
@@ -11583,11 +10243,7 @@
       <c r="E537" t="n">
         <v>76</v>
       </c>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -11595,11 +10251,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B538" t="inlineStr"/>
       <c r="C538" t="n">
         <v>2024</v>
       </c>
@@ -11609,11 +10261,7 @@
       <c r="E538" t="n">
         <v>49</v>
       </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -11621,11 +10269,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B539" t="inlineStr"/>
       <c r="C539" t="n">
         <v>2024</v>
       </c>
@@ -11635,11 +10279,7 @@
       <c r="E539" t="n">
         <v>83</v>
       </c>
-      <c r="F539" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -11647,11 +10287,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B540" t="inlineStr"/>
       <c r="C540" t="n">
         <v>2024</v>
       </c>
@@ -11661,11 +10297,7 @@
       <c r="E540" t="n">
         <v>54</v>
       </c>
-      <c r="F540" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -11673,11 +10305,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B541" t="inlineStr"/>
       <c r="C541" t="n">
         <v>2024</v>
       </c>
@@ -11687,11 +10315,7 @@
       <c r="E541" t="n">
         <v>117</v>
       </c>
-      <c r="F541" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -11699,11 +10323,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B542" t="inlineStr"/>
       <c r="C542" t="n">
         <v>2025</v>
       </c>
@@ -11713,11 +10333,7 @@
       <c r="E542" t="n">
         <v>171</v>
       </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -11725,11 +10341,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B543" t="inlineStr"/>
       <c r="C543" t="n">
         <v>2025</v>
       </c>
@@ -11739,11 +10351,7 @@
       <c r="E543" t="n">
         <v>85</v>
       </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -11751,11 +10359,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B544" t="inlineStr"/>
       <c r="C544" t="n">
         <v>2025</v>
       </c>
@@ -11765,11 +10369,7 @@
       <c r="E544" t="n">
         <v>108</v>
       </c>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -11777,11 +10377,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B545" t="inlineStr"/>
       <c r="C545" t="n">
         <v>2025</v>
       </c>
@@ -11791,11 +10387,7 @@
       <c r="E545" t="n">
         <v>90</v>
       </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -11803,11 +10395,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B546" t="inlineStr"/>
       <c r="C546" t="n">
         <v>2025</v>
       </c>
@@ -11817,11 +10405,7 @@
       <c r="E546" t="n">
         <v>87</v>
       </c>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -11829,11 +10413,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B547" t="inlineStr"/>
       <c r="C547" t="n">
         <v>2025</v>
       </c>
@@ -11843,11 +10423,7 @@
       <c r="E547" t="n">
         <v>71</v>
       </c>
-      <c r="F547" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -11855,11 +10431,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B548" t="inlineStr"/>
       <c r="C548" t="n">
         <v>2025</v>
       </c>
@@ -11869,11 +10441,7 @@
       <c r="E548" t="n">
         <v>107</v>
       </c>
-      <c r="F548" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -11881,11 +10449,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B549" t="inlineStr"/>
       <c r="C549" t="n">
         <v>2025</v>
       </c>
@@ -11895,11 +10459,7 @@
       <c r="E549" t="n">
         <v>85</v>
       </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -11907,11 +10467,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B550" t="inlineStr"/>
       <c r="C550" t="n">
         <v>2025</v>
       </c>
@@ -11921,11 +10477,7 @@
       <c r="E550" t="n">
         <v>89</v>
       </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -11933,11 +10485,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B551" t="inlineStr"/>
       <c r="C551" t="n">
         <v>2025</v>
       </c>
@@ -11947,11 +10495,7 @@
       <c r="E551" t="n">
         <v>75</v>
       </c>
-      <c r="F551" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -11959,11 +10503,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B552" t="inlineStr"/>
       <c r="C552" t="n">
         <v>2025</v>
       </c>
@@ -11973,11 +10513,7 @@
       <c r="E552" t="n">
         <v>58</v>
       </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -11985,11 +10521,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B553" t="inlineStr"/>
       <c r="C553" t="n">
         <v>2025</v>
       </c>
@@ -11999,11 +10531,7 @@
       <c r="E553" t="n">
         <v>64</v>
       </c>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -12011,11 +10539,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B554" t="inlineStr"/>
       <c r="C554" t="n">
         <v>2026</v>
       </c>
@@ -12025,11 +10549,7 @@
       <c r="E554" t="n">
         <v>121</v>
       </c>
-      <c r="F554" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -12037,11 +10557,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B555" t="inlineStr"/>
       <c r="C555" t="n">
         <v>2026</v>
       </c>
@@ -12051,11 +10567,7 @@
       <c r="E555" t="n">
         <v>84</v>
       </c>
-      <c r="F555" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -12063,11 +10575,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B556" t="inlineStr"/>
       <c r="C556" t="n">
         <v>2026</v>
       </c>
@@ -12077,11 +10585,7 @@
       <c r="E556" t="n">
         <v>72</v>
       </c>
-      <c r="F556" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -12089,11 +10593,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B557" t="inlineStr"/>
       <c r="C557" t="n">
         <v>2026</v>
       </c>
@@ -12103,11 +10603,7 @@
       <c r="E557" t="n">
         <v>73</v>
       </c>
-      <c r="F557" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -12115,11 +10611,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B558" t="inlineStr"/>
       <c r="C558" t="n">
         <v>2026</v>
       </c>
@@ -12129,11 +10621,7 @@
       <c r="E558" t="n">
         <v>87</v>
       </c>
-      <c r="F558" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -12141,11 +10629,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B559" t="inlineStr"/>
       <c r="C559" t="n">
         <v>2026</v>
       </c>
@@ -12155,11 +10639,7 @@
       <c r="E559" t="n">
         <v>52</v>
       </c>
-      <c r="F559" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -12167,11 +10647,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B560" t="inlineStr"/>
       <c r="C560" t="n">
         <v>2026</v>
       </c>
@@ -12181,11 +10657,7 @@
       <c r="E560" t="n">
         <v>97</v>
       </c>
-      <c r="F560" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -12193,11 +10665,7 @@
           <t>Parquelandia</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B561" t="inlineStr"/>
       <c r="C561" t="n">
         <v>2026</v>
       </c>
@@ -12207,11 +10675,7 @@
       <c r="E561" t="n">
         <v>64</v>
       </c>
-      <c r="F561" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -12231,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -12245,11 +10709,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B563" t="inlineStr"/>
       <c r="C563" t="n">
         <v>2024</v>
       </c>
@@ -12259,11 +10719,7 @@
       <c r="E563" t="n">
         <v>255</v>
       </c>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -12271,11 +10727,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B564" t="inlineStr"/>
       <c r="C564" t="n">
         <v>2024</v>
       </c>
@@ -12285,11 +10737,7 @@
       <c r="E564" t="n">
         <v>164</v>
       </c>
-      <c r="F564" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -12297,11 +10745,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B565" t="inlineStr"/>
       <c r="C565" t="n">
         <v>2024</v>
       </c>
@@ -12311,11 +10755,7 @@
       <c r="E565" t="n">
         <v>179</v>
       </c>
-      <c r="F565" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -12323,11 +10763,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B566" t="inlineStr"/>
       <c r="C566" t="n">
         <v>2024</v>
       </c>
@@ -12337,11 +10773,7 @@
       <c r="E566" t="n">
         <v>132</v>
       </c>
-      <c r="F566" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -12349,11 +10781,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B567" t="inlineStr"/>
       <c r="C567" t="n">
         <v>2024</v>
       </c>
@@ -12363,11 +10791,7 @@
       <c r="E567" t="n">
         <v>118</v>
       </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -12375,11 +10799,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B568" t="inlineStr"/>
       <c r="C568" t="n">
         <v>2024</v>
       </c>
@@ -12389,11 +10809,7 @@
       <c r="E568" t="n">
         <v>113</v>
       </c>
-      <c r="F568" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -12401,11 +10817,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B569" t="inlineStr"/>
       <c r="C569" t="n">
         <v>2024</v>
       </c>
@@ -12415,11 +10827,7 @@
       <c r="E569" t="n">
         <v>57</v>
       </c>
-      <c r="F569" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -12427,11 +10835,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B570" t="inlineStr"/>
       <c r="C570" t="n">
         <v>2024</v>
       </c>
@@ -12441,11 +10845,7 @@
       <c r="E570" t="n">
         <v>136</v>
       </c>
-      <c r="F570" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -12453,11 +10853,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B571" t="inlineStr"/>
       <c r="C571" t="n">
         <v>2024</v>
       </c>
@@ -12467,11 +10863,7 @@
       <c r="E571" t="n">
         <v>139</v>
       </c>
-      <c r="F571" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -12479,11 +10871,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B572" t="inlineStr"/>
       <c r="C572" t="n">
         <v>2024</v>
       </c>
@@ -12493,11 +10881,7 @@
       <c r="E572" t="n">
         <v>146</v>
       </c>
-      <c r="F572" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -12505,11 +10889,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B573" t="inlineStr"/>
       <c r="C573" t="n">
         <v>2024</v>
       </c>
@@ -12519,11 +10899,7 @@
       <c r="E573" t="n">
         <v>133</v>
       </c>
-      <c r="F573" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -12531,11 +10907,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B574" t="inlineStr"/>
       <c r="C574" t="n">
         <v>2024</v>
       </c>
@@ -12545,11 +10917,7 @@
       <c r="E574" t="n">
         <v>174</v>
       </c>
-      <c r="F574" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -12557,11 +10925,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B575" t="inlineStr"/>
       <c r="C575" t="n">
         <v>2025</v>
       </c>
@@ -12571,11 +10935,7 @@
       <c r="E575" t="n">
         <v>271</v>
       </c>
-      <c r="F575" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -12583,11 +10943,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B576" t="inlineStr"/>
       <c r="C576" t="n">
         <v>2025</v>
       </c>
@@ -12597,11 +10953,7 @@
       <c r="E576" t="n">
         <v>193</v>
       </c>
-      <c r="F576" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -12609,11 +10961,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B577" t="inlineStr"/>
       <c r="C577" t="n">
         <v>2025</v>
       </c>
@@ -12623,11 +10971,7 @@
       <c r="E577" t="n">
         <v>155</v>
       </c>
-      <c r="F577" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -12635,11 +10979,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B578" t="inlineStr"/>
       <c r="C578" t="n">
         <v>2025</v>
       </c>
@@ -12649,11 +10989,7 @@
       <c r="E578" t="n">
         <v>135</v>
       </c>
-      <c r="F578" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -12661,11 +10997,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B579" t="inlineStr"/>
       <c r="C579" t="n">
         <v>2025</v>
       </c>
@@ -12675,11 +11007,7 @@
       <c r="E579" t="n">
         <v>186</v>
       </c>
-      <c r="F579" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -12687,11 +11015,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B580" t="inlineStr"/>
       <c r="C580" t="n">
         <v>2025</v>
       </c>
@@ -12701,11 +11025,7 @@
       <c r="E580" t="n">
         <v>153</v>
       </c>
-      <c r="F580" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -12713,11 +11033,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B581" t="inlineStr"/>
       <c r="C581" t="n">
         <v>2025</v>
       </c>
@@ -12727,11 +11043,7 @@
       <c r="E581" t="n">
         <v>157</v>
       </c>
-      <c r="F581" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -12739,11 +11051,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B582" t="inlineStr"/>
       <c r="C582" t="n">
         <v>2025</v>
       </c>
@@ -12753,11 +11061,7 @@
       <c r="E582" t="n">
         <v>149</v>
       </c>
-      <c r="F582" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -12765,11 +11069,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B583" t="inlineStr"/>
       <c r="C583" t="n">
         <v>2025</v>
       </c>
@@ -12779,11 +11079,7 @@
       <c r="E583" t="n">
         <v>167</v>
       </c>
-      <c r="F583" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -12791,11 +11087,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B584" t="inlineStr"/>
       <c r="C584" t="n">
         <v>2025</v>
       </c>
@@ -12805,11 +11097,7 @@
       <c r="E584" t="n">
         <v>146</v>
       </c>
-      <c r="F584" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -12817,11 +11105,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B585" t="inlineStr"/>
       <c r="C585" t="n">
         <v>2025</v>
       </c>
@@ -12831,11 +11115,7 @@
       <c r="E585" t="n">
         <v>159</v>
       </c>
-      <c r="F585" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -12843,11 +11123,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B586" t="inlineStr"/>
       <c r="C586" t="n">
         <v>2025</v>
       </c>
@@ -12857,11 +11133,7 @@
       <c r="E586" t="n">
         <v>130</v>
       </c>
-      <c r="F586" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -12869,11 +11141,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B587" t="inlineStr"/>
       <c r="C587" t="n">
         <v>2026</v>
       </c>
@@ -12883,11 +11151,7 @@
       <c r="E587" t="n">
         <v>221</v>
       </c>
-      <c r="F587" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -12895,11 +11159,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B588" t="inlineStr"/>
       <c r="C588" t="n">
         <v>2026</v>
       </c>
@@ -12909,11 +11169,7 @@
       <c r="E588" t="n">
         <v>113</v>
       </c>
-      <c r="F588" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -12921,11 +11177,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B589" t="inlineStr"/>
       <c r="C589" t="n">
         <v>2026</v>
       </c>
@@ -12935,11 +11187,7 @@
       <c r="E589" t="n">
         <v>119</v>
       </c>
-      <c r="F589" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -12947,11 +11195,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B590" t="inlineStr"/>
       <c r="C590" t="n">
         <v>2026</v>
       </c>
@@ -12961,11 +11205,7 @@
       <c r="E590" t="n">
         <v>117</v>
       </c>
-      <c r="F590" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -12973,11 +11213,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B591" t="inlineStr"/>
       <c r="C591" t="n">
         <v>2026</v>
       </c>
@@ -12987,11 +11223,7 @@
       <c r="E591" t="n">
         <v>124</v>
       </c>
-      <c r="F591" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -12999,11 +11231,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B592" t="inlineStr"/>
       <c r="C592" t="n">
         <v>2026</v>
       </c>
@@ -13013,11 +11241,7 @@
       <c r="E592" t="n">
         <v>103</v>
       </c>
-      <c r="F592" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -13025,11 +11249,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B593" t="inlineStr"/>
       <c r="C593" t="n">
         <v>2026</v>
       </c>
@@ -13039,11 +11259,7 @@
       <c r="E593" t="n">
         <v>175</v>
       </c>
-      <c r="F593" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -13051,11 +11267,7 @@
           <t>Passare</t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B594" t="inlineStr"/>
       <c r="C594" t="n">
         <v>2026</v>
       </c>
@@ -13065,11 +11277,7 @@
       <c r="E594" t="n">
         <v>130</v>
       </c>
-      <c r="F594" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -13089,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -13691,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -14293,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -14895,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -14909,11 +13117,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B695" t="inlineStr"/>
       <c r="C695" t="n">
         <v>2024</v>
       </c>
@@ -14923,11 +13127,7 @@
       <c r="E695" t="n">
         <v>0</v>
       </c>
-      <c r="F695" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -14935,11 +13135,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B696" t="inlineStr"/>
       <c r="C696" t="n">
         <v>2024</v>
       </c>
@@ -14949,11 +13145,7 @@
       <c r="E696" t="n">
         <v>0</v>
       </c>
-      <c r="F696" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -14961,11 +13153,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B697" t="inlineStr"/>
       <c r="C697" t="n">
         <v>2024</v>
       </c>
@@ -14975,11 +13163,7 @@
       <c r="E697" t="n">
         <v>0</v>
       </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -14987,11 +13171,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B698" t="inlineStr"/>
       <c r="C698" t="n">
         <v>2024</v>
       </c>
@@ -15001,11 +13181,7 @@
       <c r="E698" t="n">
         <v>0</v>
       </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -15013,11 +13189,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B699" t="inlineStr"/>
       <c r="C699" t="n">
         <v>2024</v>
       </c>
@@ -15027,11 +13199,7 @@
       <c r="E699" t="n">
         <v>0</v>
       </c>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -15039,11 +13207,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B700" t="inlineStr"/>
       <c r="C700" t="n">
         <v>2024</v>
       </c>
@@ -15053,11 +13217,7 @@
       <c r="E700" t="n">
         <v>0</v>
       </c>
-      <c r="F700" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -15065,11 +13225,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B701" t="inlineStr"/>
       <c r="C701" t="n">
         <v>2024</v>
       </c>
@@ -15079,11 +13235,7 @@
       <c r="E701" t="n">
         <v>0</v>
       </c>
-      <c r="F701" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -15091,11 +13243,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B702" t="inlineStr"/>
       <c r="C702" t="n">
         <v>2024</v>
       </c>
@@ -15105,11 +13253,7 @@
       <c r="E702" t="n">
         <v>0</v>
       </c>
-      <c r="F702" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -15117,11 +13261,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B703" t="inlineStr"/>
       <c r="C703" t="n">
         <v>2024</v>
       </c>
@@ -15131,11 +13271,7 @@
       <c r="E703" t="n">
         <v>0</v>
       </c>
-      <c r="F703" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -15143,11 +13279,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B704" t="inlineStr"/>
       <c r="C704" t="n">
         <v>2024</v>
       </c>
@@ -15157,11 +13289,7 @@
       <c r="E704" t="n">
         <v>0</v>
       </c>
-      <c r="F704" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -15169,11 +13297,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B705" t="inlineStr"/>
       <c r="C705" t="n">
         <v>2024</v>
       </c>
@@ -15183,11 +13307,7 @@
       <c r="E705" t="n">
         <v>0</v>
       </c>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -15195,11 +13315,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B706" t="inlineStr"/>
       <c r="C706" t="n">
         <v>2024</v>
       </c>
@@ -15209,11 +13325,7 @@
       <c r="E706" t="n">
         <v>0</v>
       </c>
-      <c r="F706" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -15221,11 +13333,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B707" t="inlineStr"/>
       <c r="C707" t="n">
         <v>2025</v>
       </c>
@@ -15235,11 +13343,7 @@
       <c r="E707" t="n">
         <v>0</v>
       </c>
-      <c r="F707" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -15247,11 +13351,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B708" t="inlineStr"/>
       <c r="C708" t="n">
         <v>2025</v>
       </c>
@@ -15261,11 +13361,7 @@
       <c r="E708" t="n">
         <v>176</v>
       </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -15273,11 +13369,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B709" t="inlineStr"/>
       <c r="C709" t="n">
         <v>2025</v>
       </c>
@@ -15287,11 +13379,7 @@
       <c r="E709" t="n">
         <v>57</v>
       </c>
-      <c r="F709" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -15299,11 +13387,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B710" t="inlineStr"/>
       <c r="C710" t="n">
         <v>2025</v>
       </c>
@@ -15313,11 +13397,7 @@
       <c r="E710" t="n">
         <v>55</v>
       </c>
-      <c r="F710" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -15325,11 +13405,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B711" t="inlineStr"/>
       <c r="C711" t="n">
         <v>2025</v>
       </c>
@@ -15339,11 +13415,7 @@
       <c r="E711" t="n">
         <v>448</v>
       </c>
-      <c r="F711" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -15351,11 +13423,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B712" t="inlineStr"/>
       <c r="C712" t="n">
         <v>2025</v>
       </c>
@@ -15365,11 +13433,7 @@
       <c r="E712" t="n">
         <v>393</v>
       </c>
-      <c r="F712" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -15377,11 +13441,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B713" t="inlineStr"/>
       <c r="C713" t="n">
         <v>2025</v>
       </c>
@@ -15391,11 +13451,7 @@
       <c r="E713" t="n">
         <v>472</v>
       </c>
-      <c r="F713" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -15403,11 +13459,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B714" t="inlineStr"/>
       <c r="C714" t="n">
         <v>2025</v>
       </c>
@@ -15417,11 +13469,7 @@
       <c r="E714" t="n">
         <v>221</v>
       </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -15429,11 +13477,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B715" t="inlineStr"/>
       <c r="C715" t="n">
         <v>2025</v>
       </c>
@@ -15443,11 +13487,7 @@
       <c r="E715" t="n">
         <v>299</v>
       </c>
-      <c r="F715" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -15455,11 +13495,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B716" t="inlineStr"/>
       <c r="C716" t="n">
         <v>2025</v>
       </c>
@@ -15469,11 +13505,7 @@
       <c r="E716" t="n">
         <v>271</v>
       </c>
-      <c r="F716" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -15481,11 +13513,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B717" t="inlineStr"/>
       <c r="C717" t="n">
         <v>2025</v>
       </c>
@@ -15495,11 +13523,7 @@
       <c r="E717" t="n">
         <v>192</v>
       </c>
-      <c r="F717" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -15507,11 +13531,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B718" t="inlineStr"/>
       <c r="C718" t="n">
         <v>2025</v>
       </c>
@@ -15521,11 +13541,7 @@
       <c r="E718" t="n">
         <v>197</v>
       </c>
-      <c r="F718" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -15533,11 +13549,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B719" t="inlineStr"/>
       <c r="C719" t="n">
         <v>2026</v>
       </c>
@@ -15547,11 +13559,7 @@
       <c r="E719" t="n">
         <v>278</v>
       </c>
-      <c r="F719" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -15559,11 +13567,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B720" t="inlineStr"/>
       <c r="C720" t="n">
         <v>2026</v>
       </c>
@@ -15573,11 +13577,7 @@
       <c r="E720" t="n">
         <v>177</v>
       </c>
-      <c r="F720" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -15585,11 +13585,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B721" t="inlineStr"/>
       <c r="C721" t="n">
         <v>2026</v>
       </c>
@@ -15599,11 +13595,7 @@
       <c r="E721" t="n">
         <v>175</v>
       </c>
-      <c r="F721" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -15611,11 +13603,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B722" t="inlineStr"/>
       <c r="C722" t="n">
         <v>2026</v>
       </c>
@@ -15625,11 +13613,7 @@
       <c r="E722" t="n">
         <v>190</v>
       </c>
-      <c r="F722" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -15637,11 +13621,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B723" t="inlineStr"/>
       <c r="C723" t="n">
         <v>2026</v>
       </c>
@@ -15651,11 +13631,7 @@
       <c r="E723" t="n">
         <v>152</v>
       </c>
-      <c r="F723" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -15663,11 +13639,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B724" t="inlineStr"/>
       <c r="C724" t="n">
         <v>2026</v>
       </c>
@@ -15677,11 +13649,7 @@
       <c r="E724" t="n">
         <v>186</v>
       </c>
-      <c r="F724" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -15689,11 +13657,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B725" t="inlineStr"/>
       <c r="C725" t="n">
         <v>2026</v>
       </c>
@@ -15703,11 +13667,7 @@
       <c r="E725" t="n">
         <v>211</v>
       </c>
-      <c r="F725" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -15715,11 +13675,7 @@
           <t>Shopping Aldeota</t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B726" t="inlineStr"/>
       <c r="C726" t="n">
         <v>2026</v>
       </c>
@@ -15729,11 +13685,7 @@
       <c r="E726" t="n">
         <v>175</v>
       </c>
-      <c r="F726" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:15</t>
-        </is>
-      </c>
+      <c r="F726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -15753,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -16355,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -16961,7 +14913,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15</t>
+          <t>2026-09-30 13:11</t>
         </is>
       </c>
     </row>
@@ -17233,64 +15185,64 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>865</v>
+        <v>899</v>
       </c>
     </row>
     <row r="3">
@@ -17300,103 +15252,103 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1223</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1149</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>993</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1040</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1183</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1315</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1286</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1165</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1355</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1106</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1242</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1243</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1337</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1211</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1105</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>826</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1445</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>967</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>771</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1146</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1087</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1004</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="4">
@@ -17406,103 +15358,103 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>710</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5">
@@ -17608,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>829</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6">
@@ -17714,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>3408</v>
+        <v>3555</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C138" t="n">
         <v>2024</v>
       </c>
@@ -2965,7 +2969,11 @@
       <c r="E138" t="n">
         <v>258</v>
       </c>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2973,7 +2981,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C139" t="n">
         <v>2024</v>
       </c>
@@ -2983,7 +2995,11 @@
       <c r="E139" t="n">
         <v>131</v>
       </c>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2991,7 +3007,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C140" t="n">
         <v>2024</v>
       </c>
@@ -3001,7 +3021,11 @@
       <c r="E140" t="n">
         <v>94</v>
       </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3009,7 +3033,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C141" t="n">
         <v>2024</v>
       </c>
@@ -3019,7 +3047,11 @@
       <c r="E141" t="n">
         <v>57</v>
       </c>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3027,7 +3059,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C142" t="n">
         <v>2024</v>
       </c>
@@ -3037,7 +3073,11 @@
       <c r="E142" t="n">
         <v>83</v>
       </c>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3045,7 +3085,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C143" t="n">
         <v>2024</v>
       </c>
@@ -3055,7 +3099,11 @@
       <c r="E143" t="n">
         <v>86</v>
       </c>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3063,7 +3111,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C144" t="n">
         <v>2024</v>
       </c>
@@ -3073,7 +3125,11 @@
       <c r="E144" t="n">
         <v>68</v>
       </c>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3081,7 +3137,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C145" t="n">
         <v>2024</v>
       </c>
@@ -3091,7 +3151,11 @@
       <c r="E145" t="n">
         <v>115</v>
       </c>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3099,7 +3163,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C146" t="n">
         <v>2024</v>
       </c>
@@ -3109,7 +3177,11 @@
       <c r="E146" t="n">
         <v>102</v>
       </c>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3117,7 +3189,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C147" t="n">
         <v>2024</v>
       </c>
@@ -3127,7 +3203,11 @@
       <c r="E147" t="n">
         <v>100</v>
       </c>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3135,7 +3215,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C148" t="n">
         <v>2024</v>
       </c>
@@ -3145,7 +3229,11 @@
       <c r="E148" t="n">
         <v>62</v>
       </c>
-      <c r="F148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3153,7 +3241,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C149" t="n">
         <v>2024</v>
       </c>
@@ -3163,7 +3255,11 @@
       <c r="E149" t="n">
         <v>129</v>
       </c>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3171,7 +3267,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C150" t="n">
         <v>2025</v>
       </c>
@@ -3181,7 +3281,11 @@
       <c r="E150" t="n">
         <v>232</v>
       </c>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3189,7 +3293,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C151" t="n">
         <v>2025</v>
       </c>
@@ -3199,7 +3307,11 @@
       <c r="E151" t="n">
         <v>159</v>
       </c>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3207,7 +3319,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C152" t="n">
         <v>2025</v>
       </c>
@@ -3217,7 +3333,11 @@
       <c r="E152" t="n">
         <v>138</v>
       </c>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3225,7 +3345,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C153" t="n">
         <v>2025</v>
       </c>
@@ -3235,7 +3359,11 @@
       <c r="E153" t="n">
         <v>121</v>
       </c>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3243,7 +3371,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C154" t="n">
         <v>2025</v>
       </c>
@@ -3253,7 +3385,11 @@
       <c r="E154" t="n">
         <v>99</v>
       </c>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3261,7 +3397,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C155" t="n">
         <v>2025</v>
       </c>
@@ -3271,7 +3411,11 @@
       <c r="E155" t="n">
         <v>93</v>
       </c>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3279,7 +3423,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C156" t="n">
         <v>2025</v>
       </c>
@@ -3289,7 +3437,11 @@
       <c r="E156" t="n">
         <v>124</v>
       </c>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3297,7 +3449,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C157" t="n">
         <v>2025</v>
       </c>
@@ -3307,7 +3463,11 @@
       <c r="E157" t="n">
         <v>142</v>
       </c>
-      <c r="F157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3315,7 +3475,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C158" t="n">
         <v>2025</v>
       </c>
@@ -3325,7 +3489,11 @@
       <c r="E158" t="n">
         <v>138</v>
       </c>
-      <c r="F158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3333,7 +3501,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C159" t="n">
         <v>2025</v>
       </c>
@@ -3343,7 +3515,11 @@
       <c r="E159" t="n">
         <v>125</v>
       </c>
-      <c r="F159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3351,7 +3527,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C160" t="n">
         <v>2025</v>
       </c>
@@ -3361,7 +3541,11 @@
       <c r="E160" t="n">
         <v>109</v>
       </c>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3369,7 +3553,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C161" t="n">
         <v>2025</v>
       </c>
@@ -3379,7 +3567,11 @@
       <c r="E161" t="n">
         <v>78</v>
       </c>
-      <c r="F161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3387,7 +3579,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C162" t="n">
         <v>2026</v>
       </c>
@@ -3397,7 +3593,11 @@
       <c r="E162" t="n">
         <v>180</v>
       </c>
-      <c r="F162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3405,7 +3605,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C163" t="n">
         <v>2026</v>
       </c>
@@ -3415,7 +3619,11 @@
       <c r="E163" t="n">
         <v>103</v>
       </c>
-      <c r="F163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3423,7 +3631,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C164" t="n">
         <v>2026</v>
       </c>
@@ -3433,7 +3645,11 @@
       <c r="E164" t="n">
         <v>83</v>
       </c>
-      <c r="F164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3441,7 +3657,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C165" t="n">
         <v>2026</v>
       </c>
@@ -3451,7 +3671,11 @@
       <c r="E165" t="n">
         <v>83</v>
       </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3459,7 +3683,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C166" t="n">
         <v>2026</v>
       </c>
@@ -3469,7 +3697,11 @@
       <c r="E166" t="n">
         <v>86</v>
       </c>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3477,7 +3709,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C167" t="n">
         <v>2026</v>
       </c>
@@ -3487,7 +3723,11 @@
       <c r="E167" t="n">
         <v>74</v>
       </c>
-      <c r="F167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3495,7 +3735,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C168" t="n">
         <v>2026</v>
       </c>
@@ -3505,7 +3749,11 @@
       <c r="E168" t="n">
         <v>104</v>
       </c>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3513,7 +3761,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C169" t="n">
         <v>2026</v>
       </c>
@@ -3523,7 +3775,11 @@
       <c r="E169" t="n">
         <v>83</v>
       </c>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3531,7 +3787,11 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C170" t="n">
         <v>2026</v>
       </c>
@@ -3541,7 +3801,11 @@
       <c r="E170" t="n">
         <v>74</v>
       </c>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3565,7 +3829,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4445,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -4801,11 +5065,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5685,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6305,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6929,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7545,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7559,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C376" t="n">
         <v>2024</v>
       </c>
@@ -7305,7 +7573,11 @@
       <c r="E376" t="n">
         <v>315</v>
       </c>
-      <c r="F376" t="inlineStr"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -7313,7 +7585,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C377" t="n">
         <v>2024</v>
       </c>
@@ -7323,7 +7599,11 @@
       <c r="E377" t="n">
         <v>138</v>
       </c>
-      <c r="F377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -7331,7 +7611,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr"/>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C378" t="n">
         <v>2024</v>
       </c>
@@ -7341,7 +7625,11 @@
       <c r="E378" t="n">
         <v>97</v>
       </c>
-      <c r="F378" t="inlineStr"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -7349,7 +7637,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr"/>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C379" t="n">
         <v>2024</v>
       </c>
@@ -7359,7 +7651,11 @@
       <c r="E379" t="n">
         <v>73</v>
       </c>
-      <c r="F379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -7367,7 +7663,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr"/>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C380" t="n">
         <v>2024</v>
       </c>
@@ -7377,7 +7677,11 @@
       <c r="E380" t="n">
         <v>61</v>
       </c>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -7385,7 +7689,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr"/>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C381" t="n">
         <v>2024</v>
       </c>
@@ -7395,7 +7703,11 @@
       <c r="E381" t="n">
         <v>69</v>
       </c>
-      <c r="F381" t="inlineStr"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -7403,7 +7715,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr"/>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C382" t="n">
         <v>2024</v>
       </c>
@@ -7413,7 +7729,11 @@
       <c r="E382" t="n">
         <v>87</v>
       </c>
-      <c r="F382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -7421,7 +7741,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr"/>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C383" t="n">
         <v>2024</v>
       </c>
@@ -7431,7 +7755,11 @@
       <c r="E383" t="n">
         <v>63</v>
       </c>
-      <c r="F383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -7439,7 +7767,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr"/>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C384" t="n">
         <v>2024</v>
       </c>
@@ -7449,7 +7781,11 @@
       <c r="E384" t="n">
         <v>84</v>
       </c>
-      <c r="F384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -7457,7 +7793,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr"/>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C385" t="n">
         <v>2024</v>
       </c>
@@ -7467,7 +7807,11 @@
       <c r="E385" t="n">
         <v>78</v>
       </c>
-      <c r="F385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -7475,7 +7819,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C386" t="n">
         <v>2024</v>
       </c>
@@ -7485,7 +7833,11 @@
       <c r="E386" t="n">
         <v>52</v>
       </c>
-      <c r="F386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -7493,7 +7845,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr"/>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C387" t="n">
         <v>2024</v>
       </c>
@@ -7503,7 +7859,11 @@
       <c r="E387" t="n">
         <v>68</v>
       </c>
-      <c r="F387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -7511,7 +7871,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr"/>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C388" t="n">
         <v>2025</v>
       </c>
@@ -7521,7 +7885,11 @@
       <c r="E388" t="n">
         <v>120</v>
       </c>
-      <c r="F388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -7529,7 +7897,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr"/>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C389" t="n">
         <v>2025</v>
       </c>
@@ -7539,7 +7911,11 @@
       <c r="E389" t="n">
         <v>68</v>
       </c>
-      <c r="F389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -7547,7 +7923,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr"/>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C390" t="n">
         <v>2025</v>
       </c>
@@ -7557,7 +7937,11 @@
       <c r="E390" t="n">
         <v>80</v>
       </c>
-      <c r="F390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -7565,7 +7949,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr"/>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C391" t="n">
         <v>2025</v>
       </c>
@@ -7575,7 +7963,11 @@
       <c r="E391" t="n">
         <v>69</v>
       </c>
-      <c r="F391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -7583,7 +7975,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C392" t="n">
         <v>2025</v>
       </c>
@@ -7593,7 +7989,11 @@
       <c r="E392" t="n">
         <v>77</v>
       </c>
-      <c r="F392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -7601,7 +8001,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C393" t="n">
         <v>2025</v>
       </c>
@@ -7611,7 +8015,11 @@
       <c r="E393" t="n">
         <v>59</v>
       </c>
-      <c r="F393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -7619,7 +8027,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C394" t="n">
         <v>2025</v>
       </c>
@@ -7629,7 +8041,11 @@
       <c r="E394" t="n">
         <v>69</v>
       </c>
-      <c r="F394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -7637,7 +8053,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C395" t="n">
         <v>2025</v>
       </c>
@@ -7647,7 +8067,11 @@
       <c r="E395" t="n">
         <v>62</v>
       </c>
-      <c r="F395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -7655,7 +8079,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C396" t="n">
         <v>2025</v>
       </c>
@@ -7665,7 +8093,11 @@
       <c r="E396" t="n">
         <v>65</v>
       </c>
-      <c r="F396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -7673,7 +8105,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr"/>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C397" t="n">
         <v>2025</v>
       </c>
@@ -7683,7 +8119,11 @@
       <c r="E397" t="n">
         <v>81</v>
       </c>
-      <c r="F397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -7691,7 +8131,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C398" t="n">
         <v>2025</v>
       </c>
@@ -7701,7 +8145,11 @@
       <c r="E398" t="n">
         <v>65</v>
       </c>
-      <c r="F398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -7709,7 +8157,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C399" t="n">
         <v>2025</v>
       </c>
@@ -7719,7 +8171,11 @@
       <c r="E399" t="n">
         <v>58</v>
       </c>
-      <c r="F399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -7727,7 +8183,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C400" t="n">
         <v>2026</v>
       </c>
@@ -7737,7 +8197,11 @@
       <c r="E400" t="n">
         <v>85</v>
       </c>
-      <c r="F400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -7745,7 +8209,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C401" t="n">
         <v>2026</v>
       </c>
@@ -7755,7 +8223,11 @@
       <c r="E401" t="n">
         <v>39</v>
       </c>
-      <c r="F401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -7763,7 +8235,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C402" t="n">
         <v>2026</v>
       </c>
@@ -7773,7 +8249,11 @@
       <c r="E402" t="n">
         <v>37</v>
       </c>
-      <c r="F402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -7781,7 +8261,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C403" t="n">
         <v>2026</v>
       </c>
@@ -7791,7 +8275,11 @@
       <c r="E403" t="n">
         <v>32</v>
       </c>
-      <c r="F403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -7799,7 +8287,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C404" t="n">
         <v>2026</v>
       </c>
@@ -7809,7 +8301,11 @@
       <c r="E404" t="n">
         <v>64</v>
       </c>
-      <c r="F404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -7817,7 +8313,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C405" t="n">
         <v>2026</v>
       </c>
@@ -7827,7 +8327,11 @@
       <c r="E405" t="n">
         <v>35</v>
       </c>
-      <c r="F405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -7835,7 +8339,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C406" t="n">
         <v>2026</v>
       </c>
@@ -7845,7 +8353,11 @@
       <c r="E406" t="n">
         <v>59</v>
       </c>
-      <c r="F406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -7853,7 +8365,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C407" t="n">
         <v>2026</v>
       </c>
@@ -7863,7 +8379,11 @@
       <c r="E407" t="n">
         <v>64</v>
       </c>
-      <c r="F407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -7871,7 +8391,11 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C408" t="n">
         <v>2026</v>
       </c>
@@ -7881,7 +8405,11 @@
       <c r="E408" t="n">
         <v>65</v>
       </c>
-      <c r="F408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -7905,7 +8433,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -7915,7 +8443,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr"/>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C410" t="n">
         <v>2024</v>
       </c>
@@ -7925,7 +8457,11 @@
       <c r="E410" t="n">
         <v>199</v>
       </c>
-      <c r="F410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -7933,7 +8469,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C411" t="n">
         <v>2024</v>
       </c>
@@ -7943,7 +8483,11 @@
       <c r="E411" t="n">
         <v>136</v>
       </c>
-      <c r="F411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -7951,7 +8495,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C412" t="n">
         <v>2024</v>
       </c>
@@ -7961,7 +8509,11 @@
       <c r="E412" t="n">
         <v>148</v>
       </c>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -7969,7 +8521,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C413" t="n">
         <v>2024</v>
       </c>
@@ -7979,7 +8535,11 @@
       <c r="E413" t="n">
         <v>108</v>
       </c>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -7987,7 +8547,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr"/>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C414" t="n">
         <v>2024</v>
       </c>
@@ -7997,7 +8561,11 @@
       <c r="E414" t="n">
         <v>135</v>
       </c>
-      <c r="F414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -8005,7 +8573,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C415" t="n">
         <v>2024</v>
       </c>
@@ -8015,7 +8587,11 @@
       <c r="E415" t="n">
         <v>142</v>
       </c>
-      <c r="F415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -8023,7 +8599,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr"/>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C416" t="n">
         <v>2024</v>
       </c>
@@ -8033,7 +8613,11 @@
       <c r="E416" t="n">
         <v>63</v>
       </c>
-      <c r="F416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -8041,7 +8625,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C417" t="n">
         <v>2024</v>
       </c>
@@ -8051,7 +8639,11 @@
       <c r="E417" t="n">
         <v>179</v>
       </c>
-      <c r="F417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -8059,7 +8651,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr"/>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C418" t="n">
         <v>2024</v>
       </c>
@@ -8069,7 +8665,11 @@
       <c r="E418" t="n">
         <v>198</v>
       </c>
-      <c r="F418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -8077,7 +8677,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr"/>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C419" t="n">
         <v>2024</v>
       </c>
@@ -8087,7 +8691,11 @@
       <c r="E419" t="n">
         <v>126</v>
       </c>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -8095,7 +8703,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr"/>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C420" t="n">
         <v>2024</v>
       </c>
@@ -8105,7 +8717,11 @@
       <c r="E420" t="n">
         <v>143</v>
       </c>
-      <c r="F420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -8113,7 +8729,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C421" t="n">
         <v>2024</v>
       </c>
@@ -8123,7 +8743,11 @@
       <c r="E421" t="n">
         <v>180</v>
       </c>
-      <c r="F421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -8131,7 +8755,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr"/>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C422" t="n">
         <v>2025</v>
       </c>
@@ -8141,7 +8769,11 @@
       <c r="E422" t="n">
         <v>301</v>
       </c>
-      <c r="F422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -8149,7 +8781,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr"/>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C423" t="n">
         <v>2025</v>
       </c>
@@ -8159,7 +8795,11 @@
       <c r="E423" t="n">
         <v>225</v>
       </c>
-      <c r="F423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -8167,7 +8807,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr"/>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C424" t="n">
         <v>2025</v>
       </c>
@@ -8177,7 +8821,11 @@
       <c r="E424" t="n">
         <v>185</v>
       </c>
-      <c r="F424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -8185,7 +8833,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr"/>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C425" t="n">
         <v>2025</v>
       </c>
@@ -8195,7 +8847,11 @@
       <c r="E425" t="n">
         <v>173</v>
       </c>
-      <c r="F425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -8203,7 +8859,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr"/>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C426" t="n">
         <v>2025</v>
       </c>
@@ -8213,7 +8873,11 @@
       <c r="E426" t="n">
         <v>235</v>
       </c>
-      <c r="F426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -8221,7 +8885,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr"/>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C427" t="n">
         <v>2025</v>
       </c>
@@ -8231,7 +8899,11 @@
       <c r="E427" t="n">
         <v>176</v>
       </c>
-      <c r="F427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -8239,7 +8911,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr"/>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C428" t="n">
         <v>2025</v>
       </c>
@@ -8249,7 +8925,11 @@
       <c r="E428" t="n">
         <v>229</v>
       </c>
-      <c r="F428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -8257,7 +8937,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr"/>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C429" t="n">
         <v>2025</v>
       </c>
@@ -8267,7 +8951,11 @@
       <c r="E429" t="n">
         <v>248</v>
       </c>
-      <c r="F429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -8275,7 +8963,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr"/>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C430" t="n">
         <v>2025</v>
       </c>
@@ -8285,7 +8977,11 @@
       <c r="E430" t="n">
         <v>214</v>
       </c>
-      <c r="F430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -8293,7 +8989,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr"/>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C431" t="n">
         <v>2025</v>
       </c>
@@ -8303,7 +9003,11 @@
       <c r="E431" t="n">
         <v>194</v>
       </c>
-      <c r="F431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -8311,7 +9015,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr"/>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C432" t="n">
         <v>2025</v>
       </c>
@@ -8321,7 +9029,11 @@
       <c r="E432" t="n">
         <v>185</v>
       </c>
-      <c r="F432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -8329,7 +9041,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr"/>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C433" t="n">
         <v>2025</v>
       </c>
@@ -8339,7 +9055,11 @@
       <c r="E433" t="n">
         <v>146</v>
       </c>
-      <c r="F433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -8347,7 +9067,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr"/>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C434" t="n">
         <v>2026</v>
       </c>
@@ -8357,7 +9081,11 @@
       <c r="E434" t="n">
         <v>229</v>
       </c>
-      <c r="F434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -8365,7 +9093,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr"/>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C435" t="n">
         <v>2026</v>
       </c>
@@ -8375,7 +9107,11 @@
       <c r="E435" t="n">
         <v>126</v>
       </c>
-      <c r="F435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -8383,7 +9119,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr"/>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C436" t="n">
         <v>2026</v>
       </c>
@@ -8393,7 +9133,11 @@
       <c r="E436" t="n">
         <v>156</v>
       </c>
-      <c r="F436" t="inlineStr"/>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -8401,7 +9145,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr"/>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C437" t="n">
         <v>2026</v>
       </c>
@@ -8411,7 +9159,11 @@
       <c r="E437" t="n">
         <v>168</v>
       </c>
-      <c r="F437" t="inlineStr"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -8419,7 +9171,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr"/>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C438" t="n">
         <v>2026</v>
       </c>
@@ -8429,7 +9185,11 @@
       <c r="E438" t="n">
         <v>132</v>
       </c>
-      <c r="F438" t="inlineStr"/>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -8437,7 +9197,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr"/>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C439" t="n">
         <v>2026</v>
       </c>
@@ -8447,7 +9211,11 @@
       <c r="E439" t="n">
         <v>122</v>
       </c>
-      <c r="F439" t="inlineStr"/>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -8455,7 +9223,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr"/>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C440" t="n">
         <v>2026</v>
       </c>
@@ -8465,7 +9237,11 @@
       <c r="E440" t="n">
         <v>241</v>
       </c>
-      <c r="F440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -8473,7 +9249,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr"/>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C441" t="n">
         <v>2026</v>
       </c>
@@ -8483,7 +9263,11 @@
       <c r="E441" t="n">
         <v>262</v>
       </c>
-      <c r="F441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -8491,7 +9275,11 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr"/>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C442" t="n">
         <v>2026</v>
       </c>
@@ -8501,7 +9289,11 @@
       <c r="E442" t="n">
         <v>230</v>
       </c>
-      <c r="F442" t="inlineStr"/>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -8525,7 +9317,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9933,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -9761,11 +10553,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -10381,11 +11173,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11793,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -11621,11 +12413,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -12241,11 +13033,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -12861,11 +13653,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -13485,7 +14277,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14893,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -14721,11 +15513,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -15345,7 +16137,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-02 13:02</t>
+          <t>2026-10-03 11:29</t>
         </is>
       </c>
     </row>
@@ -15683,7 +16475,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -15693,106 +16485,106 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AI3" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -15802,106 +16594,106 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>573</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="AI4" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16802,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16911,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>162</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -2955,11 +2955,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>2024</v>
       </c>
@@ -2969,11 +2965,7 @@
       <c r="E138" t="n">
         <v>258</v>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2981,11 +2973,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>2024</v>
       </c>
@@ -2995,11 +2983,7 @@
       <c r="E139" t="n">
         <v>131</v>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3007,11 +2991,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>2024</v>
       </c>
@@ -3021,11 +3001,7 @@
       <c r="E140" t="n">
         <v>94</v>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3033,11 +3009,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>2024</v>
       </c>
@@ -3047,11 +3019,7 @@
       <c r="E141" t="n">
         <v>57</v>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3059,11 +3027,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>2024</v>
       </c>
@@ -3073,11 +3037,7 @@
       <c r="E142" t="n">
         <v>83</v>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3085,11 +3045,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
         <v>2024</v>
       </c>
@@ -3099,11 +3055,7 @@
       <c r="E143" t="n">
         <v>86</v>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3111,11 +3063,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>2024</v>
       </c>
@@ -3125,11 +3073,7 @@
       <c r="E144" t="n">
         <v>68</v>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3137,11 +3081,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>2024</v>
       </c>
@@ -3151,11 +3091,7 @@
       <c r="E145" t="n">
         <v>115</v>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3163,11 +3099,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>2024</v>
       </c>
@@ -3177,11 +3109,7 @@
       <c r="E146" t="n">
         <v>102</v>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3189,11 +3117,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
         <v>2024</v>
       </c>
@@ -3203,11 +3127,7 @@
       <c r="E147" t="n">
         <v>100</v>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3215,11 +3135,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>2024</v>
       </c>
@@ -3229,11 +3145,7 @@
       <c r="E148" t="n">
         <v>62</v>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3241,11 +3153,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>2024</v>
       </c>
@@ -3255,11 +3163,7 @@
       <c r="E149" t="n">
         <v>129</v>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3267,11 +3171,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>2025</v>
       </c>
@@ -3281,11 +3181,7 @@
       <c r="E150" t="n">
         <v>232</v>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3293,11 +3189,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>2025</v>
       </c>
@@ -3307,11 +3199,7 @@
       <c r="E151" t="n">
         <v>159</v>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3319,11 +3207,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>2025</v>
       </c>
@@ -3333,11 +3217,7 @@
       <c r="E152" t="n">
         <v>138</v>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3345,11 +3225,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
         <v>2025</v>
       </c>
@@ -3359,11 +3235,7 @@
       <c r="E153" t="n">
         <v>121</v>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3371,11 +3243,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
         <v>2025</v>
       </c>
@@ -3385,11 +3253,7 @@
       <c r="E154" t="n">
         <v>99</v>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3397,11 +3261,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
         <v>2025</v>
       </c>
@@ -3411,11 +3271,7 @@
       <c r="E155" t="n">
         <v>93</v>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3423,11 +3279,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
         <v>2025</v>
       </c>
@@ -3437,11 +3289,7 @@
       <c r="E156" t="n">
         <v>124</v>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3449,11 +3297,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
         <v>2025</v>
       </c>
@@ -3463,11 +3307,7 @@
       <c r="E157" t="n">
         <v>142</v>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3475,11 +3315,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
         <v>2025</v>
       </c>
@@ -3489,11 +3325,7 @@
       <c r="E158" t="n">
         <v>138</v>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3501,11 +3333,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
         <v>2025</v>
       </c>
@@ -3515,11 +3343,7 @@
       <c r="E159" t="n">
         <v>125</v>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3527,11 +3351,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
         <v>2025</v>
       </c>
@@ -3541,11 +3361,7 @@
       <c r="E160" t="n">
         <v>109</v>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3553,11 +3369,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
         <v>2025</v>
       </c>
@@ -3567,11 +3379,7 @@
       <c r="E161" t="n">
         <v>78</v>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3579,11 +3387,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
         <v>2026</v>
       </c>
@@ -3593,11 +3397,7 @@
       <c r="E162" t="n">
         <v>180</v>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3605,11 +3405,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
         <v>2026</v>
       </c>
@@ -3619,11 +3415,7 @@
       <c r="E163" t="n">
         <v>103</v>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3631,11 +3423,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
         <v>2026</v>
       </c>
@@ -3645,11 +3433,7 @@
       <c r="E164" t="n">
         <v>83</v>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3657,11 +3441,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
         <v>2026</v>
       </c>
@@ -3671,11 +3451,7 @@
       <c r="E165" t="n">
         <v>83</v>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3683,11 +3459,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
         <v>2026</v>
       </c>
@@ -3697,11 +3469,7 @@
       <c r="E166" t="n">
         <v>86</v>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3709,11 +3477,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
         <v>2026</v>
       </c>
@@ -3723,11 +3487,7 @@
       <c r="E167" t="n">
         <v>74</v>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3735,11 +3495,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
         <v>2026</v>
       </c>
@@ -3749,11 +3505,7 @@
       <c r="E168" t="n">
         <v>104</v>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3761,11 +3513,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
         <v>2026</v>
       </c>
@@ -3775,11 +3523,7 @@
       <c r="E169" t="n">
         <v>83</v>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3787,11 +3531,7 @@
           <t>Cambeba</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
         <v>2026</v>
       </c>
@@ -3801,11 +3541,7 @@
       <c r="E170" t="n">
         <v>74</v>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3825,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -4445,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4195,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C206" t="n">
         <v>2024</v>
       </c>
@@ -4469,7 +4209,11 @@
       <c r="E206" t="n">
         <v>114</v>
       </c>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4477,7 +4221,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C207" t="n">
         <v>2024</v>
       </c>
@@ -4487,7 +4235,11 @@
       <c r="E207" t="n">
         <v>81</v>
       </c>
-      <c r="F207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4495,7 +4247,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C208" t="n">
         <v>2024</v>
       </c>
@@ -4505,7 +4261,11 @@
       <c r="E208" t="n">
         <v>90</v>
       </c>
-      <c r="F208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4513,7 +4273,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C209" t="n">
         <v>2024</v>
       </c>
@@ -4523,7 +4287,11 @@
       <c r="E209" t="n">
         <v>52</v>
       </c>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4531,7 +4299,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C210" t="n">
         <v>2024</v>
       </c>
@@ -4541,7 +4313,11 @@
       <c r="E210" t="n">
         <v>70</v>
       </c>
-      <c r="F210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4549,7 +4325,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C211" t="n">
         <v>2024</v>
       </c>
@@ -4559,7 +4339,11 @@
       <c r="E211" t="n">
         <v>52</v>
       </c>
-      <c r="F211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4567,7 +4351,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C212" t="n">
         <v>2024</v>
       </c>
@@ -4577,7 +4365,11 @@
       <c r="E212" t="n">
         <v>61</v>
       </c>
-      <c r="F212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4585,7 +4377,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C213" t="n">
         <v>2024</v>
       </c>
@@ -4595,7 +4391,11 @@
       <c r="E213" t="n">
         <v>114</v>
       </c>
-      <c r="F213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4603,7 +4403,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C214" t="n">
         <v>2024</v>
       </c>
@@ -4613,7 +4417,11 @@
       <c r="E214" t="n">
         <v>112</v>
       </c>
-      <c r="F214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4621,7 +4429,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C215" t="n">
         <v>2024</v>
       </c>
@@ -4631,7 +4443,11 @@
       <c r="E215" t="n">
         <v>124</v>
       </c>
-      <c r="F215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4639,7 +4455,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C216" t="n">
         <v>2024</v>
       </c>
@@ -4649,7 +4469,11 @@
       <c r="E216" t="n">
         <v>89</v>
       </c>
-      <c r="F216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4657,7 +4481,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C217" t="n">
         <v>2024</v>
       </c>
@@ -4667,7 +4495,11 @@
       <c r="E217" t="n">
         <v>163</v>
       </c>
-      <c r="F217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4675,7 +4507,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C218" t="n">
         <v>2025</v>
       </c>
@@ -4685,7 +4521,11 @@
       <c r="E218" t="n">
         <v>211</v>
       </c>
-      <c r="F218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4693,7 +4533,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C219" t="n">
         <v>2025</v>
       </c>
@@ -4703,7 +4547,11 @@
       <c r="E219" t="n">
         <v>151</v>
       </c>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4711,7 +4559,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C220" t="n">
         <v>2025</v>
       </c>
@@ -4721,7 +4573,11 @@
       <c r="E220" t="n">
         <v>131</v>
       </c>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4729,7 +4585,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C221" t="n">
         <v>2025</v>
       </c>
@@ -4739,7 +4599,11 @@
       <c r="E221" t="n">
         <v>121</v>
       </c>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4747,7 +4611,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C222" t="n">
         <v>2025</v>
       </c>
@@ -4757,7 +4625,11 @@
       <c r="E222" t="n">
         <v>171</v>
       </c>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4765,7 +4637,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C223" t="n">
         <v>2025</v>
       </c>
@@ -4775,7 +4651,11 @@
       <c r="E223" t="n">
         <v>123</v>
       </c>
-      <c r="F223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4783,7 +4663,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C224" t="n">
         <v>2025</v>
       </c>
@@ -4793,7 +4677,11 @@
       <c r="E224" t="n">
         <v>128</v>
       </c>
-      <c r="F224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4801,7 +4689,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C225" t="n">
         <v>2025</v>
       </c>
@@ -4811,7 +4703,11 @@
       <c r="E225" t="n">
         <v>128</v>
       </c>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4819,7 +4715,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C226" t="n">
         <v>2025</v>
       </c>
@@ -4829,7 +4729,11 @@
       <c r="E226" t="n">
         <v>155</v>
       </c>
-      <c r="F226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4837,7 +4741,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C227" t="n">
         <v>2025</v>
       </c>
@@ -4847,7 +4755,11 @@
       <c r="E227" t="n">
         <v>139</v>
       </c>
-      <c r="F227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4855,7 +4767,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C228" t="n">
         <v>2025</v>
       </c>
@@ -4865,7 +4781,11 @@
       <c r="E228" t="n">
         <v>140</v>
       </c>
-      <c r="F228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4873,7 +4793,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C229" t="n">
         <v>2025</v>
       </c>
@@ -4883,7 +4807,11 @@
       <c r="E229" t="n">
         <v>132</v>
       </c>
-      <c r="F229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4891,7 +4819,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C230" t="n">
         <v>2026</v>
       </c>
@@ -4901,7 +4833,11 @@
       <c r="E230" t="n">
         <v>189</v>
       </c>
-      <c r="F230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4909,7 +4845,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C231" t="n">
         <v>2026</v>
       </c>
@@ -4919,7 +4859,11 @@
       <c r="E231" t="n">
         <v>89</v>
       </c>
-      <c r="F231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4927,7 +4871,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C232" t="n">
         <v>2026</v>
       </c>
@@ -4937,7 +4885,11 @@
       <c r="E232" t="n">
         <v>110</v>
       </c>
-      <c r="F232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4945,7 +4897,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C233" t="n">
         <v>2026</v>
       </c>
@@ -4955,7 +4911,11 @@
       <c r="E233" t="n">
         <v>122</v>
       </c>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4963,7 +4923,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C234" t="n">
         <v>2026</v>
       </c>
@@ -4973,7 +4937,11 @@
       <c r="E234" t="n">
         <v>118</v>
       </c>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4981,7 +4949,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C235" t="n">
         <v>2026</v>
       </c>
@@ -4991,7 +4963,11 @@
       <c r="E235" t="n">
         <v>132</v>
       </c>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4999,7 +4975,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C236" t="n">
         <v>2026</v>
       </c>
@@ -5009,7 +4989,11 @@
       <c r="E236" t="n">
         <v>153</v>
       </c>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5017,7 +5001,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C237" t="n">
         <v>2026</v>
       </c>
@@ -5027,7 +5015,11 @@
       <c r="E237" t="n">
         <v>139</v>
       </c>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5035,7 +5027,11 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C238" t="n">
         <v>2026</v>
       </c>
@@ -5045,7 +5041,11 @@
       <c r="E238" t="n">
         <v>136</v>
       </c>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -5685,11 +5685,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -6925,11 +6925,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -7545,11 +7545,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -7559,11 +7559,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
         <v>2024</v>
       </c>
@@ -7573,11 +7569,7 @@
       <c r="E376" t="n">
         <v>315</v>
       </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -7585,11 +7577,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B377" t="inlineStr"/>
       <c r="C377" t="n">
         <v>2024</v>
       </c>
@@ -7599,11 +7587,7 @@
       <c r="E377" t="n">
         <v>138</v>
       </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -7611,11 +7595,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
         <v>2024</v>
       </c>
@@ -7625,11 +7605,7 @@
       <c r="E378" t="n">
         <v>97</v>
       </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -7637,11 +7613,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B379" t="inlineStr"/>
       <c r="C379" t="n">
         <v>2024</v>
       </c>
@@ -7651,11 +7623,7 @@
       <c r="E379" t="n">
         <v>73</v>
       </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -7663,11 +7631,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B380" t="inlineStr"/>
       <c r="C380" t="n">
         <v>2024</v>
       </c>
@@ -7677,11 +7641,7 @@
       <c r="E380" t="n">
         <v>61</v>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -7689,11 +7649,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B381" t="inlineStr"/>
       <c r="C381" t="n">
         <v>2024</v>
       </c>
@@ -7703,11 +7659,7 @@
       <c r="E381" t="n">
         <v>69</v>
       </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -7715,11 +7667,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B382" t="inlineStr"/>
       <c r="C382" t="n">
         <v>2024</v>
       </c>
@@ -7729,11 +7677,7 @@
       <c r="E382" t="n">
         <v>87</v>
       </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -7741,11 +7685,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
         <v>2024</v>
       </c>
@@ -7755,11 +7695,7 @@
       <c r="E383" t="n">
         <v>63</v>
       </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -7767,11 +7703,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B384" t="inlineStr"/>
       <c r="C384" t="n">
         <v>2024</v>
       </c>
@@ -7781,11 +7713,7 @@
       <c r="E384" t="n">
         <v>84</v>
       </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -7793,11 +7721,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B385" t="inlineStr"/>
       <c r="C385" t="n">
         <v>2024</v>
       </c>
@@ -7807,11 +7731,7 @@
       <c r="E385" t="n">
         <v>78</v>
       </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -7819,11 +7739,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B386" t="inlineStr"/>
       <c r="C386" t="n">
         <v>2024</v>
       </c>
@@ -7833,11 +7749,7 @@
       <c r="E386" t="n">
         <v>52</v>
       </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -7845,11 +7757,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B387" t="inlineStr"/>
       <c r="C387" t="n">
         <v>2024</v>
       </c>
@@ -7859,11 +7767,7 @@
       <c r="E387" t="n">
         <v>68</v>
       </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -7871,11 +7775,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B388" t="inlineStr"/>
       <c r="C388" t="n">
         <v>2025</v>
       </c>
@@ -7885,11 +7785,7 @@
       <c r="E388" t="n">
         <v>120</v>
       </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -7897,11 +7793,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B389" t="inlineStr"/>
       <c r="C389" t="n">
         <v>2025</v>
       </c>
@@ -7911,11 +7803,7 @@
       <c r="E389" t="n">
         <v>68</v>
       </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -7923,11 +7811,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B390" t="inlineStr"/>
       <c r="C390" t="n">
         <v>2025</v>
       </c>
@@ -7937,11 +7821,7 @@
       <c r="E390" t="n">
         <v>80</v>
       </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -7949,11 +7829,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B391" t="inlineStr"/>
       <c r="C391" t="n">
         <v>2025</v>
       </c>
@@ -7963,11 +7839,7 @@
       <c r="E391" t="n">
         <v>69</v>
       </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -7975,11 +7847,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B392" t="inlineStr"/>
       <c r="C392" t="n">
         <v>2025</v>
       </c>
@@ -7989,11 +7857,7 @@
       <c r="E392" t="n">
         <v>77</v>
       </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -8001,11 +7865,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B393" t="inlineStr"/>
       <c r="C393" t="n">
         <v>2025</v>
       </c>
@@ -8015,11 +7875,7 @@
       <c r="E393" t="n">
         <v>59</v>
       </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -8027,11 +7883,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B394" t="inlineStr"/>
       <c r="C394" t="n">
         <v>2025</v>
       </c>
@@ -8041,11 +7893,7 @@
       <c r="E394" t="n">
         <v>69</v>
       </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -8053,11 +7901,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B395" t="inlineStr"/>
       <c r="C395" t="n">
         <v>2025</v>
       </c>
@@ -8067,11 +7911,7 @@
       <c r="E395" t="n">
         <v>62</v>
       </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -8079,11 +7919,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B396" t="inlineStr"/>
       <c r="C396" t="n">
         <v>2025</v>
       </c>
@@ -8093,11 +7929,7 @@
       <c r="E396" t="n">
         <v>65</v>
       </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -8105,11 +7937,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B397" t="inlineStr"/>
       <c r="C397" t="n">
         <v>2025</v>
       </c>
@@ -8119,11 +7947,7 @@
       <c r="E397" t="n">
         <v>81</v>
       </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -8131,11 +7955,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B398" t="inlineStr"/>
       <c r="C398" t="n">
         <v>2025</v>
       </c>
@@ -8145,11 +7965,7 @@
       <c r="E398" t="n">
         <v>65</v>
       </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -8157,11 +7973,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B399" t="inlineStr"/>
       <c r="C399" t="n">
         <v>2025</v>
       </c>
@@ -8171,11 +7983,7 @@
       <c r="E399" t="n">
         <v>58</v>
       </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -8183,11 +7991,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B400" t="inlineStr"/>
       <c r="C400" t="n">
         <v>2026</v>
       </c>
@@ -8197,11 +8001,7 @@
       <c r="E400" t="n">
         <v>85</v>
       </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8209,11 +8009,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B401" t="inlineStr"/>
       <c r="C401" t="n">
         <v>2026</v>
       </c>
@@ -8223,11 +8019,7 @@
       <c r="E401" t="n">
         <v>39</v>
       </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -8235,11 +8027,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B402" t="inlineStr"/>
       <c r="C402" t="n">
         <v>2026</v>
       </c>
@@ -8249,11 +8037,7 @@
       <c r="E402" t="n">
         <v>37</v>
       </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -8261,11 +8045,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B403" t="inlineStr"/>
       <c r="C403" t="n">
         <v>2026</v>
       </c>
@@ -8275,11 +8055,7 @@
       <c r="E403" t="n">
         <v>32</v>
       </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -8287,11 +8063,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B404" t="inlineStr"/>
       <c r="C404" t="n">
         <v>2026</v>
       </c>
@@ -8301,11 +8073,7 @@
       <c r="E404" t="n">
         <v>64</v>
       </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -8313,11 +8081,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B405" t="inlineStr"/>
       <c r="C405" t="n">
         <v>2026</v>
       </c>
@@ -8327,11 +8091,7 @@
       <c r="E405" t="n">
         <v>35</v>
       </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -8339,11 +8099,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B406" t="inlineStr"/>
       <c r="C406" t="n">
         <v>2026</v>
       </c>
@@ -8353,11 +8109,7 @@
       <c r="E406" t="n">
         <v>59</v>
       </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -8365,11 +8117,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B407" t="inlineStr"/>
       <c r="C407" t="n">
         <v>2026</v>
       </c>
@@ -8379,11 +8127,7 @@
       <c r="E407" t="n">
         <v>64</v>
       </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -8391,11 +8135,7 @@
           <t>Maranguape</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B408" t="inlineStr"/>
       <c r="C408" t="n">
         <v>2026</v>
       </c>
@@ -8405,11 +8145,7 @@
       <c r="E408" t="n">
         <v>65</v>
       </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -8429,11 +8165,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -8443,11 +8179,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B410" t="inlineStr"/>
       <c r="C410" t="n">
         <v>2024</v>
       </c>
@@ -8457,11 +8189,7 @@
       <c r="E410" t="n">
         <v>199</v>
       </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -8469,11 +8197,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B411" t="inlineStr"/>
       <c r="C411" t="n">
         <v>2024</v>
       </c>
@@ -8483,11 +8207,7 @@
       <c r="E411" t="n">
         <v>136</v>
       </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -8495,11 +8215,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B412" t="inlineStr"/>
       <c r="C412" t="n">
         <v>2024</v>
       </c>
@@ -8509,11 +8225,7 @@
       <c r="E412" t="n">
         <v>148</v>
       </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -8521,11 +8233,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B413" t="inlineStr"/>
       <c r="C413" t="n">
         <v>2024</v>
       </c>
@@ -8535,11 +8243,7 @@
       <c r="E413" t="n">
         <v>108</v>
       </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -8547,11 +8251,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B414" t="inlineStr"/>
       <c r="C414" t="n">
         <v>2024</v>
       </c>
@@ -8561,11 +8261,7 @@
       <c r="E414" t="n">
         <v>135</v>
       </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -8573,11 +8269,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B415" t="inlineStr"/>
       <c r="C415" t="n">
         <v>2024</v>
       </c>
@@ -8587,11 +8279,7 @@
       <c r="E415" t="n">
         <v>142</v>
       </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -8599,11 +8287,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B416" t="inlineStr"/>
       <c r="C416" t="n">
         <v>2024</v>
       </c>
@@ -8613,11 +8297,7 @@
       <c r="E416" t="n">
         <v>63</v>
       </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -8625,11 +8305,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B417" t="inlineStr"/>
       <c r="C417" t="n">
         <v>2024</v>
       </c>
@@ -8639,11 +8315,7 @@
       <c r="E417" t="n">
         <v>179</v>
       </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -8651,11 +8323,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B418" t="inlineStr"/>
       <c r="C418" t="n">
         <v>2024</v>
       </c>
@@ -8665,11 +8333,7 @@
       <c r="E418" t="n">
         <v>198</v>
       </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -8677,11 +8341,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B419" t="inlineStr"/>
       <c r="C419" t="n">
         <v>2024</v>
       </c>
@@ -8691,11 +8351,7 @@
       <c r="E419" t="n">
         <v>126</v>
       </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -8703,11 +8359,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B420" t="inlineStr"/>
       <c r="C420" t="n">
         <v>2024</v>
       </c>
@@ -8717,11 +8369,7 @@
       <c r="E420" t="n">
         <v>143</v>
       </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -8729,11 +8377,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B421" t="inlineStr"/>
       <c r="C421" t="n">
         <v>2024</v>
       </c>
@@ -8743,11 +8387,7 @@
       <c r="E421" t="n">
         <v>180</v>
       </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -8755,11 +8395,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B422" t="inlineStr"/>
       <c r="C422" t="n">
         <v>2025</v>
       </c>
@@ -8769,11 +8405,7 @@
       <c r="E422" t="n">
         <v>301</v>
       </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -8781,11 +8413,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B423" t="inlineStr"/>
       <c r="C423" t="n">
         <v>2025</v>
       </c>
@@ -8795,11 +8423,7 @@
       <c r="E423" t="n">
         <v>225</v>
       </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -8807,11 +8431,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B424" t="inlineStr"/>
       <c r="C424" t="n">
         <v>2025</v>
       </c>
@@ -8821,11 +8441,7 @@
       <c r="E424" t="n">
         <v>185</v>
       </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -8833,11 +8449,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B425" t="inlineStr"/>
       <c r="C425" t="n">
         <v>2025</v>
       </c>
@@ -8847,11 +8459,7 @@
       <c r="E425" t="n">
         <v>173</v>
       </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -8859,11 +8467,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B426" t="inlineStr"/>
       <c r="C426" t="n">
         <v>2025</v>
       </c>
@@ -8873,11 +8477,7 @@
       <c r="E426" t="n">
         <v>235</v>
       </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -8885,11 +8485,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B427" t="inlineStr"/>
       <c r="C427" t="n">
         <v>2025</v>
       </c>
@@ -8899,11 +8495,7 @@
       <c r="E427" t="n">
         <v>176</v>
       </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -8911,11 +8503,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B428" t="inlineStr"/>
       <c r="C428" t="n">
         <v>2025</v>
       </c>
@@ -8925,11 +8513,7 @@
       <c r="E428" t="n">
         <v>229</v>
       </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -8937,11 +8521,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B429" t="inlineStr"/>
       <c r="C429" t="n">
         <v>2025</v>
       </c>
@@ -8951,11 +8531,7 @@
       <c r="E429" t="n">
         <v>248</v>
       </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -8963,11 +8539,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B430" t="inlineStr"/>
       <c r="C430" t="n">
         <v>2025</v>
       </c>
@@ -8977,11 +8549,7 @@
       <c r="E430" t="n">
         <v>214</v>
       </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -8989,11 +8557,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B431" t="inlineStr"/>
       <c r="C431" t="n">
         <v>2025</v>
       </c>
@@ -9003,11 +8567,7 @@
       <c r="E431" t="n">
         <v>194</v>
       </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9015,11 +8575,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B432" t="inlineStr"/>
       <c r="C432" t="n">
         <v>2025</v>
       </c>
@@ -9029,11 +8585,7 @@
       <c r="E432" t="n">
         <v>185</v>
       </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9041,11 +8593,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B433" t="inlineStr"/>
       <c r="C433" t="n">
         <v>2025</v>
       </c>
@@ -9055,11 +8603,7 @@
       <c r="E433" t="n">
         <v>146</v>
       </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9067,11 +8611,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B434" t="inlineStr"/>
       <c r="C434" t="n">
         <v>2026</v>
       </c>
@@ -9081,11 +8621,7 @@
       <c r="E434" t="n">
         <v>229</v>
       </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -9093,11 +8629,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B435" t="inlineStr"/>
       <c r="C435" t="n">
         <v>2026</v>
       </c>
@@ -9107,11 +8639,7 @@
       <c r="E435" t="n">
         <v>126</v>
       </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -9119,11 +8647,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B436" t="inlineStr"/>
       <c r="C436" t="n">
         <v>2026</v>
       </c>
@@ -9133,11 +8657,7 @@
       <c r="E436" t="n">
         <v>156</v>
       </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -9145,11 +8665,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B437" t="inlineStr"/>
       <c r="C437" t="n">
         <v>2026</v>
       </c>
@@ -9159,11 +8675,7 @@
       <c r="E437" t="n">
         <v>168</v>
       </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -9171,11 +8683,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B438" t="inlineStr"/>
       <c r="C438" t="n">
         <v>2026</v>
       </c>
@@ -9185,11 +8693,7 @@
       <c r="E438" t="n">
         <v>132</v>
       </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -9197,11 +8701,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B439" t="inlineStr"/>
       <c r="C439" t="n">
         <v>2026</v>
       </c>
@@ -9211,11 +8711,7 @@
       <c r="E439" t="n">
         <v>122</v>
       </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -9223,11 +8719,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B440" t="inlineStr"/>
       <c r="C440" t="n">
         <v>2026</v>
       </c>
@@ -9237,11 +8729,7 @@
       <c r="E440" t="n">
         <v>241</v>
       </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -9249,11 +8737,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B441" t="inlineStr"/>
       <c r="C441" t="n">
         <v>2026</v>
       </c>
@@ -9263,11 +8747,7 @@
       <c r="E441" t="n">
         <v>262</v>
       </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -9275,11 +8755,7 @@
           <t>Maraponga</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B442" t="inlineStr"/>
       <c r="C442" t="n">
         <v>2026</v>
       </c>
@@ -9289,11 +8765,7 @@
       <c r="E442" t="n">
         <v>230</v>
       </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>2026-10-03 11:29</t>
-        </is>
-      </c>
+      <c r="F442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -9313,11 +8785,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -9933,11 +9405,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -10553,11 +10025,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -11173,11 +10645,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -11793,11 +11265,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -12413,11 +11885,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -13033,11 +12505,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -13653,11 +13125,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -13667,7 +13139,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr"/>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C682" t="n">
         <v>2024</v>
       </c>
@@ -13677,7 +13153,11 @@
       <c r="E682" t="n">
         <v>156</v>
       </c>
-      <c r="F682" t="inlineStr"/>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -13685,7 +13165,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr"/>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C683" t="n">
         <v>2024</v>
       </c>
@@ -13695,7 +13179,11 @@
       <c r="E683" t="n">
         <v>94</v>
       </c>
-      <c r="F683" t="inlineStr"/>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -13703,7 +13191,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B684" t="inlineStr"/>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C684" t="n">
         <v>2024</v>
       </c>
@@ -13713,7 +13205,11 @@
       <c r="E684" t="n">
         <v>113</v>
       </c>
-      <c r="F684" t="inlineStr"/>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -13721,7 +13217,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr"/>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C685" t="n">
         <v>2024</v>
       </c>
@@ -13731,7 +13231,11 @@
       <c r="E685" t="n">
         <v>94</v>
       </c>
-      <c r="F685" t="inlineStr"/>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -13739,7 +13243,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr"/>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C686" t="n">
         <v>2024</v>
       </c>
@@ -13749,7 +13257,11 @@
       <c r="E686" t="n">
         <v>87</v>
       </c>
-      <c r="F686" t="inlineStr"/>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -13757,7 +13269,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B687" t="inlineStr"/>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C687" t="n">
         <v>2024</v>
       </c>
@@ -13767,7 +13283,11 @@
       <c r="E687" t="n">
         <v>85</v>
       </c>
-      <c r="F687" t="inlineStr"/>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -13775,7 +13295,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B688" t="inlineStr"/>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C688" t="n">
         <v>2024</v>
       </c>
@@ -13785,7 +13309,11 @@
       <c r="E688" t="n">
         <v>60</v>
       </c>
-      <c r="F688" t="inlineStr"/>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -13793,7 +13321,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B689" t="inlineStr"/>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C689" t="n">
         <v>2024</v>
       </c>
@@ -13803,7 +13335,11 @@
       <c r="E689" t="n">
         <v>92</v>
       </c>
-      <c r="F689" t="inlineStr"/>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -13811,7 +13347,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B690" t="inlineStr"/>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C690" t="n">
         <v>2024</v>
       </c>
@@ -13821,7 +13361,11 @@
       <c r="E690" t="n">
         <v>95</v>
       </c>
-      <c r="F690" t="inlineStr"/>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -13829,7 +13373,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B691" t="inlineStr"/>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C691" t="n">
         <v>2024</v>
       </c>
@@ -13839,7 +13387,11 @@
       <c r="E691" t="n">
         <v>106</v>
       </c>
-      <c r="F691" t="inlineStr"/>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -13847,7 +13399,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B692" t="inlineStr"/>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C692" t="n">
         <v>2024</v>
       </c>
@@ -13857,7 +13413,11 @@
       <c r="E692" t="n">
         <v>68</v>
       </c>
-      <c r="F692" t="inlineStr"/>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -13865,7 +13425,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B693" t="inlineStr"/>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C693" t="n">
         <v>2024</v>
       </c>
@@ -13875,7 +13439,11 @@
       <c r="E693" t="n">
         <v>116</v>
       </c>
-      <c r="F693" t="inlineStr"/>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -13883,7 +13451,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B694" t="inlineStr"/>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C694" t="n">
         <v>2025</v>
       </c>
@@ -13893,7 +13465,11 @@
       <c r="E694" t="n">
         <v>210</v>
       </c>
-      <c r="F694" t="inlineStr"/>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -13901,7 +13477,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B695" t="inlineStr"/>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C695" t="n">
         <v>2025</v>
       </c>
@@ -13911,7 +13491,11 @@
       <c r="E695" t="n">
         <v>144</v>
       </c>
-      <c r="F695" t="inlineStr"/>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -13919,7 +13503,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr"/>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C696" t="n">
         <v>2025</v>
       </c>
@@ -13929,7 +13517,11 @@
       <c r="E696" t="n">
         <v>131</v>
       </c>
-      <c r="F696" t="inlineStr"/>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -13937,7 +13529,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B697" t="inlineStr"/>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C697" t="n">
         <v>2025</v>
       </c>
@@ -13947,7 +13543,11 @@
       <c r="E697" t="n">
         <v>101</v>
       </c>
-      <c r="F697" t="inlineStr"/>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -13955,7 +13555,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr"/>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C698" t="n">
         <v>2025</v>
       </c>
@@ -13965,7 +13569,11 @@
       <c r="E698" t="n">
         <v>133</v>
       </c>
-      <c r="F698" t="inlineStr"/>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -13973,7 +13581,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr"/>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C699" t="n">
         <v>2025</v>
       </c>
@@ -13983,7 +13595,11 @@
       <c r="E699" t="n">
         <v>89</v>
       </c>
-      <c r="F699" t="inlineStr"/>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -13991,7 +13607,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr"/>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C700" t="n">
         <v>2025</v>
       </c>
@@ -14001,7 +13621,11 @@
       <c r="E700" t="n">
         <v>90</v>
       </c>
-      <c r="F700" t="inlineStr"/>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -14009,7 +13633,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr"/>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C701" t="n">
         <v>2025</v>
       </c>
@@ -14019,7 +13647,11 @@
       <c r="E701" t="n">
         <v>148</v>
       </c>
-      <c r="F701" t="inlineStr"/>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -14027,7 +13659,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr"/>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C702" t="n">
         <v>2025</v>
       </c>
@@ -14037,7 +13673,11 @@
       <c r="E702" t="n">
         <v>102</v>
       </c>
-      <c r="F702" t="inlineStr"/>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -14045,7 +13685,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C703" t="n">
         <v>2025</v>
       </c>
@@ -14055,7 +13699,11 @@
       <c r="E703" t="n">
         <v>101</v>
       </c>
-      <c r="F703" t="inlineStr"/>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -14063,7 +13711,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr"/>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C704" t="n">
         <v>2025</v>
       </c>
@@ -14073,7 +13725,11 @@
       <c r="E704" t="n">
         <v>79</v>
       </c>
-      <c r="F704" t="inlineStr"/>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -14081,7 +13737,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr"/>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C705" t="n">
         <v>2025</v>
       </c>
@@ -14091,7 +13751,11 @@
       <c r="E705" t="n">
         <v>106</v>
       </c>
-      <c r="F705" t="inlineStr"/>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -14099,7 +13763,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr"/>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C706" t="n">
         <v>2026</v>
       </c>
@@ -14109,7 +13777,11 @@
       <c r="E706" t="n">
         <v>173</v>
       </c>
-      <c r="F706" t="inlineStr"/>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -14117,7 +13789,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr"/>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C707" t="n">
         <v>2026</v>
       </c>
@@ -14127,7 +13803,11 @@
       <c r="E707" t="n">
         <v>98</v>
       </c>
-      <c r="F707" t="inlineStr"/>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -14135,7 +13815,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B708" t="inlineStr"/>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C708" t="n">
         <v>2026</v>
       </c>
@@ -14145,7 +13829,11 @@
       <c r="E708" t="n">
         <v>114</v>
       </c>
-      <c r="F708" t="inlineStr"/>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -14153,7 +13841,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr"/>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C709" t="n">
         <v>2026</v>
       </c>
@@ -14163,7 +13855,11 @@
       <c r="E709" t="n">
         <v>85</v>
       </c>
-      <c r="F709" t="inlineStr"/>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -14171,7 +13867,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B710" t="inlineStr"/>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C710" t="n">
         <v>2026</v>
       </c>
@@ -14181,7 +13881,11 @@
       <c r="E710" t="n">
         <v>78</v>
       </c>
-      <c r="F710" t="inlineStr"/>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -14189,7 +13893,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr"/>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C711" t="n">
         <v>2026</v>
       </c>
@@ -14199,7 +13907,11 @@
       <c r="E711" t="n">
         <v>82</v>
       </c>
-      <c r="F711" t="inlineStr"/>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -14207,7 +13919,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B712" t="inlineStr"/>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C712" t="n">
         <v>2026</v>
       </c>
@@ -14217,7 +13933,11 @@
       <c r="E712" t="n">
         <v>123</v>
       </c>
-      <c r="F712" t="inlineStr"/>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -14225,7 +13945,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr"/>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C713" t="n">
         <v>2026</v>
       </c>
@@ -14235,7 +13959,11 @@
       <c r="E713" t="n">
         <v>110</v>
       </c>
-      <c r="F713" t="inlineStr"/>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -14243,7 +13971,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr"/>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C714" t="n">
         <v>2026</v>
       </c>
@@ -14253,7 +13985,11 @@
       <c r="E714" t="n">
         <v>85</v>
       </c>
-      <c r="F714" t="inlineStr"/>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:03</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -14277,7 +14013,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -14893,11 +14629,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -15513,11 +15249,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -16137,7 +15873,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-03 11:29</t>
+          <t>2026-10-04 12:03</t>
         </is>
       </c>
     </row>
@@ -16376,106 +16112,106 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AI2" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -16485,106 +16221,106 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -16594,106 +16330,106 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>573</v>
+        <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
+        <v>52</v>
+      </c>
+      <c r="H4" t="n">
+        <v>61</v>
+      </c>
+      <c r="I4" t="n">
+        <v>114</v>
+      </c>
+      <c r="J4" t="n">
+        <v>112</v>
+      </c>
+      <c r="K4" t="n">
+        <v>124</v>
+      </c>
+      <c r="L4" t="n">
+        <v>89</v>
+      </c>
+      <c r="M4" t="n">
+        <v>163</v>
+      </c>
+      <c r="N4" t="n">
+        <v>211</v>
+      </c>
+      <c r="O4" t="n">
+        <v>151</v>
+      </c>
+      <c r="P4" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>121</v>
+      </c>
+      <c r="R4" t="n">
+        <v>171</v>
+      </c>
+      <c r="S4" t="n">
+        <v>123</v>
+      </c>
+      <c r="T4" t="n">
+        <v>128</v>
+      </c>
+      <c r="U4" t="n">
+        <v>128</v>
+      </c>
+      <c r="V4" t="n">
         <v>155</v>
       </c>
-      <c r="H4" t="n">
-        <v>155</v>
-      </c>
-      <c r="I4" t="n">
-        <v>178</v>
-      </c>
-      <c r="J4" t="n">
-        <v>186</v>
-      </c>
-      <c r="K4" t="n">
-        <v>178</v>
-      </c>
-      <c r="L4" t="n">
-        <v>114</v>
-      </c>
-      <c r="M4" t="n">
-        <v>197</v>
-      </c>
-      <c r="N4" t="n">
-        <v>352</v>
-      </c>
-      <c r="O4" t="n">
-        <v>227</v>
-      </c>
-      <c r="P4" t="n">
-        <v>218</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>190</v>
-      </c>
-      <c r="R4" t="n">
-        <v>176</v>
-      </c>
-      <c r="S4" t="n">
-        <v>152</v>
-      </c>
-      <c r="T4" t="n">
-        <v>193</v>
-      </c>
-      <c r="U4" t="n">
-        <v>204</v>
-      </c>
-      <c r="V4" t="n">
-        <v>203</v>
-      </c>
       <c r="W4" t="n">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="X4" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="Y4" t="n">
+        <v>132</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>189</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>89</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>118</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>132</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>153</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>139</v>
+      </c>
+      <c r="AH4" t="n">
         <v>136</v>
       </c>
-      <c r="Z4" t="n">
-        <v>265</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>142</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>115</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>109</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>163</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>147</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>139</v>
-      </c>
       <c r="AI4" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -16802,7 +16538,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -16911,7 +16647,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>242</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -4195,11 +4195,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
         <v>2024</v>
       </c>
@@ -4209,11 +4205,7 @@
       <c r="E206" t="n">
         <v>114</v>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4221,11 +4213,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
         <v>2024</v>
       </c>
@@ -4235,11 +4223,7 @@
       <c r="E207" t="n">
         <v>81</v>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4247,11 +4231,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
         <v>2024</v>
       </c>
@@ -4261,11 +4241,7 @@
       <c r="E208" t="n">
         <v>90</v>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4273,11 +4249,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
         <v>2024</v>
       </c>
@@ -4287,11 +4259,7 @@
       <c r="E209" t="n">
         <v>52</v>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4299,11 +4267,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
         <v>2024</v>
       </c>
@@ -4313,11 +4277,7 @@
       <c r="E210" t="n">
         <v>70</v>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4325,11 +4285,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
         <v>2024</v>
       </c>
@@ -4339,11 +4295,7 @@
       <c r="E211" t="n">
         <v>52</v>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4351,11 +4303,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
         <v>2024</v>
       </c>
@@ -4365,11 +4313,7 @@
       <c r="E212" t="n">
         <v>61</v>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4377,11 +4321,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
         <v>2024</v>
       </c>
@@ -4391,11 +4331,7 @@
       <c r="E213" t="n">
         <v>114</v>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4403,11 +4339,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
         <v>2024</v>
       </c>
@@ -4417,11 +4349,7 @@
       <c r="E214" t="n">
         <v>112</v>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4429,11 +4357,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
         <v>2024</v>
       </c>
@@ -4443,11 +4367,7 @@
       <c r="E215" t="n">
         <v>124</v>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4455,11 +4375,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
         <v>2024</v>
       </c>
@@ -4469,11 +4385,7 @@
       <c r="E216" t="n">
         <v>89</v>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4481,11 +4393,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
         <v>2024</v>
       </c>
@@ -4495,11 +4403,7 @@
       <c r="E217" t="n">
         <v>163</v>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4507,11 +4411,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
         <v>2025</v>
       </c>
@@ -4521,11 +4421,7 @@
       <c r="E218" t="n">
         <v>211</v>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4533,11 +4429,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
         <v>2025</v>
       </c>
@@ -4547,11 +4439,7 @@
       <c r="E219" t="n">
         <v>151</v>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4559,11 +4447,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
         <v>2025</v>
       </c>
@@ -4573,11 +4457,7 @@
       <c r="E220" t="n">
         <v>131</v>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4585,11 +4465,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
         <v>2025</v>
       </c>
@@ -4599,11 +4475,7 @@
       <c r="E221" t="n">
         <v>121</v>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4611,11 +4483,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
         <v>2025</v>
       </c>
@@ -4625,11 +4493,7 @@
       <c r="E222" t="n">
         <v>171</v>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4637,11 +4501,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
         <v>2025</v>
       </c>
@@ -4651,11 +4511,7 @@
       <c r="E223" t="n">
         <v>123</v>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4663,11 +4519,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="n">
         <v>2025</v>
       </c>
@@ -4677,11 +4529,7 @@
       <c r="E224" t="n">
         <v>128</v>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4689,11 +4537,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="n">
         <v>2025</v>
       </c>
@@ -4703,11 +4547,7 @@
       <c r="E225" t="n">
         <v>128</v>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4715,11 +4555,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
         <v>2025</v>
       </c>
@@ -4729,11 +4565,7 @@
       <c r="E226" t="n">
         <v>155</v>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4741,11 +4573,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
         <v>2025</v>
       </c>
@@ -4755,11 +4583,7 @@
       <c r="E227" t="n">
         <v>139</v>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4767,11 +4591,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
         <v>2025</v>
       </c>
@@ -4781,11 +4601,7 @@
       <c r="E228" t="n">
         <v>140</v>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4793,11 +4609,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
         <v>2025</v>
       </c>
@@ -4807,11 +4619,7 @@
       <c r="E229" t="n">
         <v>132</v>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4819,11 +4627,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
         <v>2026</v>
       </c>
@@ -4833,11 +4637,7 @@
       <c r="E230" t="n">
         <v>189</v>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4845,11 +4645,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
         <v>2026</v>
       </c>
@@ -4859,11 +4655,7 @@
       <c r="E231" t="n">
         <v>89</v>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4871,11 +4663,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
         <v>2026</v>
       </c>
@@ -4885,11 +4673,7 @@
       <c r="E232" t="n">
         <v>110</v>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4897,11 +4681,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
         <v>2026</v>
       </c>
@@ -4911,11 +4691,7 @@
       <c r="E233" t="n">
         <v>122</v>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4923,11 +4699,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
         <v>2026</v>
       </c>
@@ -4937,11 +4709,7 @@
       <c r="E234" t="n">
         <v>118</v>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4949,11 +4717,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
         <v>2026</v>
       </c>
@@ -4963,11 +4727,7 @@
       <c r="E235" t="n">
         <v>132</v>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4975,11 +4735,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
         <v>2026</v>
       </c>
@@ -4989,11 +4745,7 @@
       <c r="E236" t="n">
         <v>153</v>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5001,11 +4753,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
         <v>2026</v>
       </c>
@@ -5015,11 +4763,7 @@
       <c r="E237" t="n">
         <v>139</v>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5027,11 +4771,7 @@
           <t>Eusebio</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
         <v>2026</v>
       </c>
@@ -5041,11 +4781,7 @@
       <c r="E238" t="n">
         <v>136</v>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5065,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -5685,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -6305,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -6925,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -7545,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -8165,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -8785,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -9405,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -10025,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -10645,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11005,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -11885,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -12505,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -13125,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -13139,11 +12875,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B682" t="inlineStr"/>
       <c r="C682" t="n">
         <v>2024</v>
       </c>
@@ -13153,11 +12885,7 @@
       <c r="E682" t="n">
         <v>156</v>
       </c>
-      <c r="F682" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -13165,11 +12893,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B683" t="inlineStr"/>
       <c r="C683" t="n">
         <v>2024</v>
       </c>
@@ -13179,11 +12903,7 @@
       <c r="E683" t="n">
         <v>94</v>
       </c>
-      <c r="F683" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -13191,11 +12911,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B684" t="inlineStr"/>
       <c r="C684" t="n">
         <v>2024</v>
       </c>
@@ -13205,11 +12921,7 @@
       <c r="E684" t="n">
         <v>113</v>
       </c>
-      <c r="F684" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -13217,11 +12929,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B685" t="inlineStr"/>
       <c r="C685" t="n">
         <v>2024</v>
       </c>
@@ -13231,11 +12939,7 @@
       <c r="E685" t="n">
         <v>94</v>
       </c>
-      <c r="F685" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -13243,11 +12947,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B686" t="inlineStr"/>
       <c r="C686" t="n">
         <v>2024</v>
       </c>
@@ -13257,11 +12957,7 @@
       <c r="E686" t="n">
         <v>87</v>
       </c>
-      <c r="F686" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -13269,11 +12965,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B687" t="inlineStr"/>
       <c r="C687" t="n">
         <v>2024</v>
       </c>
@@ -13283,11 +12975,7 @@
       <c r="E687" t="n">
         <v>85</v>
       </c>
-      <c r="F687" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -13295,11 +12983,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B688" t="inlineStr"/>
       <c r="C688" t="n">
         <v>2024</v>
       </c>
@@ -13309,11 +12993,7 @@
       <c r="E688" t="n">
         <v>60</v>
       </c>
-      <c r="F688" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -13321,11 +13001,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B689" t="inlineStr"/>
       <c r="C689" t="n">
         <v>2024</v>
       </c>
@@ -13335,11 +13011,7 @@
       <c r="E689" t="n">
         <v>92</v>
       </c>
-      <c r="F689" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -13347,11 +13019,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B690" t="inlineStr"/>
       <c r="C690" t="n">
         <v>2024</v>
       </c>
@@ -13361,11 +13029,7 @@
       <c r="E690" t="n">
         <v>95</v>
       </c>
-      <c r="F690" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -13373,11 +13037,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B691" t="inlineStr"/>
       <c r="C691" t="n">
         <v>2024</v>
       </c>
@@ -13387,11 +13047,7 @@
       <c r="E691" t="n">
         <v>106</v>
       </c>
-      <c r="F691" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -13399,11 +13055,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B692" t="inlineStr"/>
       <c r="C692" t="n">
         <v>2024</v>
       </c>
@@ -13413,11 +13065,7 @@
       <c r="E692" t="n">
         <v>68</v>
       </c>
-      <c r="F692" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -13425,11 +13073,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B693" t="inlineStr"/>
       <c r="C693" t="n">
         <v>2024</v>
       </c>
@@ -13439,11 +13083,7 @@
       <c r="E693" t="n">
         <v>116</v>
       </c>
-      <c r="F693" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -13451,11 +13091,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B694" t="inlineStr"/>
       <c r="C694" t="n">
         <v>2025</v>
       </c>
@@ -13465,11 +13101,7 @@
       <c r="E694" t="n">
         <v>210</v>
       </c>
-      <c r="F694" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -13477,11 +13109,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B695" t="inlineStr"/>
       <c r="C695" t="n">
         <v>2025</v>
       </c>
@@ -13491,11 +13119,7 @@
       <c r="E695" t="n">
         <v>144</v>
       </c>
-      <c r="F695" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -13503,11 +13127,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B696" t="inlineStr"/>
       <c r="C696" t="n">
         <v>2025</v>
       </c>
@@ -13517,11 +13137,7 @@
       <c r="E696" t="n">
         <v>131</v>
       </c>
-      <c r="F696" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -13529,11 +13145,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B697" t="inlineStr"/>
       <c r="C697" t="n">
         <v>2025</v>
       </c>
@@ -13543,11 +13155,7 @@
       <c r="E697" t="n">
         <v>101</v>
       </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -13555,11 +13163,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B698" t="inlineStr"/>
       <c r="C698" t="n">
         <v>2025</v>
       </c>
@@ -13569,11 +13173,7 @@
       <c r="E698" t="n">
         <v>133</v>
       </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -13581,11 +13181,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B699" t="inlineStr"/>
       <c r="C699" t="n">
         <v>2025</v>
       </c>
@@ -13595,11 +13191,7 @@
       <c r="E699" t="n">
         <v>89</v>
       </c>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -13607,11 +13199,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B700" t="inlineStr"/>
       <c r="C700" t="n">
         <v>2025</v>
       </c>
@@ -13621,11 +13209,7 @@
       <c r="E700" t="n">
         <v>90</v>
       </c>
-      <c r="F700" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -13633,11 +13217,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B701" t="inlineStr"/>
       <c r="C701" t="n">
         <v>2025</v>
       </c>
@@ -13647,11 +13227,7 @@
       <c r="E701" t="n">
         <v>148</v>
       </c>
-      <c r="F701" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -13659,11 +13235,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B702" t="inlineStr"/>
       <c r="C702" t="n">
         <v>2025</v>
       </c>
@@ -13673,11 +13245,7 @@
       <c r="E702" t="n">
         <v>102</v>
       </c>
-      <c r="F702" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -13685,11 +13253,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B703" t="inlineStr"/>
       <c r="C703" t="n">
         <v>2025</v>
       </c>
@@ -13699,11 +13263,7 @@
       <c r="E703" t="n">
         <v>101</v>
       </c>
-      <c r="F703" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -13711,11 +13271,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B704" t="inlineStr"/>
       <c r="C704" t="n">
         <v>2025</v>
       </c>
@@ -13725,11 +13281,7 @@
       <c r="E704" t="n">
         <v>79</v>
       </c>
-      <c r="F704" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -13737,11 +13289,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B705" t="inlineStr"/>
       <c r="C705" t="n">
         <v>2025</v>
       </c>
@@ -13751,11 +13299,7 @@
       <c r="E705" t="n">
         <v>106</v>
       </c>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -13763,11 +13307,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B706" t="inlineStr"/>
       <c r="C706" t="n">
         <v>2026</v>
       </c>
@@ -13777,11 +13317,7 @@
       <c r="E706" t="n">
         <v>173</v>
       </c>
-      <c r="F706" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -13789,11 +13325,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B707" t="inlineStr"/>
       <c r="C707" t="n">
         <v>2026</v>
       </c>
@@ -13803,11 +13335,7 @@
       <c r="E707" t="n">
         <v>98</v>
       </c>
-      <c r="F707" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -13815,11 +13343,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B708" t="inlineStr"/>
       <c r="C708" t="n">
         <v>2026</v>
       </c>
@@ -13829,11 +13353,7 @@
       <c r="E708" t="n">
         <v>114</v>
       </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -13841,11 +13361,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B709" t="inlineStr"/>
       <c r="C709" t="n">
         <v>2026</v>
       </c>
@@ -13855,11 +13371,7 @@
       <c r="E709" t="n">
         <v>85</v>
       </c>
-      <c r="F709" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -13867,11 +13379,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B710" t="inlineStr"/>
       <c r="C710" t="n">
         <v>2026</v>
       </c>
@@ -13881,11 +13389,7 @@
       <c r="E710" t="n">
         <v>78</v>
       </c>
-      <c r="F710" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -13893,11 +13397,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B711" t="inlineStr"/>
       <c r="C711" t="n">
         <v>2026</v>
       </c>
@@ -13907,11 +13407,7 @@
       <c r="E711" t="n">
         <v>82</v>
       </c>
-      <c r="F711" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -13919,11 +13415,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B712" t="inlineStr"/>
       <c r="C712" t="n">
         <v>2026</v>
       </c>
@@ -13933,11 +13425,7 @@
       <c r="E712" t="n">
         <v>123</v>
       </c>
-      <c r="F712" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -13945,11 +13433,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B713" t="inlineStr"/>
       <c r="C713" t="n">
         <v>2026</v>
       </c>
@@ -13959,11 +13443,7 @@
       <c r="E713" t="n">
         <v>110</v>
       </c>
-      <c r="F713" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -13971,11 +13451,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B714" t="inlineStr"/>
       <c r="C714" t="n">
         <v>2026</v>
       </c>
@@ -13985,11 +13461,7 @@
       <c r="E714" t="n">
         <v>85</v>
       </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>2026-10-04 12:03</t>
-        </is>
-      </c>
+      <c r="F714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -14009,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -14629,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -15249,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -15869,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-04 12:03</t>
+          <t>2026-10-05 15:58</t>
         </is>
       </c>
     </row>
@@ -16112,106 +15584,106 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
@@ -16320,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4">
@@ -16330,106 +15802,106 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -16538,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -16647,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>305</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-05 15:58</t>
+          <t>2026-10-06 13:23</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>109</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>380</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23</t>
+          <t>2026-10-07 14:07</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>153</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>495</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-07 14:07</t>
+          <t>2026-10-08 14:06</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>167</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>114</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>606</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-08 14:06</t>
+          <t>2026-10-09 13:43</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>211</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>235</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>733</v>
+        <v>844</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-09 13:43</t>
+          <t>2026-10-10 12:41</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>255</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>161</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>156</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>844</v>
+        <v>958</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-10 12:41</t>
+          <t>2026-10-11 13:03</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>298</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>958</v>
+        <v>1037</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03</t>
+          <t>2026-10-12 16:32</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>320</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>317</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1037</v>
+        <v>1149</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-12 16:32</t>
+          <t>2026-10-13 14:15</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>348</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>356</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>220</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1149</v>
+        <v>1264</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-13 14:15</t>
+          <t>2026-10-14 11:48</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>379</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>389</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1264</v>
+        <v>1383</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-14 11:48</t>
+          <t>2026-10-15 11:32</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>430</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>429</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>271</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>253</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1383</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-15 11:32</t>
+          <t>2026-10-16 11:24</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>504</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>469</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1556</v>
+        <v>1667</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-16 11:24</t>
+          <t>2026-10-17 10:22</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>556</v>
+        <v>589</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>291</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1667</v>
+        <v>1783</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-17 10:22</t>
+          <t>2026-10-18 10:42</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>589</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>320</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1783</v>
+        <v>1852</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-18 10:42</t>
+          <t>2026-10-19 13:44</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>606</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>549</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>351</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1852</v>
+        <v>1938</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-19 13:44</t>
+          <t>2026-10-20 11:33</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>620</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>581</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>367</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>1938</v>
+        <v>2027</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33</t>
+          <t>2026-10-21 11:47</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>647</v>
+        <v>695</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>611</v>
+        <v>660</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>384</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>385</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2027</v>
+        <v>2160</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47</t>
+          <t>2026-10-22 11:46</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>695</v>
+        <v>725</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>660</v>
+        <v>683</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>406</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>399</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2160</v>
+        <v>2244</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C274" t="n">
         <v>2024</v>
       </c>
@@ -5445,7 +5449,11 @@
       <c r="E274" t="n">
         <v>116</v>
       </c>
-      <c r="F274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5453,7 +5461,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C275" t="n">
         <v>2024</v>
       </c>
@@ -5463,7 +5475,11 @@
       <c r="E275" t="n">
         <v>81</v>
       </c>
-      <c r="F275" t="inlineStr"/>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5471,7 +5487,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C276" t="n">
         <v>2024</v>
       </c>
@@ -5481,7 +5501,11 @@
       <c r="E276" t="n">
         <v>79</v>
       </c>
-      <c r="F276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5489,7 +5513,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C277" t="n">
         <v>2024</v>
       </c>
@@ -5499,7 +5527,11 @@
       <c r="E277" t="n">
         <v>54</v>
       </c>
-      <c r="F277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5507,7 +5539,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C278" t="n">
         <v>2024</v>
       </c>
@@ -5517,7 +5553,11 @@
       <c r="E278" t="n">
         <v>27</v>
       </c>
-      <c r="F278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5525,7 +5565,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C279" t="n">
         <v>2024</v>
       </c>
@@ -5535,7 +5579,11 @@
       <c r="E279" t="n">
         <v>78</v>
       </c>
-      <c r="F279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5543,7 +5591,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C280" t="n">
         <v>2024</v>
       </c>
@@ -5553,7 +5605,11 @@
       <c r="E280" t="n">
         <v>52</v>
       </c>
-      <c r="F280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5561,7 +5617,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C281" t="n">
         <v>2024</v>
       </c>
@@ -5571,7 +5631,11 @@
       <c r="E281" t="n">
         <v>110</v>
       </c>
-      <c r="F281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5579,7 +5643,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C282" t="n">
         <v>2024</v>
       </c>
@@ -5589,7 +5657,11 @@
       <c r="E282" t="n">
         <v>108</v>
       </c>
-      <c r="F282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5597,7 +5669,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C283" t="n">
         <v>2024</v>
       </c>
@@ -5607,7 +5683,11 @@
       <c r="E283" t="n">
         <v>102</v>
       </c>
-      <c r="F283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5615,7 +5695,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C284" t="n">
         <v>2024</v>
       </c>
@@ -5625,7 +5709,11 @@
       <c r="E284" t="n">
         <v>78</v>
       </c>
-      <c r="F284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5633,7 +5721,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C285" t="n">
         <v>2024</v>
       </c>
@@ -5643,7 +5735,11 @@
       <c r="E285" t="n">
         <v>121</v>
       </c>
-      <c r="F285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5651,7 +5747,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C286" t="n">
         <v>2025</v>
       </c>
@@ -5661,7 +5761,11 @@
       <c r="E286" t="n">
         <v>223</v>
       </c>
-      <c r="F286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5669,7 +5773,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C287" t="n">
         <v>2025</v>
       </c>
@@ -5679,7 +5787,11 @@
       <c r="E287" t="n">
         <v>122</v>
       </c>
-      <c r="F287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5687,7 +5799,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C288" t="n">
         <v>2025</v>
       </c>
@@ -5697,7 +5813,11 @@
       <c r="E288" t="n">
         <v>147</v>
       </c>
-      <c r="F288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5705,7 +5825,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C289" t="n">
         <v>2025</v>
       </c>
@@ -5715,7 +5839,11 @@
       <c r="E289" t="n">
         <v>128</v>
       </c>
-      <c r="F289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5723,7 +5851,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C290" t="n">
         <v>2025</v>
       </c>
@@ -5733,7 +5865,11 @@
       <c r="E290" t="n">
         <v>103</v>
       </c>
-      <c r="F290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5741,7 +5877,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C291" t="n">
         <v>2025</v>
       </c>
@@ -5751,7 +5891,11 @@
       <c r="E291" t="n">
         <v>106</v>
       </c>
-      <c r="F291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5759,7 +5903,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C292" t="n">
         <v>2025</v>
       </c>
@@ -5769,7 +5917,11 @@
       <c r="E292" t="n">
         <v>80</v>
       </c>
-      <c r="F292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5777,7 +5929,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C293" t="n">
         <v>2025</v>
       </c>
@@ -5787,7 +5943,11 @@
       <c r="E293" t="n">
         <v>107</v>
       </c>
-      <c r="F293" t="inlineStr"/>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5795,7 +5955,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C294" t="n">
         <v>2025</v>
       </c>
@@ -5805,7 +5969,11 @@
       <c r="E294" t="n">
         <v>86</v>
       </c>
-      <c r="F294" t="inlineStr"/>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5813,7 +5981,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C295" t="n">
         <v>2025</v>
       </c>
@@ -5823,7 +5995,11 @@
       <c r="E295" t="n">
         <v>85</v>
       </c>
-      <c r="F295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5831,7 +6007,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C296" t="n">
         <v>2025</v>
       </c>
@@ -5841,7 +6021,11 @@
       <c r="E296" t="n">
         <v>81</v>
       </c>
-      <c r="F296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5849,7 +6033,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C297" t="n">
         <v>2025</v>
       </c>
@@ -5859,7 +6047,11 @@
       <c r="E297" t="n">
         <v>77</v>
       </c>
-      <c r="F297" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5867,7 +6059,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C298" t="n">
         <v>2026</v>
       </c>
@@ -5877,7 +6073,11 @@
       <c r="E298" t="n">
         <v>106</v>
       </c>
-      <c r="F298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5885,7 +6085,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C299" t="n">
         <v>2026</v>
       </c>
@@ -5895,7 +6099,11 @@
       <c r="E299" t="n">
         <v>87</v>
       </c>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5903,7 +6111,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C300" t="n">
         <v>2026</v>
       </c>
@@ -5913,7 +6125,11 @@
       <c r="E300" t="n">
         <v>93</v>
       </c>
-      <c r="F300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5921,7 +6137,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C301" t="n">
         <v>2026</v>
       </c>
@@ -5931,7 +6151,11 @@
       <c r="E301" t="n">
         <v>87</v>
       </c>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5939,7 +6163,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C302" t="n">
         <v>2026</v>
       </c>
@@ -5949,7 +6177,11 @@
       <c r="E302" t="n">
         <v>118</v>
       </c>
-      <c r="F302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5957,7 +6189,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C303" t="n">
         <v>2026</v>
       </c>
@@ -5967,7 +6203,11 @@
       <c r="E303" t="n">
         <v>91</v>
       </c>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5975,7 +6215,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C304" t="n">
         <v>2026</v>
       </c>
@@ -5985,7 +6229,11 @@
       <c r="E304" t="n">
         <v>132</v>
       </c>
-      <c r="F304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5993,7 +6241,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C305" t="n">
         <v>2026</v>
       </c>
@@ -6003,7 +6255,11 @@
       <c r="E305" t="n">
         <v>80</v>
       </c>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6011,7 +6267,11 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C306" t="n">
         <v>2026</v>
       </c>
@@ -6021,7 +6281,11 @@
       <c r="E306" t="n">
         <v>70</v>
       </c>
-      <c r="F306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6045,7 +6309,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6925,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7545,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -7901,11 +8165,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8785,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9405,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -9761,11 +10025,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10645,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11265,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11885,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11899,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B614" t="inlineStr"/>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C614" t="n">
         <v>2024</v>
       </c>
@@ -11645,7 +11913,11 @@
       <c r="E614" t="n">
         <v>48</v>
       </c>
-      <c r="F614" t="inlineStr"/>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -11653,7 +11925,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B615" t="inlineStr"/>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C615" t="n">
         <v>2024</v>
       </c>
@@ -11663,7 +11939,11 @@
       <c r="E615" t="n">
         <v>79</v>
       </c>
-      <c r="F615" t="inlineStr"/>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -11671,7 +11951,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B616" t="inlineStr"/>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C616" t="n">
         <v>2024</v>
       </c>
@@ -11681,7 +11965,11 @@
       <c r="E616" t="n">
         <v>43</v>
       </c>
-      <c r="F616" t="inlineStr"/>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -11689,7 +11977,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B617" t="inlineStr"/>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C617" t="n">
         <v>2024</v>
       </c>
@@ -11699,7 +11991,11 @@
       <c r="E617" t="n">
         <v>34</v>
       </c>
-      <c r="F617" t="inlineStr"/>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -11707,7 +12003,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B618" t="inlineStr"/>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C618" t="n">
         <v>2024</v>
       </c>
@@ -11717,7 +12017,11 @@
       <c r="E618" t="n">
         <v>33</v>
       </c>
-      <c r="F618" t="inlineStr"/>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -11725,7 +12029,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B619" t="inlineStr"/>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C619" t="n">
         <v>2024</v>
       </c>
@@ -11735,7 +12043,11 @@
       <c r="E619" t="n">
         <v>25</v>
       </c>
-      <c r="F619" t="inlineStr"/>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -11743,7 +12055,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B620" t="inlineStr"/>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C620" t="n">
         <v>2024</v>
       </c>
@@ -11753,7 +12069,11 @@
       <c r="E620" t="n">
         <v>15</v>
       </c>
-      <c r="F620" t="inlineStr"/>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -11761,7 +12081,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B621" t="inlineStr"/>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C621" t="n">
         <v>2024</v>
       </c>
@@ -11771,7 +12095,11 @@
       <c r="E621" t="n">
         <v>14</v>
       </c>
-      <c r="F621" t="inlineStr"/>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -11779,7 +12107,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B622" t="inlineStr"/>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C622" t="n">
         <v>2024</v>
       </c>
@@ -11789,7 +12121,11 @@
       <c r="E622" t="n">
         <v>25</v>
       </c>
-      <c r="F622" t="inlineStr"/>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -11797,7 +12133,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B623" t="inlineStr"/>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C623" t="n">
         <v>2024</v>
       </c>
@@ -11807,7 +12147,11 @@
       <c r="E623" t="n">
         <v>21</v>
       </c>
-      <c r="F623" t="inlineStr"/>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -11815,7 +12159,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B624" t="inlineStr"/>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C624" t="n">
         <v>2024</v>
       </c>
@@ -11825,7 +12173,11 @@
       <c r="E624" t="n">
         <v>29</v>
       </c>
-      <c r="F624" t="inlineStr"/>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -11833,7 +12185,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B625" t="inlineStr"/>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C625" t="n">
         <v>2024</v>
       </c>
@@ -11843,7 +12199,11 @@
       <c r="E625" t="n">
         <v>56</v>
       </c>
-      <c r="F625" t="inlineStr"/>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -11851,7 +12211,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B626" t="inlineStr"/>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C626" t="n">
         <v>2025</v>
       </c>
@@ -11861,7 +12225,11 @@
       <c r="E626" t="n">
         <v>63</v>
       </c>
-      <c r="F626" t="inlineStr"/>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -11869,7 +12237,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B627" t="inlineStr"/>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C627" t="n">
         <v>2025</v>
       </c>
@@ -11879,7 +12251,11 @@
       <c r="E627" t="n">
         <v>42</v>
       </c>
-      <c r="F627" t="inlineStr"/>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -11887,7 +12263,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B628" t="inlineStr"/>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C628" t="n">
         <v>2025</v>
       </c>
@@ -11897,7 +12277,11 @@
       <c r="E628" t="n">
         <v>36</v>
       </c>
-      <c r="F628" t="inlineStr"/>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -11905,7 +12289,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B629" t="inlineStr"/>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C629" t="n">
         <v>2025</v>
       </c>
@@ -11915,7 +12303,11 @@
       <c r="E629" t="n">
         <v>26</v>
       </c>
-      <c r="F629" t="inlineStr"/>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -11923,7 +12315,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B630" t="inlineStr"/>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C630" t="n">
         <v>2025</v>
       </c>
@@ -11933,7 +12329,11 @@
       <c r="E630" t="n">
         <v>60</v>
       </c>
-      <c r="F630" t="inlineStr"/>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -11941,7 +12341,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B631" t="inlineStr"/>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C631" t="n">
         <v>2025</v>
       </c>
@@ -11951,7 +12355,11 @@
       <c r="E631" t="n">
         <v>44</v>
       </c>
-      <c r="F631" t="inlineStr"/>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -11959,7 +12367,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B632" t="inlineStr"/>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C632" t="n">
         <v>2025</v>
       </c>
@@ -11969,7 +12381,11 @@
       <c r="E632" t="n">
         <v>88</v>
       </c>
-      <c r="F632" t="inlineStr"/>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -11977,7 +12393,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B633" t="inlineStr"/>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C633" t="n">
         <v>2025</v>
       </c>
@@ -11987,7 +12407,11 @@
       <c r="E633" t="n">
         <v>63</v>
       </c>
-      <c r="F633" t="inlineStr"/>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -11995,7 +12419,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B634" t="inlineStr"/>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C634" t="n">
         <v>2025</v>
       </c>
@@ -12005,7 +12433,11 @@
       <c r="E634" t="n">
         <v>278</v>
       </c>
-      <c r="F634" t="inlineStr"/>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -12013,7 +12445,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B635" t="inlineStr"/>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C635" t="n">
         <v>2025</v>
       </c>
@@ -12023,7 +12459,11 @@
       <c r="E635" t="n">
         <v>62</v>
       </c>
-      <c r="F635" t="inlineStr"/>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -12031,7 +12471,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B636" t="inlineStr"/>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C636" t="n">
         <v>2025</v>
       </c>
@@ -12041,7 +12485,11 @@
       <c r="E636" t="n">
         <v>156</v>
       </c>
-      <c r="F636" t="inlineStr"/>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -12049,7 +12497,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B637" t="inlineStr"/>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C637" t="n">
         <v>2025</v>
       </c>
@@ -12059,7 +12511,11 @@
       <c r="E637" t="n">
         <v>112</v>
       </c>
-      <c r="F637" t="inlineStr"/>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -12067,7 +12523,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B638" t="inlineStr"/>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C638" t="n">
         <v>2026</v>
       </c>
@@ -12077,7 +12537,11 @@
       <c r="E638" t="n">
         <v>117</v>
       </c>
-      <c r="F638" t="inlineStr"/>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -12085,7 +12549,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B639" t="inlineStr"/>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C639" t="n">
         <v>2026</v>
       </c>
@@ -12095,7 +12563,11 @@
       <c r="E639" t="n">
         <v>90</v>
       </c>
-      <c r="F639" t="inlineStr"/>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -12103,7 +12575,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B640" t="inlineStr"/>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C640" t="n">
         <v>2026</v>
       </c>
@@ -12113,7 +12589,11 @@
       <c r="E640" t="n">
         <v>93</v>
       </c>
-      <c r="F640" t="inlineStr"/>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -12121,7 +12601,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B641" t="inlineStr"/>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C641" t="n">
         <v>2026</v>
       </c>
@@ -12131,7 +12615,11 @@
       <c r="E641" t="n">
         <v>101</v>
       </c>
-      <c r="F641" t="inlineStr"/>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -12139,7 +12627,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B642" t="inlineStr"/>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C642" t="n">
         <v>2026</v>
       </c>
@@ -12149,7 +12641,11 @@
       <c r="E642" t="n">
         <v>90</v>
       </c>
-      <c r="F642" t="inlineStr"/>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -12157,7 +12653,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B643" t="inlineStr"/>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C643" t="n">
         <v>2026</v>
       </c>
@@ -12167,7 +12667,11 @@
       <c r="E643" t="n">
         <v>40</v>
       </c>
-      <c r="F643" t="inlineStr"/>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -12175,7 +12679,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr"/>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C644" t="n">
         <v>2026</v>
       </c>
@@ -12185,7 +12693,11 @@
       <c r="E644" t="n">
         <v>82</v>
       </c>
-      <c r="F644" t="inlineStr"/>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -12193,7 +12705,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B645" t="inlineStr"/>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C645" t="n">
         <v>2026</v>
       </c>
@@ -12203,7 +12719,11 @@
       <c r="E645" t="n">
         <v>79</v>
       </c>
-      <c r="F645" t="inlineStr"/>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -12211,7 +12731,11 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B646" t="inlineStr"/>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C646" t="n">
         <v>2026</v>
       </c>
@@ -12221,7 +12745,11 @@
       <c r="E646" t="n">
         <v>55</v>
       </c>
-      <c r="F646" t="inlineStr"/>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -12245,7 +12773,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -12255,7 +12783,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B648" t="inlineStr"/>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C648" t="n">
         <v>2024</v>
       </c>
@@ -12265,7 +12797,11 @@
       <c r="E648" t="n">
         <v>0</v>
       </c>
-      <c r="F648" t="inlineStr"/>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -12273,7 +12809,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr"/>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C649" t="n">
         <v>2024</v>
       </c>
@@ -12283,7 +12823,11 @@
       <c r="E649" t="n">
         <v>0</v>
       </c>
-      <c r="F649" t="inlineStr"/>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -12291,7 +12835,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr"/>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C650" t="n">
         <v>2024</v>
       </c>
@@ -12301,7 +12849,11 @@
       <c r="E650" t="n">
         <v>0</v>
       </c>
-      <c r="F650" t="inlineStr"/>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -12309,7 +12861,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr"/>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C651" t="n">
         <v>2024</v>
       </c>
@@ -12319,7 +12875,11 @@
       <c r="E651" t="n">
         <v>304</v>
       </c>
-      <c r="F651" t="inlineStr"/>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -12327,7 +12887,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr"/>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C652" t="n">
         <v>2024</v>
       </c>
@@ -12337,7 +12901,11 @@
       <c r="E652" t="n">
         <v>8</v>
       </c>
-      <c r="F652" t="inlineStr"/>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -12345,7 +12913,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr"/>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C653" t="n">
         <v>2024</v>
       </c>
@@ -12355,7 +12927,11 @@
       <c r="E653" t="n">
         <v>201</v>
       </c>
-      <c r="F653" t="inlineStr"/>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -12363,7 +12939,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr"/>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C654" t="n">
         <v>2024</v>
       </c>
@@ -12373,7 +12953,11 @@
       <c r="E654" t="n">
         <v>234</v>
       </c>
-      <c r="F654" t="inlineStr"/>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -12381,7 +12965,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr"/>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C655" t="n">
         <v>2024</v>
       </c>
@@ -12391,7 +12979,11 @@
       <c r="E655" t="n">
         <v>212</v>
       </c>
-      <c r="F655" t="inlineStr"/>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -12399,7 +12991,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr"/>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C656" t="n">
         <v>2024</v>
       </c>
@@ -12409,7 +13005,11 @@
       <c r="E656" t="n">
         <v>197</v>
       </c>
-      <c r="F656" t="inlineStr"/>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -12417,7 +13017,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr"/>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C657" t="n">
         <v>2024</v>
       </c>
@@ -12427,7 +13031,11 @@
       <c r="E657" t="n">
         <v>220</v>
       </c>
-      <c r="F657" t="inlineStr"/>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -12435,7 +13043,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr"/>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C658" t="n">
         <v>2024</v>
       </c>
@@ -12445,7 +13057,11 @@
       <c r="E658" t="n">
         <v>167</v>
       </c>
-      <c r="F658" t="inlineStr"/>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -12453,7 +13069,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr"/>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C659" t="n">
         <v>2024</v>
       </c>
@@ -12463,7 +13083,11 @@
       <c r="E659" t="n">
         <v>285</v>
       </c>
-      <c r="F659" t="inlineStr"/>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -12471,7 +13095,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr"/>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C660" t="n">
         <v>2025</v>
       </c>
@@ -12481,7 +13109,11 @@
       <c r="E660" t="n">
         <v>381</v>
       </c>
-      <c r="F660" t="inlineStr"/>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -12489,7 +13121,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr"/>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C661" t="n">
         <v>2025</v>
       </c>
@@ -12499,7 +13135,11 @@
       <c r="E661" t="n">
         <v>250</v>
       </c>
-      <c r="F661" t="inlineStr"/>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -12507,7 +13147,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr"/>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C662" t="n">
         <v>2025</v>
       </c>
@@ -12517,7 +13161,11 @@
       <c r="E662" t="n">
         <v>225</v>
       </c>
-      <c r="F662" t="inlineStr"/>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -12525,7 +13173,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr"/>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C663" t="n">
         <v>2025</v>
       </c>
@@ -12535,7 +13187,11 @@
       <c r="E663" t="n">
         <v>210</v>
       </c>
-      <c r="F663" t="inlineStr"/>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -12543,7 +13199,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr"/>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C664" t="n">
         <v>2025</v>
       </c>
@@ -12553,7 +13213,11 @@
       <c r="E664" t="n">
         <v>211</v>
       </c>
-      <c r="F664" t="inlineStr"/>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -12561,7 +13225,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr"/>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C665" t="n">
         <v>2025</v>
       </c>
@@ -12571,7 +13239,11 @@
       <c r="E665" t="n">
         <v>149</v>
       </c>
-      <c r="F665" t="inlineStr"/>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -12579,7 +13251,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr"/>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C666" t="n">
         <v>2025</v>
       </c>
@@ -12589,7 +13265,11 @@
       <c r="E666" t="n">
         <v>200</v>
       </c>
-      <c r="F666" t="inlineStr"/>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -12597,7 +13277,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr"/>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C667" t="n">
         <v>2025</v>
       </c>
@@ -12607,7 +13291,11 @@
       <c r="E667" t="n">
         <v>154</v>
       </c>
-      <c r="F667" t="inlineStr"/>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -12615,7 +13303,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr"/>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C668" t="n">
         <v>2025</v>
       </c>
@@ -12625,7 +13317,11 @@
       <c r="E668" t="n">
         <v>183</v>
       </c>
-      <c r="F668" t="inlineStr"/>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -12633,7 +13329,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr"/>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C669" t="n">
         <v>2025</v>
       </c>
@@ -12643,7 +13343,11 @@
       <c r="E669" t="n">
         <v>169</v>
       </c>
-      <c r="F669" t="inlineStr"/>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -12651,7 +13355,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B670" t="inlineStr"/>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C670" t="n">
         <v>2025</v>
       </c>
@@ -12661,7 +13369,11 @@
       <c r="E670" t="n">
         <v>153</v>
       </c>
-      <c r="F670" t="inlineStr"/>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -12669,7 +13381,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr"/>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C671" t="n">
         <v>2025</v>
       </c>
@@ -12679,7 +13395,11 @@
       <c r="E671" t="n">
         <v>165</v>
       </c>
-      <c r="F671" t="inlineStr"/>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -12687,7 +13407,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr"/>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C672" t="n">
         <v>2026</v>
       </c>
@@ -12697,7 +13421,11 @@
       <c r="E672" t="n">
         <v>254</v>
       </c>
-      <c r="F672" t="inlineStr"/>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -12705,7 +13433,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B673" t="inlineStr"/>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C673" t="n">
         <v>2026</v>
       </c>
@@ -12715,7 +13447,11 @@
       <c r="E673" t="n">
         <v>145</v>
       </c>
-      <c r="F673" t="inlineStr"/>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -12723,7 +13459,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B674" t="inlineStr"/>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C674" t="n">
         <v>2026</v>
       </c>
@@ -12733,7 +13473,11 @@
       <c r="E674" t="n">
         <v>171</v>
       </c>
-      <c r="F674" t="inlineStr"/>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -12741,7 +13485,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B675" t="inlineStr"/>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C675" t="n">
         <v>2026</v>
       </c>
@@ -12751,7 +13499,11 @@
       <c r="E675" t="n">
         <v>186</v>
       </c>
-      <c r="F675" t="inlineStr"/>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -12759,7 +13511,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B676" t="inlineStr"/>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C676" t="n">
         <v>2026</v>
       </c>
@@ -12769,7 +13525,11 @@
       <c r="E676" t="n">
         <v>171</v>
       </c>
-      <c r="F676" t="inlineStr"/>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -12777,7 +13537,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B677" t="inlineStr"/>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C677" t="n">
         <v>2026</v>
       </c>
@@ -12787,7 +13551,11 @@
       <c r="E677" t="n">
         <v>185</v>
       </c>
-      <c r="F677" t="inlineStr"/>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -12795,7 +13563,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B678" t="inlineStr"/>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C678" t="n">
         <v>2026</v>
       </c>
@@ -12805,7 +13577,11 @@
       <c r="E678" t="n">
         <v>251</v>
       </c>
-      <c r="F678" t="inlineStr"/>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -12813,7 +13589,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B679" t="inlineStr"/>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C679" t="n">
         <v>2026</v>
       </c>
@@ -12823,7 +13603,11 @@
       <c r="E679" t="n">
         <v>203</v>
       </c>
-      <c r="F679" t="inlineStr"/>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -12831,7 +13615,11 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr"/>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C680" t="n">
         <v>2026</v>
       </c>
@@ -12841,7 +13629,11 @@
       <c r="E680" t="n">
         <v>162</v>
       </c>
-      <c r="F680" t="inlineStr"/>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -12865,7 +13657,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -12875,7 +13667,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr"/>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C682" t="n">
         <v>2024</v>
       </c>
@@ -12885,7 +13681,11 @@
       <c r="E682" t="n">
         <v>156</v>
       </c>
-      <c r="F682" t="inlineStr"/>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -12893,7 +13693,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr"/>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C683" t="n">
         <v>2024</v>
       </c>
@@ -12903,7 +13707,11 @@
       <c r="E683" t="n">
         <v>94</v>
       </c>
-      <c r="F683" t="inlineStr"/>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -12911,7 +13719,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B684" t="inlineStr"/>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C684" t="n">
         <v>2024</v>
       </c>
@@ -12921,7 +13733,11 @@
       <c r="E684" t="n">
         <v>113</v>
       </c>
-      <c r="F684" t="inlineStr"/>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -12929,7 +13745,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr"/>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C685" t="n">
         <v>2024</v>
       </c>
@@ -12939,7 +13759,11 @@
       <c r="E685" t="n">
         <v>94</v>
       </c>
-      <c r="F685" t="inlineStr"/>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -12947,7 +13771,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr"/>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C686" t="n">
         <v>2024</v>
       </c>
@@ -12957,7 +13785,11 @@
       <c r="E686" t="n">
         <v>87</v>
       </c>
-      <c r="F686" t="inlineStr"/>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -12965,7 +13797,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B687" t="inlineStr"/>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C687" t="n">
         <v>2024</v>
       </c>
@@ -12975,7 +13811,11 @@
       <c r="E687" t="n">
         <v>85</v>
       </c>
-      <c r="F687" t="inlineStr"/>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -12983,7 +13823,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B688" t="inlineStr"/>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C688" t="n">
         <v>2024</v>
       </c>
@@ -12993,7 +13837,11 @@
       <c r="E688" t="n">
         <v>60</v>
       </c>
-      <c r="F688" t="inlineStr"/>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -13001,7 +13849,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B689" t="inlineStr"/>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C689" t="n">
         <v>2024</v>
       </c>
@@ -13011,7 +13863,11 @@
       <c r="E689" t="n">
         <v>92</v>
       </c>
-      <c r="F689" t="inlineStr"/>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -13019,7 +13875,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B690" t="inlineStr"/>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C690" t="n">
         <v>2024</v>
       </c>
@@ -13029,7 +13889,11 @@
       <c r="E690" t="n">
         <v>95</v>
       </c>
-      <c r="F690" t="inlineStr"/>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -13037,7 +13901,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B691" t="inlineStr"/>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C691" t="n">
         <v>2024</v>
       </c>
@@ -13047,7 +13915,11 @@
       <c r="E691" t="n">
         <v>106</v>
       </c>
-      <c r="F691" t="inlineStr"/>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -13055,7 +13927,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B692" t="inlineStr"/>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C692" t="n">
         <v>2024</v>
       </c>
@@ -13065,7 +13941,11 @@
       <c r="E692" t="n">
         <v>68</v>
       </c>
-      <c r="F692" t="inlineStr"/>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -13073,7 +13953,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B693" t="inlineStr"/>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C693" t="n">
         <v>2024</v>
       </c>
@@ -13083,7 +13967,11 @@
       <c r="E693" t="n">
         <v>116</v>
       </c>
-      <c r="F693" t="inlineStr"/>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -13091,7 +13979,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B694" t="inlineStr"/>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C694" t="n">
         <v>2025</v>
       </c>
@@ -13101,7 +13993,11 @@
       <c r="E694" t="n">
         <v>210</v>
       </c>
-      <c r="F694" t="inlineStr"/>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -13109,7 +14005,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B695" t="inlineStr"/>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C695" t="n">
         <v>2025</v>
       </c>
@@ -13119,7 +14019,11 @@
       <c r="E695" t="n">
         <v>144</v>
       </c>
-      <c r="F695" t="inlineStr"/>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -13127,7 +14031,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr"/>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C696" t="n">
         <v>2025</v>
       </c>
@@ -13137,7 +14045,11 @@
       <c r="E696" t="n">
         <v>131</v>
       </c>
-      <c r="F696" t="inlineStr"/>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -13145,7 +14057,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B697" t="inlineStr"/>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C697" t="n">
         <v>2025</v>
       </c>
@@ -13155,7 +14071,11 @@
       <c r="E697" t="n">
         <v>101</v>
       </c>
-      <c r="F697" t="inlineStr"/>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -13163,7 +14083,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr"/>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C698" t="n">
         <v>2025</v>
       </c>
@@ -13173,7 +14097,11 @@
       <c r="E698" t="n">
         <v>133</v>
       </c>
-      <c r="F698" t="inlineStr"/>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -13181,7 +14109,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr"/>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C699" t="n">
         <v>2025</v>
       </c>
@@ -13191,7 +14123,11 @@
       <c r="E699" t="n">
         <v>89</v>
       </c>
-      <c r="F699" t="inlineStr"/>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -13199,7 +14135,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr"/>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C700" t="n">
         <v>2025</v>
       </c>
@@ -13209,7 +14149,11 @@
       <c r="E700" t="n">
         <v>90</v>
       </c>
-      <c r="F700" t="inlineStr"/>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -13217,7 +14161,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr"/>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C701" t="n">
         <v>2025</v>
       </c>
@@ -13227,7 +14175,11 @@
       <c r="E701" t="n">
         <v>148</v>
       </c>
-      <c r="F701" t="inlineStr"/>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -13235,7 +14187,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr"/>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C702" t="n">
         <v>2025</v>
       </c>
@@ -13245,7 +14201,11 @@
       <c r="E702" t="n">
         <v>102</v>
       </c>
-      <c r="F702" t="inlineStr"/>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -13253,7 +14213,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C703" t="n">
         <v>2025</v>
       </c>
@@ -13263,7 +14227,11 @@
       <c r="E703" t="n">
         <v>101</v>
       </c>
-      <c r="F703" t="inlineStr"/>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -13271,7 +14239,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr"/>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C704" t="n">
         <v>2025</v>
       </c>
@@ -13281,7 +14253,11 @@
       <c r="E704" t="n">
         <v>79</v>
       </c>
-      <c r="F704" t="inlineStr"/>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -13289,7 +14265,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr"/>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C705" t="n">
         <v>2025</v>
       </c>
@@ -13299,7 +14279,11 @@
       <c r="E705" t="n">
         <v>106</v>
       </c>
-      <c r="F705" t="inlineStr"/>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -13307,7 +14291,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr"/>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C706" t="n">
         <v>2026</v>
       </c>
@@ -13317,7 +14305,11 @@
       <c r="E706" t="n">
         <v>173</v>
       </c>
-      <c r="F706" t="inlineStr"/>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -13325,7 +14317,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr"/>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C707" t="n">
         <v>2026</v>
       </c>
@@ -13335,7 +14331,11 @@
       <c r="E707" t="n">
         <v>98</v>
       </c>
-      <c r="F707" t="inlineStr"/>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -13343,7 +14343,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B708" t="inlineStr"/>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C708" t="n">
         <v>2026</v>
       </c>
@@ -13353,7 +14357,11 @@
       <c r="E708" t="n">
         <v>114</v>
       </c>
-      <c r="F708" t="inlineStr"/>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -13361,7 +14369,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr"/>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C709" t="n">
         <v>2026</v>
       </c>
@@ -13371,7 +14383,11 @@
       <c r="E709" t="n">
         <v>85</v>
       </c>
-      <c r="F709" t="inlineStr"/>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -13379,7 +14395,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B710" t="inlineStr"/>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C710" t="n">
         <v>2026</v>
       </c>
@@ -13389,7 +14409,11 @@
       <c r="E710" t="n">
         <v>78</v>
       </c>
-      <c r="F710" t="inlineStr"/>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -13397,7 +14421,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr"/>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C711" t="n">
         <v>2026</v>
       </c>
@@ -13407,7 +14435,11 @@
       <c r="E711" t="n">
         <v>82</v>
       </c>
-      <c r="F711" t="inlineStr"/>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -13415,7 +14447,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B712" t="inlineStr"/>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C712" t="n">
         <v>2026</v>
       </c>
@@ -13425,7 +14461,11 @@
       <c r="E712" t="n">
         <v>123</v>
       </c>
-      <c r="F712" t="inlineStr"/>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -13433,7 +14473,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr"/>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C713" t="n">
         <v>2026</v>
       </c>
@@ -13443,7 +14487,11 @@
       <c r="E713" t="n">
         <v>110</v>
       </c>
-      <c r="F713" t="inlineStr"/>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -13451,7 +14499,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr"/>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C714" t="n">
         <v>2026</v>
       </c>
@@ -13461,7 +14513,11 @@
       <c r="E714" t="n">
         <v>85</v>
       </c>
-      <c r="F714" t="inlineStr"/>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -13485,7 +14541,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -14101,11 +15157,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -14721,11 +15777,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -15341,11 +16397,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-22 11:46</t>
+          <t>2026-10-23 11:33</t>
         </is>
       </c>
     </row>
@@ -15584,106 +16640,106 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>449</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="AI2" t="n">
-        <v>725</v>
+        <v>735</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +16848,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>683</v>
+        <v>723</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +16957,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +17066,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>413</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +17175,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2244</v>
+        <v>2326</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -475,7 +475,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>2024</v>
       </c>
@@ -485,7 +489,11 @@
       <c r="E2" t="n">
         <v>238</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,7 +501,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C3" t="n">
         <v>2024</v>
       </c>
@@ -503,7 +515,11 @@
       <c r="E3" t="n">
         <v>158</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,7 +527,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2024</v>
       </c>
@@ -521,7 +541,11 @@
       <c r="E4" t="n">
         <v>135</v>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -529,7 +553,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C5" t="n">
         <v>2024</v>
       </c>
@@ -539,7 +567,11 @@
       <c r="E5" t="n">
         <v>107</v>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -547,7 +579,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C6" t="n">
         <v>2024</v>
       </c>
@@ -557,7 +593,11 @@
       <c r="E6" t="n">
         <v>50</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -565,7 +605,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C7" t="n">
         <v>2024</v>
       </c>
@@ -575,7 +619,11 @@
       <c r="E7" t="n">
         <v>227</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -583,7 +631,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C8" t="n">
         <v>2024</v>
       </c>
@@ -593,7 +645,11 @@
       <c r="E8" t="n">
         <v>115</v>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -601,7 +657,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C9" t="n">
         <v>2024</v>
       </c>
@@ -611,7 +671,11 @@
       <c r="E9" t="n">
         <v>223</v>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -619,7 +683,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C10" t="n">
         <v>2024</v>
       </c>
@@ -629,7 +697,11 @@
       <c r="E10" t="n">
         <v>224</v>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -637,7 +709,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C11" t="n">
         <v>2024</v>
       </c>
@@ -647,7 +723,11 @@
       <c r="E11" t="n">
         <v>204</v>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -655,7 +735,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C12" t="n">
         <v>2024</v>
       </c>
@@ -665,7 +749,11 @@
       <c r="E12" t="n">
         <v>173</v>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -673,7 +761,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C13" t="n">
         <v>2024</v>
       </c>
@@ -683,7 +775,11 @@
       <c r="E13" t="n">
         <v>264</v>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -691,7 +787,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C14" t="n">
         <v>2025</v>
       </c>
@@ -701,7 +801,11 @@
       <c r="E14" t="n">
         <v>371</v>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -709,7 +813,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C15" t="n">
         <v>2025</v>
       </c>
@@ -719,7 +827,11 @@
       <c r="E15" t="n">
         <v>371</v>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -727,7 +839,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C16" t="n">
         <v>2025</v>
       </c>
@@ -737,7 +853,11 @@
       <c r="E16" t="n">
         <v>227</v>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -745,7 +865,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C17" t="n">
         <v>2025</v>
       </c>
@@ -755,7 +879,11 @@
       <c r="E17" t="n">
         <v>232</v>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -763,7 +891,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C18" t="n">
         <v>2025</v>
       </c>
@@ -773,7 +905,11 @@
       <c r="E18" t="n">
         <v>261</v>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -781,7 +917,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C19" t="n">
         <v>2025</v>
       </c>
@@ -791,7 +931,11 @@
       <c r="E19" t="n">
         <v>129</v>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -799,7 +943,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C20" t="n">
         <v>2025</v>
       </c>
@@ -809,7 +957,11 @@
       <c r="E20" t="n">
         <v>186</v>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -817,7 +969,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C21" t="n">
         <v>2025</v>
       </c>
@@ -827,7 +983,11 @@
       <c r="E21" t="n">
         <v>194</v>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -835,7 +995,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C22" t="n">
         <v>2025</v>
       </c>
@@ -845,7 +1009,11 @@
       <c r="E22" t="n">
         <v>195</v>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -853,7 +1021,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C23" t="n">
         <v>2025</v>
       </c>
@@ -863,7 +1035,11 @@
       <c r="E23" t="n">
         <v>175</v>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -871,7 +1047,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C24" t="n">
         <v>2025</v>
       </c>
@@ -881,7 +1061,11 @@
       <c r="E24" t="n">
         <v>178</v>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -889,7 +1073,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C25" t="n">
         <v>2025</v>
       </c>
@@ -899,7 +1087,11 @@
       <c r="E25" t="n">
         <v>152</v>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -907,7 +1099,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C26" t="n">
         <v>2026</v>
       </c>
@@ -917,7 +1113,11 @@
       <c r="E26" t="n">
         <v>250</v>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -925,7 +1125,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C27" t="n">
         <v>2026</v>
       </c>
@@ -935,7 +1139,11 @@
       <c r="E27" t="n">
         <v>157</v>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -943,7 +1151,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C28" t="n">
         <v>2026</v>
       </c>
@@ -953,7 +1165,11 @@
       <c r="E28" t="n">
         <v>216</v>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -961,7 +1177,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C29" t="n">
         <v>2026</v>
       </c>
@@ -971,7 +1191,11 @@
       <c r="E29" t="n">
         <v>182</v>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -979,7 +1203,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C30" t="n">
         <v>2026</v>
       </c>
@@ -989,7 +1217,11 @@
       <c r="E30" t="n">
         <v>212</v>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -997,7 +1229,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C31" t="n">
         <v>2026</v>
       </c>
@@ -1007,7 +1243,11 @@
       <c r="E31" t="n">
         <v>202</v>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1015,7 +1255,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C32" t="n">
         <v>2026</v>
       </c>
@@ -1025,7 +1269,11 @@
       <c r="E32" t="n">
         <v>261</v>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1033,7 +1281,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C33" t="n">
         <v>2026</v>
       </c>
@@ -1043,7 +1295,11 @@
       <c r="E33" t="n">
         <v>224</v>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1051,7 +1307,11 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C34" t="n">
         <v>2026</v>
       </c>
@@ -1061,7 +1321,11 @@
       <c r="E34" t="n">
         <v>180</v>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1085,7 +1349,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1965,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2585,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -2945,7 +3209,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3825,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4445,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -4801,11 +5065,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5685,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5715,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5741,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5767,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5793,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5819,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5845,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5871,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5897,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5923,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5949,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5975,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5737,7 +6001,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5763,7 +6027,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5789,7 +6053,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5815,7 +6079,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5841,7 +6105,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5867,7 +6131,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5893,7 +6157,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5919,7 +6183,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5945,7 +6209,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5971,7 +6235,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -5997,7 +6261,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6287,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6313,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6339,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6365,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6391,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6417,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6443,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6469,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6495,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6521,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6547,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6573,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -6925,11 +7189,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -7545,11 +7809,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -8165,11 +8429,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -8785,11 +9049,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -9405,11 +9669,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -10025,11 +10289,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -10645,11 +10909,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -11265,11 +11529,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -11885,11 +12149,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -11915,7 +12179,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -11941,7 +12205,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -11967,7 +12231,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -11993,7 +12257,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12019,7 +12283,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12309,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12071,7 +12335,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12097,7 +12361,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12123,7 +12387,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12413,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12439,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12465,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12491,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12253,7 +12517,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12543,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12569,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12595,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12357,7 +12621,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12647,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12673,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12699,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12725,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12751,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12777,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12803,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12565,7 +12829,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12855,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12617,7 +12881,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12643,7 +12907,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12933,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12959,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12721,7 +12985,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12747,7 +13011,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12773,7 +13037,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -12783,11 +13047,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B648" t="inlineStr"/>
       <c r="C648" t="n">
         <v>2024</v>
       </c>
@@ -12797,11 +13057,7 @@
       <c r="E648" t="n">
         <v>0</v>
       </c>
-      <c r="F648" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -12809,11 +13065,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B649" t="inlineStr"/>
       <c r="C649" t="n">
         <v>2024</v>
       </c>
@@ -12823,11 +13075,7 @@
       <c r="E649" t="n">
         <v>0</v>
       </c>
-      <c r="F649" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -12835,11 +13083,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B650" t="inlineStr"/>
       <c r="C650" t="n">
         <v>2024</v>
       </c>
@@ -12849,11 +13093,7 @@
       <c r="E650" t="n">
         <v>0</v>
       </c>
-      <c r="F650" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -12861,11 +13101,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B651" t="inlineStr"/>
       <c r="C651" t="n">
         <v>2024</v>
       </c>
@@ -12875,11 +13111,7 @@
       <c r="E651" t="n">
         <v>304</v>
       </c>
-      <c r="F651" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -12887,11 +13119,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B652" t="inlineStr"/>
       <c r="C652" t="n">
         <v>2024</v>
       </c>
@@ -12901,11 +13129,7 @@
       <c r="E652" t="n">
         <v>8</v>
       </c>
-      <c r="F652" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -12913,11 +13137,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B653" t="inlineStr"/>
       <c r="C653" t="n">
         <v>2024</v>
       </c>
@@ -12927,11 +13147,7 @@
       <c r="E653" t="n">
         <v>201</v>
       </c>
-      <c r="F653" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -12939,11 +13155,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B654" t="inlineStr"/>
       <c r="C654" t="n">
         <v>2024</v>
       </c>
@@ -12953,11 +13165,7 @@
       <c r="E654" t="n">
         <v>234</v>
       </c>
-      <c r="F654" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -12965,11 +13173,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B655" t="inlineStr"/>
       <c r="C655" t="n">
         <v>2024</v>
       </c>
@@ -12979,11 +13183,7 @@
       <c r="E655" t="n">
         <v>212</v>
       </c>
-      <c r="F655" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -12991,11 +13191,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B656" t="inlineStr"/>
       <c r="C656" t="n">
         <v>2024</v>
       </c>
@@ -13005,11 +13201,7 @@
       <c r="E656" t="n">
         <v>197</v>
       </c>
-      <c r="F656" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -13017,11 +13209,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B657" t="inlineStr"/>
       <c r="C657" t="n">
         <v>2024</v>
       </c>
@@ -13031,11 +13219,7 @@
       <c r="E657" t="n">
         <v>220</v>
       </c>
-      <c r="F657" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -13043,11 +13227,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B658" t="inlineStr"/>
       <c r="C658" t="n">
         <v>2024</v>
       </c>
@@ -13057,11 +13237,7 @@
       <c r="E658" t="n">
         <v>167</v>
       </c>
-      <c r="F658" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -13069,11 +13245,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B659" t="inlineStr"/>
       <c r="C659" t="n">
         <v>2024</v>
       </c>
@@ -13083,11 +13255,7 @@
       <c r="E659" t="n">
         <v>285</v>
       </c>
-      <c r="F659" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -13095,11 +13263,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B660" t="inlineStr"/>
       <c r="C660" t="n">
         <v>2025</v>
       </c>
@@ -13109,11 +13273,7 @@
       <c r="E660" t="n">
         <v>381</v>
       </c>
-      <c r="F660" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -13121,11 +13281,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B661" t="inlineStr"/>
       <c r="C661" t="n">
         <v>2025</v>
       </c>
@@ -13135,11 +13291,7 @@
       <c r="E661" t="n">
         <v>250</v>
       </c>
-      <c r="F661" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -13147,11 +13299,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B662" t="inlineStr"/>
       <c r="C662" t="n">
         <v>2025</v>
       </c>
@@ -13161,11 +13309,7 @@
       <c r="E662" t="n">
         <v>225</v>
       </c>
-      <c r="F662" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -13173,11 +13317,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B663" t="inlineStr"/>
       <c r="C663" t="n">
         <v>2025</v>
       </c>
@@ -13187,11 +13327,7 @@
       <c r="E663" t="n">
         <v>210</v>
       </c>
-      <c r="F663" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -13199,11 +13335,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B664" t="inlineStr"/>
       <c r="C664" t="n">
         <v>2025</v>
       </c>
@@ -13213,11 +13345,7 @@
       <c r="E664" t="n">
         <v>211</v>
       </c>
-      <c r="F664" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -13225,11 +13353,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B665" t="inlineStr"/>
       <c r="C665" t="n">
         <v>2025</v>
       </c>
@@ -13239,11 +13363,7 @@
       <c r="E665" t="n">
         <v>149</v>
       </c>
-      <c r="F665" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -13251,11 +13371,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B666" t="inlineStr"/>
       <c r="C666" t="n">
         <v>2025</v>
       </c>
@@ -13265,11 +13381,7 @@
       <c r="E666" t="n">
         <v>200</v>
       </c>
-      <c r="F666" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -13277,11 +13389,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B667" t="inlineStr"/>
       <c r="C667" t="n">
         <v>2025</v>
       </c>
@@ -13291,11 +13399,7 @@
       <c r="E667" t="n">
         <v>154</v>
       </c>
-      <c r="F667" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -13303,11 +13407,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B668" t="inlineStr"/>
       <c r="C668" t="n">
         <v>2025</v>
       </c>
@@ -13317,11 +13417,7 @@
       <c r="E668" t="n">
         <v>183</v>
       </c>
-      <c r="F668" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -13329,11 +13425,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B669" t="inlineStr"/>
       <c r="C669" t="n">
         <v>2025</v>
       </c>
@@ -13343,11 +13435,7 @@
       <c r="E669" t="n">
         <v>169</v>
       </c>
-      <c r="F669" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -13355,11 +13443,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B670" t="inlineStr"/>
       <c r="C670" t="n">
         <v>2025</v>
       </c>
@@ -13369,11 +13453,7 @@
       <c r="E670" t="n">
         <v>153</v>
       </c>
-      <c r="F670" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -13381,11 +13461,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B671" t="inlineStr"/>
       <c r="C671" t="n">
         <v>2025</v>
       </c>
@@ -13395,11 +13471,7 @@
       <c r="E671" t="n">
         <v>165</v>
       </c>
-      <c r="F671" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -13407,11 +13479,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B672" t="inlineStr"/>
       <c r="C672" t="n">
         <v>2026</v>
       </c>
@@ -13421,11 +13489,7 @@
       <c r="E672" t="n">
         <v>254</v>
       </c>
-      <c r="F672" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -13433,11 +13497,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B673" t="inlineStr"/>
       <c r="C673" t="n">
         <v>2026</v>
       </c>
@@ -13447,11 +13507,7 @@
       <c r="E673" t="n">
         <v>145</v>
       </c>
-      <c r="F673" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -13459,11 +13515,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B674" t="inlineStr"/>
       <c r="C674" t="n">
         <v>2026</v>
       </c>
@@ -13473,11 +13525,7 @@
       <c r="E674" t="n">
         <v>171</v>
       </c>
-      <c r="F674" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -13485,11 +13533,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B675" t="inlineStr"/>
       <c r="C675" t="n">
         <v>2026</v>
       </c>
@@ -13499,11 +13543,7 @@
       <c r="E675" t="n">
         <v>186</v>
       </c>
-      <c r="F675" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -13511,11 +13551,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B676" t="inlineStr"/>
       <c r="C676" t="n">
         <v>2026</v>
       </c>
@@ -13525,11 +13561,7 @@
       <c r="E676" t="n">
         <v>171</v>
       </c>
-      <c r="F676" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -13537,11 +13569,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B677" t="inlineStr"/>
       <c r="C677" t="n">
         <v>2026</v>
       </c>
@@ -13551,11 +13579,7 @@
       <c r="E677" t="n">
         <v>185</v>
       </c>
-      <c r="F677" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -13563,11 +13587,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B678" t="inlineStr"/>
       <c r="C678" t="n">
         <v>2026</v>
       </c>
@@ -13577,11 +13597,7 @@
       <c r="E678" t="n">
         <v>251</v>
       </c>
-      <c r="F678" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -13589,11 +13605,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B679" t="inlineStr"/>
       <c r="C679" t="n">
         <v>2026</v>
       </c>
@@ -13603,11 +13615,7 @@
       <c r="E679" t="n">
         <v>203</v>
       </c>
-      <c r="F679" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -13615,11 +13623,7 @@
           <t>Riomar</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B680" t="inlineStr"/>
       <c r="C680" t="n">
         <v>2026</v>
       </c>
@@ -13629,11 +13633,7 @@
       <c r="E680" t="n">
         <v>162</v>
       </c>
-      <c r="F680" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -13653,11 +13653,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -13667,11 +13667,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B682" t="inlineStr"/>
       <c r="C682" t="n">
         <v>2024</v>
       </c>
@@ -13681,11 +13677,7 @@
       <c r="E682" t="n">
         <v>156</v>
       </c>
-      <c r="F682" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -13693,11 +13685,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B683" t="inlineStr"/>
       <c r="C683" t="n">
         <v>2024</v>
       </c>
@@ -13707,11 +13695,7 @@
       <c r="E683" t="n">
         <v>94</v>
       </c>
-      <c r="F683" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -13719,11 +13703,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B684" t="inlineStr"/>
       <c r="C684" t="n">
         <v>2024</v>
       </c>
@@ -13733,11 +13713,7 @@
       <c r="E684" t="n">
         <v>113</v>
       </c>
-      <c r="F684" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -13745,11 +13721,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B685" t="inlineStr"/>
       <c r="C685" t="n">
         <v>2024</v>
       </c>
@@ -13759,11 +13731,7 @@
       <c r="E685" t="n">
         <v>94</v>
       </c>
-      <c r="F685" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -13771,11 +13739,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B686" t="inlineStr"/>
       <c r="C686" t="n">
         <v>2024</v>
       </c>
@@ -13785,11 +13749,7 @@
       <c r="E686" t="n">
         <v>87</v>
       </c>
-      <c r="F686" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -13797,11 +13757,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B687" t="inlineStr"/>
       <c r="C687" t="n">
         <v>2024</v>
       </c>
@@ -13811,11 +13767,7 @@
       <c r="E687" t="n">
         <v>85</v>
       </c>
-      <c r="F687" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -13823,11 +13775,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B688" t="inlineStr"/>
       <c r="C688" t="n">
         <v>2024</v>
       </c>
@@ -13837,11 +13785,7 @@
       <c r="E688" t="n">
         <v>60</v>
       </c>
-      <c r="F688" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -13849,11 +13793,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B689" t="inlineStr"/>
       <c r="C689" t="n">
         <v>2024</v>
       </c>
@@ -13863,11 +13803,7 @@
       <c r="E689" t="n">
         <v>92</v>
       </c>
-      <c r="F689" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -13875,11 +13811,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B690" t="inlineStr"/>
       <c r="C690" t="n">
         <v>2024</v>
       </c>
@@ -13889,11 +13821,7 @@
       <c r="E690" t="n">
         <v>95</v>
       </c>
-      <c r="F690" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -13901,11 +13829,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B691" t="inlineStr"/>
       <c r="C691" t="n">
         <v>2024</v>
       </c>
@@ -13915,11 +13839,7 @@
       <c r="E691" t="n">
         <v>106</v>
       </c>
-      <c r="F691" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -13927,11 +13847,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B692" t="inlineStr"/>
       <c r="C692" t="n">
         <v>2024</v>
       </c>
@@ -13941,11 +13857,7 @@
       <c r="E692" t="n">
         <v>68</v>
       </c>
-      <c r="F692" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -13953,11 +13865,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B693" t="inlineStr"/>
       <c r="C693" t="n">
         <v>2024</v>
       </c>
@@ -13967,11 +13875,7 @@
       <c r="E693" t="n">
         <v>116</v>
       </c>
-      <c r="F693" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -13979,11 +13883,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B694" t="inlineStr"/>
       <c r="C694" t="n">
         <v>2025</v>
       </c>
@@ -13993,11 +13893,7 @@
       <c r="E694" t="n">
         <v>210</v>
       </c>
-      <c r="F694" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -14005,11 +13901,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B695" t="inlineStr"/>
       <c r="C695" t="n">
         <v>2025</v>
       </c>
@@ -14019,11 +13911,7 @@
       <c r="E695" t="n">
         <v>144</v>
       </c>
-      <c r="F695" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -14031,11 +13919,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B696" t="inlineStr"/>
       <c r="C696" t="n">
         <v>2025</v>
       </c>
@@ -14045,11 +13929,7 @@
       <c r="E696" t="n">
         <v>131</v>
       </c>
-      <c r="F696" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -14057,11 +13937,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B697" t="inlineStr"/>
       <c r="C697" t="n">
         <v>2025</v>
       </c>
@@ -14071,11 +13947,7 @@
       <c r="E697" t="n">
         <v>101</v>
       </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -14083,11 +13955,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B698" t="inlineStr"/>
       <c r="C698" t="n">
         <v>2025</v>
       </c>
@@ -14097,11 +13965,7 @@
       <c r="E698" t="n">
         <v>133</v>
       </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -14109,11 +13973,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B699" t="inlineStr"/>
       <c r="C699" t="n">
         <v>2025</v>
       </c>
@@ -14123,11 +13983,7 @@
       <c r="E699" t="n">
         <v>89</v>
       </c>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -14135,11 +13991,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B700" t="inlineStr"/>
       <c r="C700" t="n">
         <v>2025</v>
       </c>
@@ -14149,11 +14001,7 @@
       <c r="E700" t="n">
         <v>90</v>
       </c>
-      <c r="F700" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -14161,11 +14009,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B701" t="inlineStr"/>
       <c r="C701" t="n">
         <v>2025</v>
       </c>
@@ -14175,11 +14019,7 @@
       <c r="E701" t="n">
         <v>148</v>
       </c>
-      <c r="F701" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -14187,11 +14027,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B702" t="inlineStr"/>
       <c r="C702" t="n">
         <v>2025</v>
       </c>
@@ -14201,11 +14037,7 @@
       <c r="E702" t="n">
         <v>102</v>
       </c>
-      <c r="F702" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -14213,11 +14045,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B703" t="inlineStr"/>
       <c r="C703" t="n">
         <v>2025</v>
       </c>
@@ -14227,11 +14055,7 @@
       <c r="E703" t="n">
         <v>101</v>
       </c>
-      <c r="F703" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -14239,11 +14063,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B704" t="inlineStr"/>
       <c r="C704" t="n">
         <v>2025</v>
       </c>
@@ -14253,11 +14073,7 @@
       <c r="E704" t="n">
         <v>79</v>
       </c>
-      <c r="F704" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -14265,11 +14081,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B705" t="inlineStr"/>
       <c r="C705" t="n">
         <v>2025</v>
       </c>
@@ -14279,11 +14091,7 @@
       <c r="E705" t="n">
         <v>106</v>
       </c>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -14291,11 +14099,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B706" t="inlineStr"/>
       <c r="C706" t="n">
         <v>2026</v>
       </c>
@@ -14305,11 +14109,7 @@
       <c r="E706" t="n">
         <v>173</v>
       </c>
-      <c r="F706" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -14317,11 +14117,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B707" t="inlineStr"/>
       <c r="C707" t="n">
         <v>2026</v>
       </c>
@@ -14331,11 +14127,7 @@
       <c r="E707" t="n">
         <v>98</v>
       </c>
-      <c r="F707" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -14343,11 +14135,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B708" t="inlineStr"/>
       <c r="C708" t="n">
         <v>2026</v>
       </c>
@@ -14357,11 +14145,7 @@
       <c r="E708" t="n">
         <v>114</v>
       </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -14369,11 +14153,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B709" t="inlineStr"/>
       <c r="C709" t="n">
         <v>2026</v>
       </c>
@@ -14383,11 +14163,7 @@
       <c r="E709" t="n">
         <v>85</v>
       </c>
-      <c r="F709" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -14395,11 +14171,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B710" t="inlineStr"/>
       <c r="C710" t="n">
         <v>2026</v>
       </c>
@@ -14409,11 +14181,7 @@
       <c r="E710" t="n">
         <v>78</v>
       </c>
-      <c r="F710" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -14421,11 +14189,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B711" t="inlineStr"/>
       <c r="C711" t="n">
         <v>2026</v>
       </c>
@@ -14435,11 +14199,7 @@
       <c r="E711" t="n">
         <v>82</v>
       </c>
-      <c r="F711" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -14447,11 +14207,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B712" t="inlineStr"/>
       <c r="C712" t="n">
         <v>2026</v>
       </c>
@@ -14461,11 +14217,7 @@
       <c r="E712" t="n">
         <v>123</v>
       </c>
-      <c r="F712" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -14473,11 +14225,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B713" t="inlineStr"/>
       <c r="C713" t="n">
         <v>2026</v>
       </c>
@@ -14487,11 +14235,7 @@
       <c r="E713" t="n">
         <v>110</v>
       </c>
-      <c r="F713" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -14499,11 +14243,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B714" t="inlineStr"/>
       <c r="C714" t="n">
         <v>2026</v>
       </c>
@@ -14513,11 +14253,7 @@
       <c r="E714" t="n">
         <v>85</v>
       </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:33</t>
-        </is>
-      </c>
+      <c r="F714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -14537,11 +14273,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -15157,11 +14893,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -15777,11 +15513,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16137,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-23 11:33</t>
+          <t>2026-10-24 10:42</t>
         </is>
       </c>
     </row>
@@ -16640,106 +16376,106 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>320</v>
+        <v>402</v>
       </c>
       <c r="C2" t="n">
-        <v>254</v>
+        <v>318</v>
       </c>
       <c r="D2" t="n">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E2" t="n">
-        <v>486</v>
+        <v>195</v>
       </c>
       <c r="F2" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="H2" t="n">
-        <v>361</v>
+        <v>182</v>
       </c>
       <c r="I2" t="n">
-        <v>428</v>
+        <v>347</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="K2" t="n">
-        <v>449</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>342</v>
+        <v>280</v>
       </c>
       <c r="M2" t="n">
-        <v>578</v>
+        <v>441</v>
       </c>
       <c r="N2" t="n">
-        <v>877</v>
+        <v>657</v>
       </c>
       <c r="O2" t="n">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="P2" t="n">
-        <v>539</v>
+        <v>410</v>
       </c>
       <c r="Q2" t="n">
-        <v>465</v>
+        <v>386</v>
       </c>
       <c r="R2" t="n">
-        <v>507</v>
+        <v>424</v>
       </c>
       <c r="S2" t="n">
-        <v>388</v>
+        <v>279</v>
       </c>
       <c r="T2" t="n">
-        <v>458</v>
+        <v>354</v>
       </c>
       <c r="U2" t="n">
-        <v>472</v>
+        <v>364</v>
       </c>
       <c r="V2" t="n">
-        <v>649</v>
+        <v>559</v>
       </c>
       <c r="W2" t="n">
-        <v>417</v>
+        <v>322</v>
       </c>
       <c r="X2" t="n">
-        <v>469</v>
+        <v>415</v>
       </c>
       <c r="Y2" t="n">
-        <v>460</v>
+        <v>341</v>
       </c>
       <c r="Z2" t="n">
-        <v>650</v>
+        <v>473</v>
       </c>
       <c r="AA2" t="n">
+        <v>334</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>402</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>370</v>
+      </c>
+      <c r="AD2" t="n">
         <v>420</v>
       </c>
-      <c r="AB2" t="n">
-        <v>471</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>459</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>457</v>
-      </c>
       <c r="AE2" t="n">
-        <v>398</v>
+        <v>333</v>
       </c>
       <c r="AF2" t="n">
-        <v>588</v>
+        <v>475</v>
       </c>
       <c r="AG2" t="n">
-        <v>472</v>
+        <v>383</v>
       </c>
       <c r="AH2" t="n">
-        <v>372</v>
+        <v>305</v>
       </c>
       <c r="AI2" t="n">
-        <v>735</v>
+        <v>758</v>
       </c>
     </row>
     <row r="3">
@@ -16848,7 +16584,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>723</v>
+        <v>744</v>
       </c>
     </row>
     <row r="4">
@@ -16957,7 +16693,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>437</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5">
@@ -17066,7 +16802,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>431</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6">
@@ -17175,7 +16911,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2326</v>
+        <v>2405</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -475,11 +475,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>2024</v>
       </c>
@@ -489,11 +485,7 @@
       <c r="E2" t="n">
         <v>238</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -501,11 +493,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2024</v>
       </c>
@@ -515,11 +503,7 @@
       <c r="E3" t="n">
         <v>158</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -527,11 +511,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>2024</v>
       </c>
@@ -541,11 +521,7 @@
       <c r="E4" t="n">
         <v>135</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -553,11 +529,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>2024</v>
       </c>
@@ -567,11 +539,7 @@
       <c r="E5" t="n">
         <v>107</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -579,11 +547,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>2024</v>
       </c>
@@ -593,11 +557,7 @@
       <c r="E6" t="n">
         <v>50</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -605,11 +565,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>2024</v>
       </c>
@@ -619,11 +575,7 @@
       <c r="E7" t="n">
         <v>227</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,11 +583,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>2024</v>
       </c>
@@ -645,11 +593,7 @@
       <c r="E8" t="n">
         <v>115</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -657,11 +601,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>2024</v>
       </c>
@@ -671,11 +611,7 @@
       <c r="E9" t="n">
         <v>223</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -683,11 +619,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>2024</v>
       </c>
@@ -697,11 +629,7 @@
       <c r="E10" t="n">
         <v>224</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -709,11 +637,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>2024</v>
       </c>
@@ -723,11 +647,7 @@
       <c r="E11" t="n">
         <v>204</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -735,11 +655,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>2024</v>
       </c>
@@ -749,11 +665,7 @@
       <c r="E12" t="n">
         <v>173</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -761,11 +673,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>2024</v>
       </c>
@@ -775,11 +683,7 @@
       <c r="E13" t="n">
         <v>264</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -787,11 +691,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>2025</v>
       </c>
@@ -801,11 +701,7 @@
       <c r="E14" t="n">
         <v>371</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -813,11 +709,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>2025</v>
       </c>
@@ -827,11 +719,7 @@
       <c r="E15" t="n">
         <v>371</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -839,11 +727,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>2025</v>
       </c>
@@ -853,11 +737,7 @@
       <c r="E16" t="n">
         <v>227</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -865,11 +745,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>2025</v>
       </c>
@@ -879,11 +755,7 @@
       <c r="E17" t="n">
         <v>232</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -891,11 +763,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>2025</v>
       </c>
@@ -905,11 +773,7 @@
       <c r="E18" t="n">
         <v>261</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -917,11 +781,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>2025</v>
       </c>
@@ -931,11 +791,7 @@
       <c r="E19" t="n">
         <v>129</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -943,11 +799,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>2025</v>
       </c>
@@ -957,11 +809,7 @@
       <c r="E20" t="n">
         <v>186</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -969,11 +817,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>2025</v>
       </c>
@@ -983,11 +827,7 @@
       <c r="E21" t="n">
         <v>194</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -995,11 +835,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>2025</v>
       </c>
@@ -1009,11 +845,7 @@
       <c r="E22" t="n">
         <v>195</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1021,11 +853,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>2025</v>
       </c>
@@ -1035,11 +863,7 @@
       <c r="E23" t="n">
         <v>175</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1047,11 +871,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>2025</v>
       </c>
@@ -1061,11 +881,7 @@
       <c r="E24" t="n">
         <v>178</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1073,11 +889,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>2025</v>
       </c>
@@ -1087,11 +899,7 @@
       <c r="E25" t="n">
         <v>152</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1099,11 +907,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>2026</v>
       </c>
@@ -1113,11 +917,7 @@
       <c r="E26" t="n">
         <v>250</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1125,11 +925,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>2026</v>
       </c>
@@ -1139,11 +935,7 @@
       <c r="E27" t="n">
         <v>157</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1151,11 +943,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>2026</v>
       </c>
@@ -1165,11 +953,7 @@
       <c r="E28" t="n">
         <v>216</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1177,11 +961,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>2026</v>
       </c>
@@ -1191,11 +971,7 @@
       <c r="E29" t="n">
         <v>182</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1203,11 +979,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>2026</v>
       </c>
@@ -1217,11 +989,7 @@
       <c r="E30" t="n">
         <v>212</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1229,11 +997,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>2026</v>
       </c>
@@ -1243,11 +1007,7 @@
       <c r="E31" t="n">
         <v>202</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1255,11 +1015,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>2026</v>
       </c>
@@ -1269,11 +1025,7 @@
       <c r="E32" t="n">
         <v>261</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1281,11 +1033,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>2026</v>
       </c>
@@ -1295,11 +1043,7 @@
       <c r="E33" t="n">
         <v>224</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1307,11 +1051,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>2026</v>
       </c>
@@ -1321,11 +1061,7 @@
       <c r="E34" t="n">
         <v>180</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1345,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -1965,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -2585,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -3209,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -3825,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -4445,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -5065,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5425,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -5699,11 +5435,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
         <v>2024</v>
       </c>
@@ -5713,11 +5445,7 @@
       <c r="E274" t="n">
         <v>116</v>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5725,11 +5453,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
         <v>2024</v>
       </c>
@@ -5739,11 +5463,7 @@
       <c r="E275" t="n">
         <v>81</v>
       </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5751,11 +5471,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
         <v>2024</v>
       </c>
@@ -5765,11 +5481,7 @@
       <c r="E276" t="n">
         <v>79</v>
       </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5777,11 +5489,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B277" t="inlineStr"/>
       <c r="C277" t="n">
         <v>2024</v>
       </c>
@@ -5791,11 +5499,7 @@
       <c r="E277" t="n">
         <v>54</v>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5803,11 +5507,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
         <v>2024</v>
       </c>
@@ -5817,11 +5517,7 @@
       <c r="E278" t="n">
         <v>27</v>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5829,11 +5525,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
         <v>2024</v>
       </c>
@@ -5843,11 +5535,7 @@
       <c r="E279" t="n">
         <v>78</v>
       </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5855,11 +5543,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
         <v>2024</v>
       </c>
@@ -5869,11 +5553,7 @@
       <c r="E280" t="n">
         <v>52</v>
       </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5881,11 +5561,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
         <v>2024</v>
       </c>
@@ -5895,11 +5571,7 @@
       <c r="E281" t="n">
         <v>110</v>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5907,11 +5579,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B282" t="inlineStr"/>
       <c r="C282" t="n">
         <v>2024</v>
       </c>
@@ -5921,11 +5589,7 @@
       <c r="E282" t="n">
         <v>108</v>
       </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5933,11 +5597,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B283" t="inlineStr"/>
       <c r="C283" t="n">
         <v>2024</v>
       </c>
@@ -5947,11 +5607,7 @@
       <c r="E283" t="n">
         <v>102</v>
       </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5959,11 +5615,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B284" t="inlineStr"/>
       <c r="C284" t="n">
         <v>2024</v>
       </c>
@@ -5973,11 +5625,7 @@
       <c r="E284" t="n">
         <v>78</v>
       </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5985,11 +5633,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
         <v>2024</v>
       </c>
@@ -5999,11 +5643,7 @@
       <c r="E285" t="n">
         <v>121</v>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6011,11 +5651,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B286" t="inlineStr"/>
       <c r="C286" t="n">
         <v>2025</v>
       </c>
@@ -6025,11 +5661,7 @@
       <c r="E286" t="n">
         <v>223</v>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6037,11 +5669,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
         <v>2025</v>
       </c>
@@ -6051,11 +5679,7 @@
       <c r="E287" t="n">
         <v>122</v>
       </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6063,11 +5687,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
         <v>2025</v>
       </c>
@@ -6077,11 +5697,7 @@
       <c r="E288" t="n">
         <v>147</v>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6089,11 +5705,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
         <v>2025</v>
       </c>
@@ -6103,11 +5715,7 @@
       <c r="E289" t="n">
         <v>128</v>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6115,11 +5723,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B290" t="inlineStr"/>
       <c r="C290" t="n">
         <v>2025</v>
       </c>
@@ -6129,11 +5733,7 @@
       <c r="E290" t="n">
         <v>103</v>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6141,11 +5741,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B291" t="inlineStr"/>
       <c r="C291" t="n">
         <v>2025</v>
       </c>
@@ -6155,11 +5751,7 @@
       <c r="E291" t="n">
         <v>106</v>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6167,11 +5759,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B292" t="inlineStr"/>
       <c r="C292" t="n">
         <v>2025</v>
       </c>
@@ -6181,11 +5769,7 @@
       <c r="E292" t="n">
         <v>80</v>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6193,11 +5777,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B293" t="inlineStr"/>
       <c r="C293" t="n">
         <v>2025</v>
       </c>
@@ -6207,11 +5787,7 @@
       <c r="E293" t="n">
         <v>107</v>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6219,11 +5795,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B294" t="inlineStr"/>
       <c r="C294" t="n">
         <v>2025</v>
       </c>
@@ -6233,11 +5805,7 @@
       <c r="E294" t="n">
         <v>86</v>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6245,11 +5813,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B295" t="inlineStr"/>
       <c r="C295" t="n">
         <v>2025</v>
       </c>
@@ -6259,11 +5823,7 @@
       <c r="E295" t="n">
         <v>85</v>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6271,11 +5831,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B296" t="inlineStr"/>
       <c r="C296" t="n">
         <v>2025</v>
       </c>
@@ -6285,11 +5841,7 @@
       <c r="E296" t="n">
         <v>81</v>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6297,11 +5849,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="n">
         <v>2025</v>
       </c>
@@ -6311,11 +5859,7 @@
       <c r="E297" t="n">
         <v>77</v>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6323,11 +5867,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B298" t="inlineStr"/>
       <c r="C298" t="n">
         <v>2026</v>
       </c>
@@ -6337,11 +5877,7 @@
       <c r="E298" t="n">
         <v>106</v>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6349,11 +5885,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B299" t="inlineStr"/>
       <c r="C299" t="n">
         <v>2026</v>
       </c>
@@ -6363,11 +5895,7 @@
       <c r="E299" t="n">
         <v>87</v>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6375,11 +5903,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
         <v>2026</v>
       </c>
@@ -6389,11 +5913,7 @@
       <c r="E300" t="n">
         <v>93</v>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6401,11 +5921,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
         <v>2026</v>
       </c>
@@ -6415,11 +5931,7 @@
       <c r="E301" t="n">
         <v>87</v>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6427,11 +5939,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
         <v>2026</v>
       </c>
@@ -6441,11 +5949,7 @@
       <c r="E302" t="n">
         <v>118</v>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6453,11 +5957,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>2026</v>
       </c>
@@ -6467,11 +5967,7 @@
       <c r="E303" t="n">
         <v>91</v>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6479,11 +5975,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="n">
         <v>2026</v>
       </c>
@@ -6493,11 +5985,7 @@
       <c r="E304" t="n">
         <v>132</v>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6505,11 +5993,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B305" t="inlineStr"/>
       <c r="C305" t="n">
         <v>2026</v>
       </c>
@@ -6519,11 +6003,7 @@
       <c r="E305" t="n">
         <v>80</v>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6531,11 +6011,7 @@
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B306" t="inlineStr"/>
       <c r="C306" t="n">
         <v>2026</v>
       </c>
@@ -6545,11 +6021,7 @@
       <c r="E306" t="n">
         <v>70</v>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6569,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -7189,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -7809,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -8433,7 +7905,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -9049,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -9669,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -10289,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -10909,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11005,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -12153,7 +11625,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -12163,11 +11635,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B614" t="inlineStr"/>
       <c r="C614" t="n">
         <v>2024</v>
       </c>
@@ -12177,11 +11645,7 @@
       <c r="E614" t="n">
         <v>48</v>
       </c>
-      <c r="F614" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -12189,11 +11653,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B615" t="inlineStr"/>
       <c r="C615" t="n">
         <v>2024</v>
       </c>
@@ -12203,11 +11663,7 @@
       <c r="E615" t="n">
         <v>79</v>
       </c>
-      <c r="F615" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -12215,11 +11671,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B616" t="inlineStr"/>
       <c r="C616" t="n">
         <v>2024</v>
       </c>
@@ -12229,11 +11681,7 @@
       <c r="E616" t="n">
         <v>43</v>
       </c>
-      <c r="F616" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -12241,11 +11689,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B617" t="inlineStr"/>
       <c r="C617" t="n">
         <v>2024</v>
       </c>
@@ -12255,11 +11699,7 @@
       <c r="E617" t="n">
         <v>34</v>
       </c>
-      <c r="F617" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -12267,11 +11707,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B618" t="inlineStr"/>
       <c r="C618" t="n">
         <v>2024</v>
       </c>
@@ -12281,11 +11717,7 @@
       <c r="E618" t="n">
         <v>33</v>
       </c>
-      <c r="F618" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -12293,11 +11725,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B619" t="inlineStr"/>
       <c r="C619" t="n">
         <v>2024</v>
       </c>
@@ -12307,11 +11735,7 @@
       <c r="E619" t="n">
         <v>25</v>
       </c>
-      <c r="F619" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -12319,11 +11743,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B620" t="inlineStr"/>
       <c r="C620" t="n">
         <v>2024</v>
       </c>
@@ -12333,11 +11753,7 @@
       <c r="E620" t="n">
         <v>15</v>
       </c>
-      <c r="F620" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -12345,11 +11761,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B621" t="inlineStr"/>
       <c r="C621" t="n">
         <v>2024</v>
       </c>
@@ -12359,11 +11771,7 @@
       <c r="E621" t="n">
         <v>14</v>
       </c>
-      <c r="F621" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -12371,11 +11779,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B622" t="inlineStr"/>
       <c r="C622" t="n">
         <v>2024</v>
       </c>
@@ -12385,11 +11789,7 @@
       <c r="E622" t="n">
         <v>25</v>
       </c>
-      <c r="F622" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -12397,11 +11797,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B623" t="inlineStr"/>
       <c r="C623" t="n">
         <v>2024</v>
       </c>
@@ -12411,11 +11807,7 @@
       <c r="E623" t="n">
         <v>21</v>
       </c>
-      <c r="F623" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -12423,11 +11815,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B624" t="inlineStr"/>
       <c r="C624" t="n">
         <v>2024</v>
       </c>
@@ -12437,11 +11825,7 @@
       <c r="E624" t="n">
         <v>29</v>
       </c>
-      <c r="F624" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -12449,11 +11833,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B625" t="inlineStr"/>
       <c r="C625" t="n">
         <v>2024</v>
       </c>
@@ -12463,11 +11843,7 @@
       <c r="E625" t="n">
         <v>56</v>
       </c>
-      <c r="F625" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -12475,11 +11851,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B626" t="inlineStr"/>
       <c r="C626" t="n">
         <v>2025</v>
       </c>
@@ -12489,11 +11861,7 @@
       <c r="E626" t="n">
         <v>63</v>
       </c>
-      <c r="F626" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -12501,11 +11869,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B627" t="inlineStr"/>
       <c r="C627" t="n">
         <v>2025</v>
       </c>
@@ -12515,11 +11879,7 @@
       <c r="E627" t="n">
         <v>42</v>
       </c>
-      <c r="F627" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -12527,11 +11887,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B628" t="inlineStr"/>
       <c r="C628" t="n">
         <v>2025</v>
       </c>
@@ -12541,11 +11897,7 @@
       <c r="E628" t="n">
         <v>36</v>
       </c>
-      <c r="F628" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -12553,11 +11905,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B629" t="inlineStr"/>
       <c r="C629" t="n">
         <v>2025</v>
       </c>
@@ -12567,11 +11915,7 @@
       <c r="E629" t="n">
         <v>26</v>
       </c>
-      <c r="F629" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -12579,11 +11923,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B630" t="inlineStr"/>
       <c r="C630" t="n">
         <v>2025</v>
       </c>
@@ -12593,11 +11933,7 @@
       <c r="E630" t="n">
         <v>60</v>
       </c>
-      <c r="F630" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -12605,11 +11941,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B631" t="inlineStr"/>
       <c r="C631" t="n">
         <v>2025</v>
       </c>
@@ -12619,11 +11951,7 @@
       <c r="E631" t="n">
         <v>44</v>
       </c>
-      <c r="F631" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -12631,11 +11959,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B632" t="inlineStr"/>
       <c r="C632" t="n">
         <v>2025</v>
       </c>
@@ -12645,11 +11969,7 @@
       <c r="E632" t="n">
         <v>88</v>
       </c>
-      <c r="F632" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -12657,11 +11977,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B633" t="inlineStr"/>
       <c r="C633" t="n">
         <v>2025</v>
       </c>
@@ -12671,11 +11987,7 @@
       <c r="E633" t="n">
         <v>63</v>
       </c>
-      <c r="F633" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -12683,11 +11995,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B634" t="inlineStr"/>
       <c r="C634" t="n">
         <v>2025</v>
       </c>
@@ -12697,11 +12005,7 @@
       <c r="E634" t="n">
         <v>278</v>
       </c>
-      <c r="F634" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -12709,11 +12013,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B635" t="inlineStr"/>
       <c r="C635" t="n">
         <v>2025</v>
       </c>
@@ -12723,11 +12023,7 @@
       <c r="E635" t="n">
         <v>62</v>
       </c>
-      <c r="F635" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -12735,11 +12031,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B636" t="inlineStr"/>
       <c r="C636" t="n">
         <v>2025</v>
       </c>
@@ -12749,11 +12041,7 @@
       <c r="E636" t="n">
         <v>156</v>
       </c>
-      <c r="F636" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -12761,11 +12049,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B637" t="inlineStr"/>
       <c r="C637" t="n">
         <v>2025</v>
       </c>
@@ -12775,11 +12059,7 @@
       <c r="E637" t="n">
         <v>112</v>
       </c>
-      <c r="F637" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -12787,11 +12067,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B638" t="inlineStr"/>
       <c r="C638" t="n">
         <v>2026</v>
       </c>
@@ -12801,11 +12077,7 @@
       <c r="E638" t="n">
         <v>117</v>
       </c>
-      <c r="F638" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -12813,11 +12085,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B639" t="inlineStr"/>
       <c r="C639" t="n">
         <v>2026</v>
       </c>
@@ -12827,11 +12095,7 @@
       <c r="E639" t="n">
         <v>90</v>
       </c>
-      <c r="F639" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -12839,11 +12103,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B640" t="inlineStr"/>
       <c r="C640" t="n">
         <v>2026</v>
       </c>
@@ -12853,11 +12113,7 @@
       <c r="E640" t="n">
         <v>93</v>
       </c>
-      <c r="F640" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -12865,11 +12121,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B641" t="inlineStr"/>
       <c r="C641" t="n">
         <v>2026</v>
       </c>
@@ -12879,11 +12131,7 @@
       <c r="E641" t="n">
         <v>101</v>
       </c>
-      <c r="F641" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -12891,11 +12139,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B642" t="inlineStr"/>
       <c r="C642" t="n">
         <v>2026</v>
       </c>
@@ -12905,11 +12149,7 @@
       <c r="E642" t="n">
         <v>90</v>
       </c>
-      <c r="F642" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -12917,11 +12157,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B643" t="inlineStr"/>
       <c r="C643" t="n">
         <v>2026</v>
       </c>
@@ -12931,11 +12167,7 @@
       <c r="E643" t="n">
         <v>40</v>
       </c>
-      <c r="F643" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -12943,11 +12175,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B644" t="inlineStr"/>
       <c r="C644" t="n">
         <v>2026</v>
       </c>
@@ -12957,11 +12185,7 @@
       <c r="E644" t="n">
         <v>82</v>
       </c>
-      <c r="F644" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -12969,11 +12193,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B645" t="inlineStr"/>
       <c r="C645" t="n">
         <v>2026</v>
       </c>
@@ -12983,11 +12203,7 @@
       <c r="E645" t="n">
         <v>79</v>
       </c>
-      <c r="F645" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -12995,11 +12211,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B646" t="inlineStr"/>
       <c r="C646" t="n">
         <v>2026</v>
       </c>
@@ -13009,11 +12221,7 @@
       <c r="E646" t="n">
         <v>55</v>
       </c>
-      <c r="F646" t="inlineStr">
-        <is>
-          <t>2026-10-24 10:42</t>
-        </is>
-      </c>
+      <c r="F646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -13033,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -13653,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -14277,7 +13485,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14105,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -15513,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -16137,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-24 10:42</t>
+          <t>2026-10-25 11:01</t>
         </is>
       </c>
     </row>
@@ -16376,106 +15584,106 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>657</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>758</v>
+        <v>783</v>
       </c>
     </row>
     <row r="3">
@@ -16584,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>744</v>
+        <v>755</v>
       </c>
     </row>
     <row r="4">
@@ -16693,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5">
@@ -16802,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>453</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6">
@@ -16911,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2405</v>
+        <v>2466</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C36" t="n">
         <v>2024</v>
       </c>
@@ -1105,7 +1109,11 @@
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1113,7 +1121,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C37" t="n">
         <v>2024</v>
       </c>
@@ -1123,7 +1135,11 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1131,7 +1147,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C38" t="n">
         <v>2024</v>
       </c>
@@ -1141,7 +1161,11 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1149,7 +1173,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C39" t="n">
         <v>2024</v>
       </c>
@@ -1159,7 +1187,11 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1167,7 +1199,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C40" t="n">
         <v>2024</v>
       </c>
@@ -1177,7 +1213,11 @@
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1185,7 +1225,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C41" t="n">
         <v>2024</v>
       </c>
@@ -1195,7 +1239,11 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1203,7 +1251,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C42" t="n">
         <v>2024</v>
       </c>
@@ -1213,7 +1265,11 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1221,7 +1277,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C43" t="n">
         <v>2024</v>
       </c>
@@ -1231,7 +1291,11 @@
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1239,7 +1303,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C44" t="n">
         <v>2024</v>
       </c>
@@ -1249,7 +1317,11 @@
       <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1257,7 +1329,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C45" t="n">
         <v>2024</v>
       </c>
@@ -1267,7 +1343,11 @@
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1275,7 +1355,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C46" t="n">
         <v>2024</v>
       </c>
@@ -1285,7 +1369,11 @@
       <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1293,7 +1381,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C47" t="n">
         <v>2024</v>
       </c>
@@ -1303,7 +1395,11 @@
       <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1311,7 +1407,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C48" t="n">
         <v>2025</v>
       </c>
@@ -1321,7 +1421,11 @@
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1329,7 +1433,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C49" t="n">
         <v>2025</v>
       </c>
@@ -1339,7 +1447,11 @@
       <c r="E49" t="n">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1347,7 +1459,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C50" t="n">
         <v>2025</v>
       </c>
@@ -1357,7 +1473,11 @@
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1365,7 +1485,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C51" t="n">
         <v>2025</v>
       </c>
@@ -1375,7 +1499,11 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1383,7 +1511,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C52" t="n">
         <v>2025</v>
       </c>
@@ -1393,7 +1525,11 @@
       <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1401,7 +1537,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C53" t="n">
         <v>2025</v>
       </c>
@@ -1411,7 +1551,11 @@
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1419,7 +1563,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C54" t="n">
         <v>2025</v>
       </c>
@@ -1429,7 +1577,11 @@
       <c r="E54" t="n">
         <v>0</v>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1437,7 +1589,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C55" t="n">
         <v>2025</v>
       </c>
@@ -1447,7 +1603,11 @@
       <c r="E55" t="n">
         <v>0</v>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1455,7 +1615,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C56" t="n">
         <v>2025</v>
       </c>
@@ -1465,7 +1629,11 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1473,7 +1641,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C57" t="n">
         <v>2025</v>
       </c>
@@ -1483,7 +1655,11 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1491,7 +1667,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C58" t="n">
         <v>2025</v>
       </c>
@@ -1501,7 +1681,11 @@
       <c r="E58" t="n">
         <v>0</v>
       </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1509,7 +1693,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C59" t="n">
         <v>2025</v>
       </c>
@@ -1519,7 +1707,11 @@
       <c r="E59" t="n">
         <v>3</v>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1527,7 +1719,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C60" t="n">
         <v>2026</v>
       </c>
@@ -1537,7 +1733,11 @@
       <c r="E60" t="n">
         <v>743</v>
       </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1545,7 +1745,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C61" t="n">
         <v>2026</v>
       </c>
@@ -1555,7 +1759,11 @@
       <c r="E61" t="n">
         <v>767</v>
       </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1563,7 +1771,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C62" t="n">
         <v>2026</v>
       </c>
@@ -1573,7 +1785,11 @@
       <c r="E62" t="n">
         <v>1062</v>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1581,7 +1797,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C63" t="n">
         <v>2026</v>
       </c>
@@ -1591,7 +1811,11 @@
       <c r="E63" t="n">
         <v>543</v>
       </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1599,7 +1823,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C64" t="n">
         <v>2026</v>
       </c>
@@ -1609,7 +1837,11 @@
       <c r="E64" t="n">
         <v>63</v>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1617,7 +1849,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C65" t="n">
         <v>2026</v>
       </c>
@@ -1627,7 +1863,11 @@
       <c r="E65" t="n">
         <v>54</v>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1635,7 +1875,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C66" t="n">
         <v>2026</v>
       </c>
@@ -1645,7 +1889,11 @@
       <c r="E66" t="n">
         <v>399</v>
       </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1653,7 +1901,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C67" t="n">
         <v>2026</v>
       </c>
@@ -1663,7 +1915,11 @@
       <c r="E67" t="n">
         <v>560</v>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1671,7 +1927,11 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C68" t="n">
         <v>2026</v>
       </c>
@@ -1681,7 +1941,11 @@
       <c r="E68" t="n">
         <v>431</v>
       </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1705,7 +1969,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2585,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -2945,7 +3209,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3825,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4445,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -4801,11 +5065,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5685,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6305,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6925,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7545,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -7901,11 +8165,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8789,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8799,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr"/>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C444" t="n">
         <v>2024</v>
       </c>
@@ -8545,7 +8813,11 @@
       <c r="E444" t="n">
         <v>319</v>
       </c>
-      <c r="F444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -8553,7 +8825,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr"/>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C445" t="n">
         <v>2024</v>
       </c>
@@ -8563,7 +8839,11 @@
       <c r="E445" t="n">
         <v>385</v>
       </c>
-      <c r="F445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -8571,7 +8851,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr"/>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C446" t="n">
         <v>2024</v>
       </c>
@@ -8581,7 +8865,11 @@
       <c r="E446" t="n">
         <v>282</v>
       </c>
-      <c r="F446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -8589,7 +8877,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr"/>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C447" t="n">
         <v>2024</v>
       </c>
@@ -8599,7 +8891,11 @@
       <c r="E447" t="n">
         <v>191</v>
       </c>
-      <c r="F447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -8607,7 +8903,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr"/>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C448" t="n">
         <v>2024</v>
       </c>
@@ -8617,7 +8917,11 @@
       <c r="E448" t="n">
         <v>115</v>
       </c>
-      <c r="F448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -8625,7 +8929,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr"/>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C449" t="n">
         <v>2024</v>
       </c>
@@ -8635,7 +8943,11 @@
       <c r="E449" t="n">
         <v>143</v>
       </c>
-      <c r="F449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -8643,7 +8955,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr"/>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C450" t="n">
         <v>2024</v>
       </c>
@@ -8653,7 +8969,11 @@
       <c r="E450" t="n">
         <v>86</v>
       </c>
-      <c r="F450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -8661,7 +8981,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr"/>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C451" t="n">
         <v>2024</v>
       </c>
@@ -8671,7 +8995,11 @@
       <c r="E451" t="n">
         <v>225</v>
       </c>
-      <c r="F451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -8679,7 +9007,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr"/>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C452" t="n">
         <v>2024</v>
       </c>
@@ -8689,7 +9021,11 @@
       <c r="E452" t="n">
         <v>182</v>
       </c>
-      <c r="F452" t="inlineStr"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -8697,7 +9033,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr"/>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C453" t="n">
         <v>2024</v>
       </c>
@@ -8707,7 +9047,11 @@
       <c r="E453" t="n">
         <v>191</v>
       </c>
-      <c r="F453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -8715,7 +9059,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr"/>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C454" t="n">
         <v>2024</v>
       </c>
@@ -8725,7 +9073,11 @@
       <c r="E454" t="n">
         <v>136</v>
       </c>
-      <c r="F454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -8733,7 +9085,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr"/>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C455" t="n">
         <v>2024</v>
       </c>
@@ -8743,7 +9099,11 @@
       <c r="E455" t="n">
         <v>175</v>
       </c>
-      <c r="F455" t="inlineStr"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -8751,7 +9111,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr"/>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C456" t="n">
         <v>2025</v>
       </c>
@@ -8761,7 +9125,11 @@
       <c r="E456" t="n">
         <v>379</v>
       </c>
-      <c r="F456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -8769,7 +9137,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr"/>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C457" t="n">
         <v>2025</v>
       </c>
@@ -8779,7 +9151,11 @@
       <c r="E457" t="n">
         <v>200</v>
       </c>
-      <c r="F457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -8787,7 +9163,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr"/>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C458" t="n">
         <v>2025</v>
       </c>
@@ -8797,7 +9177,11 @@
       <c r="E458" t="n">
         <v>224</v>
       </c>
-      <c r="F458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -8805,7 +9189,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr"/>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C459" t="n">
         <v>2025</v>
       </c>
@@ -8815,7 +9203,11 @@
       <c r="E459" t="n">
         <v>173</v>
       </c>
-      <c r="F459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -8823,7 +9215,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr"/>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C460" t="n">
         <v>2025</v>
       </c>
@@ -8833,7 +9229,11 @@
       <c r="E460" t="n">
         <v>185</v>
       </c>
-      <c r="F460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -8841,7 +9241,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr"/>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C461" t="n">
         <v>2025</v>
       </c>
@@ -8851,7 +9255,11 @@
       <c r="E461" t="n">
         <v>181</v>
       </c>
-      <c r="F461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -8859,7 +9267,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr"/>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C462" t="n">
         <v>2025</v>
       </c>
@@ -8869,7 +9281,11 @@
       <c r="E462" t="n">
         <v>137</v>
       </c>
-      <c r="F462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -8877,7 +9293,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr"/>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C463" t="n">
         <v>2025</v>
       </c>
@@ -8887,7 +9307,11 @@
       <c r="E463" t="n">
         <v>199</v>
       </c>
-      <c r="F463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -8895,7 +9319,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr"/>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C464" t="n">
         <v>2025</v>
       </c>
@@ -8905,7 +9333,11 @@
       <c r="E464" t="n">
         <v>198</v>
       </c>
-      <c r="F464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -8913,7 +9345,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr"/>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C465" t="n">
         <v>2025</v>
       </c>
@@ -8923,7 +9359,11 @@
       <c r="E465" t="n">
         <v>197</v>
       </c>
-      <c r="F465" t="inlineStr"/>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -8931,7 +9371,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr"/>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C466" t="n">
         <v>2025</v>
       </c>
@@ -8941,7 +9385,11 @@
       <c r="E466" t="n">
         <v>153</v>
       </c>
-      <c r="F466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -8949,7 +9397,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr"/>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C467" t="n">
         <v>2025</v>
       </c>
@@ -8959,7 +9411,11 @@
       <c r="E467" t="n">
         <v>107</v>
       </c>
-      <c r="F467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -8967,7 +9423,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr"/>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C468" t="n">
         <v>2026</v>
       </c>
@@ -8977,7 +9437,11 @@
       <c r="E468" t="n">
         <v>217</v>
       </c>
-      <c r="F468" t="inlineStr"/>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -8985,7 +9449,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr"/>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C469" t="n">
         <v>2026</v>
       </c>
@@ -8995,7 +9463,11 @@
       <c r="E469" t="n">
         <v>123</v>
       </c>
-      <c r="F469" t="inlineStr"/>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -9003,7 +9475,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr"/>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C470" t="n">
         <v>2026</v>
       </c>
@@ -9013,7 +9489,11 @@
       <c r="E470" t="n">
         <v>125</v>
       </c>
-      <c r="F470" t="inlineStr"/>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -9021,7 +9501,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr"/>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C471" t="n">
         <v>2026</v>
       </c>
@@ -9031,7 +9515,11 @@
       <c r="E471" t="n">
         <v>111</v>
       </c>
-      <c r="F471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -9039,7 +9527,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr"/>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C472" t="n">
         <v>2026</v>
       </c>
@@ -9049,7 +9541,11 @@
       <c r="E472" t="n">
         <v>100</v>
       </c>
-      <c r="F472" t="inlineStr"/>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -9057,7 +9553,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr"/>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C473" t="n">
         <v>2026</v>
       </c>
@@ -9067,7 +9567,11 @@
       <c r="E473" t="n">
         <v>79</v>
       </c>
-      <c r="F473" t="inlineStr"/>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -9075,7 +9579,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr"/>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C474" t="n">
         <v>2026</v>
       </c>
@@ -9085,7 +9593,11 @@
       <c r="E474" t="n">
         <v>119</v>
       </c>
-      <c r="F474" t="inlineStr"/>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -9093,7 +9605,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr"/>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C475" t="n">
         <v>2026</v>
       </c>
@@ -9103,7 +9619,11 @@
       <c r="E475" t="n">
         <v>115</v>
       </c>
-      <c r="F475" t="inlineStr"/>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -9111,7 +9631,11 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr"/>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Regiao 3</t>
+        </is>
+      </c>
       <c r="C476" t="n">
         <v>2026</v>
       </c>
@@ -9121,7 +9645,11 @@
       <c r="E476" t="n">
         <v>93</v>
       </c>
-      <c r="F476" t="inlineStr"/>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -9145,7 +9673,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9683,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr"/>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C478" t="n">
         <v>2024</v>
       </c>
@@ -9165,7 +9697,11 @@
       <c r="E478" t="n">
         <v>0</v>
       </c>
-      <c r="F478" t="inlineStr"/>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -9173,7 +9709,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr"/>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C479" t="n">
         <v>2024</v>
       </c>
@@ -9183,7 +9723,11 @@
       <c r="E479" t="n">
         <v>0</v>
       </c>
-      <c r="F479" t="inlineStr"/>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -9191,7 +9735,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr"/>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C480" t="n">
         <v>2024</v>
       </c>
@@ -9201,7 +9749,11 @@
       <c r="E480" t="n">
         <v>0</v>
       </c>
-      <c r="F480" t="inlineStr"/>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -9209,7 +9761,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr"/>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C481" t="n">
         <v>2024</v>
       </c>
@@ -9219,7 +9775,11 @@
       <c r="E481" t="n">
         <v>0</v>
       </c>
-      <c r="F481" t="inlineStr"/>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -9227,7 +9787,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr"/>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C482" t="n">
         <v>2024</v>
       </c>
@@ -9237,7 +9801,11 @@
       <c r="E482" t="n">
         <v>0</v>
       </c>
-      <c r="F482" t="inlineStr"/>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -9245,7 +9813,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr"/>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C483" t="n">
         <v>2024</v>
       </c>
@@ -9255,7 +9827,11 @@
       <c r="E483" t="n">
         <v>0</v>
       </c>
-      <c r="F483" t="inlineStr"/>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -9263,7 +9839,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr"/>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C484" t="n">
         <v>2024</v>
       </c>
@@ -9273,7 +9853,11 @@
       <c r="E484" t="n">
         <v>0</v>
       </c>
-      <c r="F484" t="inlineStr"/>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -9281,7 +9865,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr"/>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C485" t="n">
         <v>2024</v>
       </c>
@@ -9291,7 +9879,11 @@
       <c r="E485" t="n">
         <v>0</v>
       </c>
-      <c r="F485" t="inlineStr"/>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -9299,7 +9891,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr"/>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C486" t="n">
         <v>2024</v>
       </c>
@@ -9309,7 +9905,11 @@
       <c r="E486" t="n">
         <v>0</v>
       </c>
-      <c r="F486" t="inlineStr"/>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -9317,7 +9917,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr"/>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C487" t="n">
         <v>2024</v>
       </c>
@@ -9327,7 +9931,11 @@
       <c r="E487" t="n">
         <v>0</v>
       </c>
-      <c r="F487" t="inlineStr"/>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -9335,7 +9943,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr"/>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C488" t="n">
         <v>2024</v>
       </c>
@@ -9345,7 +9957,11 @@
       <c r="E488" t="n">
         <v>0</v>
       </c>
-      <c r="F488" t="inlineStr"/>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -9353,7 +9969,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr"/>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C489" t="n">
         <v>2024</v>
       </c>
@@ -9363,7 +9983,11 @@
       <c r="E489" t="n">
         <v>0</v>
       </c>
-      <c r="F489" t="inlineStr"/>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -9371,7 +9995,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr"/>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C490" t="n">
         <v>2025</v>
       </c>
@@ -9381,7 +10009,11 @@
       <c r="E490" t="n">
         <v>0</v>
       </c>
-      <c r="F490" t="inlineStr"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -9389,7 +10021,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr"/>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C491" t="n">
         <v>2025</v>
       </c>
@@ -9399,7 +10035,11 @@
       <c r="E491" t="n">
         <v>0</v>
       </c>
-      <c r="F491" t="inlineStr"/>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -9407,7 +10047,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr"/>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C492" t="n">
         <v>2025</v>
       </c>
@@ -9417,7 +10061,11 @@
       <c r="E492" t="n">
         <v>0</v>
       </c>
-      <c r="F492" t="inlineStr"/>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -9425,7 +10073,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr"/>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C493" t="n">
         <v>2025</v>
       </c>
@@ -9435,7 +10087,11 @@
       <c r="E493" t="n">
         <v>0</v>
       </c>
-      <c r="F493" t="inlineStr"/>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -9443,7 +10099,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr"/>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C494" t="n">
         <v>2025</v>
       </c>
@@ -9453,7 +10113,11 @@
       <c r="E494" t="n">
         <v>0</v>
       </c>
-      <c r="F494" t="inlineStr"/>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -9461,7 +10125,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B495" t="inlineStr"/>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C495" t="n">
         <v>2025</v>
       </c>
@@ -9471,7 +10139,11 @@
       <c r="E495" t="n">
         <v>0</v>
       </c>
-      <c r="F495" t="inlineStr"/>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -9479,7 +10151,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B496" t="inlineStr"/>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C496" t="n">
         <v>2025</v>
       </c>
@@ -9489,7 +10165,11 @@
       <c r="E496" t="n">
         <v>0</v>
       </c>
-      <c r="F496" t="inlineStr"/>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -9497,7 +10177,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B497" t="inlineStr"/>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C497" t="n">
         <v>2025</v>
       </c>
@@ -9507,7 +10191,11 @@
       <c r="E497" t="n">
         <v>0</v>
       </c>
-      <c r="F497" t="inlineStr"/>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -9515,7 +10203,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B498" t="inlineStr"/>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C498" t="n">
         <v>2025</v>
       </c>
@@ -9525,7 +10217,11 @@
       <c r="E498" t="n">
         <v>0</v>
       </c>
-      <c r="F498" t="inlineStr"/>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -9533,7 +10229,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B499" t="inlineStr"/>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C499" t="n">
         <v>2025</v>
       </c>
@@ -9543,7 +10243,11 @@
       <c r="E499" t="n">
         <v>0</v>
       </c>
-      <c r="F499" t="inlineStr"/>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -9551,7 +10255,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B500" t="inlineStr"/>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C500" t="n">
         <v>2025</v>
       </c>
@@ -9561,7 +10269,11 @@
       <c r="E500" t="n">
         <v>0</v>
       </c>
-      <c r="F500" t="inlineStr"/>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -9569,7 +10281,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B501" t="inlineStr"/>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C501" t="n">
         <v>2025</v>
       </c>
@@ -9579,7 +10295,11 @@
       <c r="E501" t="n">
         <v>0</v>
       </c>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -9587,7 +10307,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B502" t="inlineStr"/>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C502" t="n">
         <v>2026</v>
       </c>
@@ -9597,7 +10321,11 @@
       <c r="E502" t="n">
         <v>0</v>
       </c>
-      <c r="F502" t="inlineStr"/>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -9605,7 +10333,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B503" t="inlineStr"/>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C503" t="n">
         <v>2026</v>
       </c>
@@ -9615,7 +10347,11 @@
       <c r="E503" t="n">
         <v>6</v>
       </c>
-      <c r="F503" t="inlineStr"/>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -9623,7 +10359,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B504" t="inlineStr"/>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C504" t="n">
         <v>2026</v>
       </c>
@@ -9633,7 +10373,11 @@
       <c r="E504" t="n">
         <v>396</v>
       </c>
-      <c r="F504" t="inlineStr"/>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -9641,7 +10385,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B505" t="inlineStr"/>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C505" t="n">
         <v>2026</v>
       </c>
@@ -9651,7 +10399,11 @@
       <c r="E505" t="n">
         <v>1460</v>
       </c>
-      <c r="F505" t="inlineStr"/>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -9659,7 +10411,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B506" t="inlineStr"/>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C506" t="n">
         <v>2026</v>
       </c>
@@ -9669,7 +10425,11 @@
       <c r="E506" t="n">
         <v>273</v>
       </c>
-      <c r="F506" t="inlineStr"/>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -9677,7 +10437,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B507" t="inlineStr"/>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C507" t="n">
         <v>2026</v>
       </c>
@@ -9687,7 +10451,11 @@
       <c r="E507" t="n">
         <v>104</v>
       </c>
-      <c r="F507" t="inlineStr"/>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -9695,7 +10463,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B508" t="inlineStr"/>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C508" t="n">
         <v>2026</v>
       </c>
@@ -9705,7 +10477,11 @@
       <c r="E508" t="n">
         <v>324</v>
       </c>
-      <c r="F508" t="inlineStr"/>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -9713,7 +10489,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B509" t="inlineStr"/>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C509" t="n">
         <v>2026</v>
       </c>
@@ -9723,7 +10503,11 @@
       <c r="E509" t="n">
         <v>478</v>
       </c>
-      <c r="F509" t="inlineStr"/>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -9731,7 +10515,11 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B510" t="inlineStr"/>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C510" t="n">
         <v>2026</v>
       </c>
@@ -9741,7 +10529,11 @@
       <c r="E510" t="n">
         <v>378</v>
       </c>
-      <c r="F510" t="inlineStr"/>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -9765,7 +10557,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -10381,11 +11173,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11793,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -11621,11 +12413,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -12241,11 +13033,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -12865,7 +13657,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -13485,7 +14277,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14893,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -14721,11 +15513,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -14735,7 +15527,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B784" t="inlineStr"/>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C784" t="n">
         <v>2024</v>
       </c>
@@ -14745,7 +15541,11 @@
       <c r="E784" t="n">
         <v>0</v>
       </c>
-      <c r="F784" t="inlineStr"/>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -14753,7 +15553,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B785" t="inlineStr"/>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C785" t="n">
         <v>2024</v>
       </c>
@@ -14763,7 +15567,11 @@
       <c r="E785" t="n">
         <v>0</v>
       </c>
-      <c r="F785" t="inlineStr"/>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -14771,7 +15579,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B786" t="inlineStr"/>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C786" t="n">
         <v>2024</v>
       </c>
@@ -14781,7 +15593,11 @@
       <c r="E786" t="n">
         <v>0</v>
       </c>
-      <c r="F786" t="inlineStr"/>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -14789,7 +15605,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B787" t="inlineStr"/>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C787" t="n">
         <v>2024</v>
       </c>
@@ -14799,7 +15619,11 @@
       <c r="E787" t="n">
         <v>0</v>
       </c>
-      <c r="F787" t="inlineStr"/>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -14807,7 +15631,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B788" t="inlineStr"/>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C788" t="n">
         <v>2024</v>
       </c>
@@ -14817,7 +15645,11 @@
       <c r="E788" t="n">
         <v>0</v>
       </c>
-      <c r="F788" t="inlineStr"/>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -14825,7 +15657,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B789" t="inlineStr"/>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C789" t="n">
         <v>2024</v>
       </c>
@@ -14835,7 +15671,11 @@
       <c r="E789" t="n">
         <v>0</v>
       </c>
-      <c r="F789" t="inlineStr"/>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -14843,7 +15683,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B790" t="inlineStr"/>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C790" t="n">
         <v>2024</v>
       </c>
@@ -14853,7 +15697,11 @@
       <c r="E790" t="n">
         <v>0</v>
       </c>
-      <c r="F790" t="inlineStr"/>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -14861,7 +15709,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B791" t="inlineStr"/>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C791" t="n">
         <v>2024</v>
       </c>
@@ -14871,7 +15723,11 @@
       <c r="E791" t="n">
         <v>0</v>
       </c>
-      <c r="F791" t="inlineStr"/>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -14879,7 +15735,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B792" t="inlineStr"/>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C792" t="n">
         <v>2024</v>
       </c>
@@ -14889,7 +15749,11 @@
       <c r="E792" t="n">
         <v>0</v>
       </c>
-      <c r="F792" t="inlineStr"/>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -14897,7 +15761,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B793" t="inlineStr"/>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C793" t="n">
         <v>2024</v>
       </c>
@@ -14907,7 +15775,11 @@
       <c r="E793" t="n">
         <v>0</v>
       </c>
-      <c r="F793" t="inlineStr"/>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -14915,7 +15787,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B794" t="inlineStr"/>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C794" t="n">
         <v>2024</v>
       </c>
@@ -14925,7 +15801,11 @@
       <c r="E794" t="n">
         <v>0</v>
       </c>
-      <c r="F794" t="inlineStr"/>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -14933,7 +15813,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B795" t="inlineStr"/>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C795" t="n">
         <v>2024</v>
       </c>
@@ -14943,7 +15827,11 @@
       <c r="E795" t="n">
         <v>0</v>
       </c>
-      <c r="F795" t="inlineStr"/>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -14951,7 +15839,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B796" t="inlineStr"/>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C796" t="n">
         <v>2025</v>
       </c>
@@ -14961,7 +15853,11 @@
       <c r="E796" t="n">
         <v>0</v>
       </c>
-      <c r="F796" t="inlineStr"/>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -14969,7 +15865,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B797" t="inlineStr"/>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C797" t="n">
         <v>2025</v>
       </c>
@@ -14979,7 +15879,11 @@
       <c r="E797" t="n">
         <v>0</v>
       </c>
-      <c r="F797" t="inlineStr"/>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -14987,7 +15891,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B798" t="inlineStr"/>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C798" t="n">
         <v>2025</v>
       </c>
@@ -14997,7 +15905,11 @@
       <c r="E798" t="n">
         <v>0</v>
       </c>
-      <c r="F798" t="inlineStr"/>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -15005,7 +15917,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B799" t="inlineStr"/>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C799" t="n">
         <v>2025</v>
       </c>
@@ -15015,7 +15931,11 @@
       <c r="E799" t="n">
         <v>0</v>
       </c>
-      <c r="F799" t="inlineStr"/>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -15023,7 +15943,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B800" t="inlineStr"/>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C800" t="n">
         <v>2025</v>
       </c>
@@ -15033,7 +15957,11 @@
       <c r="E800" t="n">
         <v>0</v>
       </c>
-      <c r="F800" t="inlineStr"/>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -15041,7 +15969,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B801" t="inlineStr"/>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C801" t="n">
         <v>2025</v>
       </c>
@@ -15051,7 +15983,11 @@
       <c r="E801" t="n">
         <v>0</v>
       </c>
-      <c r="F801" t="inlineStr"/>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -15059,7 +15995,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B802" t="inlineStr"/>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C802" t="n">
         <v>2025</v>
       </c>
@@ -15069,7 +16009,11 @@
       <c r="E802" t="n">
         <v>0</v>
       </c>
-      <c r="F802" t="inlineStr"/>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -15077,7 +16021,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B803" t="inlineStr"/>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C803" t="n">
         <v>2025</v>
       </c>
@@ -15087,7 +16035,11 @@
       <c r="E803" t="n">
         <v>0</v>
       </c>
-      <c r="F803" t="inlineStr"/>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -15095,7 +16047,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B804" t="inlineStr"/>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C804" t="n">
         <v>2025</v>
       </c>
@@ -15105,7 +16061,11 @@
       <c r="E804" t="n">
         <v>0</v>
       </c>
-      <c r="F804" t="inlineStr"/>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -15113,7 +16073,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B805" t="inlineStr"/>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C805" t="n">
         <v>2025</v>
       </c>
@@ -15123,7 +16087,11 @@
       <c r="E805" t="n">
         <v>0</v>
       </c>
-      <c r="F805" t="inlineStr"/>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -15131,7 +16099,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B806" t="inlineStr"/>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C806" t="n">
         <v>2025</v>
       </c>
@@ -15141,7 +16113,11 @@
       <c r="E806" t="n">
         <v>0</v>
       </c>
-      <c r="F806" t="inlineStr"/>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -15149,7 +16125,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B807" t="inlineStr"/>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C807" t="n">
         <v>2025</v>
       </c>
@@ -15159,7 +16139,11 @@
       <c r="E807" t="n">
         <v>0</v>
       </c>
-      <c r="F807" t="inlineStr"/>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -15167,7 +16151,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B808" t="inlineStr"/>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C808" t="n">
         <v>2026</v>
       </c>
@@ -15177,7 +16165,11 @@
       <c r="E808" t="n">
         <v>0</v>
       </c>
-      <c r="F808" t="inlineStr"/>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -15185,7 +16177,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B809" t="inlineStr"/>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C809" t="n">
         <v>2026</v>
       </c>
@@ -15195,7 +16191,11 @@
       <c r="E809" t="n">
         <v>6</v>
       </c>
-      <c r="F809" t="inlineStr"/>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -15203,7 +16203,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B810" t="inlineStr"/>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C810" t="n">
         <v>2026</v>
       </c>
@@ -15213,7 +16217,11 @@
       <c r="E810" t="n">
         <v>1061</v>
       </c>
-      <c r="F810" t="inlineStr"/>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -15221,7 +16229,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B811" t="inlineStr"/>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C811" t="n">
         <v>2026</v>
       </c>
@@ -15231,7 +16243,11 @@
       <c r="E811" t="n">
         <v>226</v>
       </c>
-      <c r="F811" t="inlineStr"/>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -15239,7 +16255,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B812" t="inlineStr"/>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C812" t="n">
         <v>2026</v>
       </c>
@@ -15249,7 +16269,11 @@
       <c r="E812" t="n">
         <v>106</v>
       </c>
-      <c r="F812" t="inlineStr"/>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -15257,7 +16281,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B813" t="inlineStr"/>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C813" t="n">
         <v>2026</v>
       </c>
@@ -15267,7 +16295,11 @@
       <c r="E813" t="n">
         <v>41</v>
       </c>
-      <c r="F813" t="inlineStr"/>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -15275,7 +16307,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B814" t="inlineStr"/>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C814" t="n">
         <v>2026</v>
       </c>
@@ -15285,7 +16321,11 @@
       <c r="E814" t="n">
         <v>53</v>
       </c>
-      <c r="F814" t="inlineStr"/>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -15293,7 +16333,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B815" t="inlineStr"/>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C815" t="n">
         <v>2026</v>
       </c>
@@ -15303,7 +16347,11 @@
       <c r="E815" t="n">
         <v>60</v>
       </c>
-      <c r="F815" t="inlineStr"/>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -15311,7 +16359,11 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B816" t="inlineStr"/>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="C816" t="n">
         <v>2026</v>
       </c>
@@ -15321,7 +16373,11 @@
       <c r="E816" t="n">
         <v>45</v>
       </c>
-      <c r="F816" t="inlineStr"/>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -15345,7 +16401,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-25 11:01</t>
+          <t>2026-10-26 13:23</t>
         </is>
       </c>
     </row>
@@ -15683,7 +16739,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>783</v>
+        <v>802</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +16848,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>755</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4">
@@ -15802,106 +16858,106 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="n">
-        <v>460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5">
@@ -15980,34 +17036,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>743</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2519</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2229</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1098</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>854</v>
       </c>
       <c r="AI5" t="n">
         <v>468</v>
@@ -16119,7 +17175,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2466</v>
+        <v>2518</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -1095,11 +1095,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>2024</v>
       </c>
@@ -1109,11 +1105,7 @@
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1121,11 +1113,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>2024</v>
       </c>
@@ -1135,11 +1123,7 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1147,11 +1131,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>2024</v>
       </c>
@@ -1161,11 +1141,7 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1173,11 +1149,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>2024</v>
       </c>
@@ -1187,11 +1159,7 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1199,11 +1167,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>2024</v>
       </c>
@@ -1213,11 +1177,7 @@
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1225,11 +1185,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>2024</v>
       </c>
@@ -1239,11 +1195,7 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1251,11 +1203,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>2024</v>
       </c>
@@ -1265,11 +1213,7 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1277,11 +1221,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>2024</v>
       </c>
@@ -1291,11 +1231,7 @@
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1303,11 +1239,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>2024</v>
       </c>
@@ -1317,11 +1249,7 @@
       <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1329,11 +1257,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>2024</v>
       </c>
@@ -1343,11 +1267,7 @@
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1355,11 +1275,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>2024</v>
       </c>
@@ -1369,11 +1285,7 @@
       <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1381,11 +1293,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>2024</v>
       </c>
@@ -1395,11 +1303,7 @@
       <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1407,11 +1311,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>2025</v>
       </c>
@@ -1421,11 +1321,7 @@
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1433,11 +1329,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>2025</v>
       </c>
@@ -1447,11 +1339,7 @@
       <c r="E49" t="n">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1459,11 +1347,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>2025</v>
       </c>
@@ -1473,11 +1357,7 @@
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1485,11 +1365,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>2025</v>
       </c>
@@ -1499,11 +1375,7 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1511,11 +1383,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>2025</v>
       </c>
@@ -1525,11 +1393,7 @@
       <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1537,11 +1401,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>2025</v>
       </c>
@@ -1551,11 +1411,7 @@
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1563,11 +1419,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>2025</v>
       </c>
@@ -1577,11 +1429,7 @@
       <c r="E54" t="n">
         <v>0</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1589,11 +1437,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>2025</v>
       </c>
@@ -1603,11 +1447,7 @@
       <c r="E55" t="n">
         <v>0</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1615,11 +1455,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>2025</v>
       </c>
@@ -1629,11 +1465,7 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1641,11 +1473,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>2025</v>
       </c>
@@ -1655,11 +1483,7 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1667,11 +1491,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>2025</v>
       </c>
@@ -1681,11 +1501,7 @@
       <c r="E58" t="n">
         <v>0</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1693,11 +1509,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>2025</v>
       </c>
@@ -1707,11 +1519,7 @@
       <c r="E59" t="n">
         <v>3</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1719,11 +1527,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>2026</v>
       </c>
@@ -1733,11 +1537,7 @@
       <c r="E60" t="n">
         <v>743</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1745,11 +1545,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>2026</v>
       </c>
@@ -1759,11 +1555,7 @@
       <c r="E61" t="n">
         <v>767</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1771,11 +1563,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>2026</v>
       </c>
@@ -1785,11 +1573,7 @@
       <c r="E62" t="n">
         <v>1062</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1797,11 +1581,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>2026</v>
       </c>
@@ -1811,11 +1591,7 @@
       <c r="E63" t="n">
         <v>543</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1823,11 +1599,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>2026</v>
       </c>
@@ -1837,11 +1609,7 @@
       <c r="E64" t="n">
         <v>63</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1849,11 +1617,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>2026</v>
       </c>
@@ -1863,11 +1627,7 @@
       <c r="E65" t="n">
         <v>54</v>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1875,11 +1635,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>2026</v>
       </c>
@@ -1889,11 +1645,7 @@
       <c r="E66" t="n">
         <v>399</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1901,11 +1653,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>2026</v>
       </c>
@@ -1915,11 +1663,7 @@
       <c r="E67" t="n">
         <v>560</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1927,11 +1671,7 @@
           <t>Barra Funda</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>2026</v>
       </c>
@@ -1941,11 +1681,7 @@
       <c r="E68" t="n">
         <v>431</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1965,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -2585,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -3209,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -3825,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -4445,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -5065,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -5685,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -6305,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -6925,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -7545,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -8165,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -8785,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -8799,11 +8535,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B444" t="inlineStr"/>
       <c r="C444" t="n">
         <v>2024</v>
       </c>
@@ -8813,11 +8545,7 @@
       <c r="E444" t="n">
         <v>319</v>
       </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -8825,11 +8553,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B445" t="inlineStr"/>
       <c r="C445" t="n">
         <v>2024</v>
       </c>
@@ -8839,11 +8563,7 @@
       <c r="E445" t="n">
         <v>385</v>
       </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -8851,11 +8571,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B446" t="inlineStr"/>
       <c r="C446" t="n">
         <v>2024</v>
       </c>
@@ -8865,11 +8581,7 @@
       <c r="E446" t="n">
         <v>282</v>
       </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -8877,11 +8589,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B447" t="inlineStr"/>
       <c r="C447" t="n">
         <v>2024</v>
       </c>
@@ -8891,11 +8599,7 @@
       <c r="E447" t="n">
         <v>191</v>
       </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -8903,11 +8607,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B448" t="inlineStr"/>
       <c r="C448" t="n">
         <v>2024</v>
       </c>
@@ -8917,11 +8617,7 @@
       <c r="E448" t="n">
         <v>115</v>
       </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -8929,11 +8625,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B449" t="inlineStr"/>
       <c r="C449" t="n">
         <v>2024</v>
       </c>
@@ -8943,11 +8635,7 @@
       <c r="E449" t="n">
         <v>143</v>
       </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -8955,11 +8643,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B450" t="inlineStr"/>
       <c r="C450" t="n">
         <v>2024</v>
       </c>
@@ -8969,11 +8653,7 @@
       <c r="E450" t="n">
         <v>86</v>
       </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -8981,11 +8661,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B451" t="inlineStr"/>
       <c r="C451" t="n">
         <v>2024</v>
       </c>
@@ -8995,11 +8671,7 @@
       <c r="E451" t="n">
         <v>225</v>
       </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -9007,11 +8679,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B452" t="inlineStr"/>
       <c r="C452" t="n">
         <v>2024</v>
       </c>
@@ -9021,11 +8689,7 @@
       <c r="E452" t="n">
         <v>182</v>
       </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -9033,11 +8697,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B453" t="inlineStr"/>
       <c r="C453" t="n">
         <v>2024</v>
       </c>
@@ -9047,11 +8707,7 @@
       <c r="E453" t="n">
         <v>191</v>
       </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -9059,11 +8715,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B454" t="inlineStr"/>
       <c r="C454" t="n">
         <v>2024</v>
       </c>
@@ -9073,11 +8725,7 @@
       <c r="E454" t="n">
         <v>136</v>
       </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -9085,11 +8733,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B455" t="inlineStr"/>
       <c r="C455" t="n">
         <v>2024</v>
       </c>
@@ -9099,11 +8743,7 @@
       <c r="E455" t="n">
         <v>175</v>
       </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -9111,11 +8751,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B456" t="inlineStr"/>
       <c r="C456" t="n">
         <v>2025</v>
       </c>
@@ -9125,11 +8761,7 @@
       <c r="E456" t="n">
         <v>379</v>
       </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -9137,11 +8769,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B457" t="inlineStr"/>
       <c r="C457" t="n">
         <v>2025</v>
       </c>
@@ -9151,11 +8779,7 @@
       <c r="E457" t="n">
         <v>200</v>
       </c>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -9163,11 +8787,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B458" t="inlineStr"/>
       <c r="C458" t="n">
         <v>2025</v>
       </c>
@@ -9177,11 +8797,7 @@
       <c r="E458" t="n">
         <v>224</v>
       </c>
-      <c r="F458" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -9189,11 +8805,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B459" t="inlineStr"/>
       <c r="C459" t="n">
         <v>2025</v>
       </c>
@@ -9203,11 +8815,7 @@
       <c r="E459" t="n">
         <v>173</v>
       </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -9215,11 +8823,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B460" t="inlineStr"/>
       <c r="C460" t="n">
         <v>2025</v>
       </c>
@@ -9229,11 +8833,7 @@
       <c r="E460" t="n">
         <v>185</v>
       </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -9241,11 +8841,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B461" t="inlineStr"/>
       <c r="C461" t="n">
         <v>2025</v>
       </c>
@@ -9255,11 +8851,7 @@
       <c r="E461" t="n">
         <v>181</v>
       </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -9267,11 +8859,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B462" t="inlineStr"/>
       <c r="C462" t="n">
         <v>2025</v>
       </c>
@@ -9281,11 +8869,7 @@
       <c r="E462" t="n">
         <v>137</v>
       </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -9293,11 +8877,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B463" t="inlineStr"/>
       <c r="C463" t="n">
         <v>2025</v>
       </c>
@@ -9307,11 +8887,7 @@
       <c r="E463" t="n">
         <v>199</v>
       </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -9319,11 +8895,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B464" t="inlineStr"/>
       <c r="C464" t="n">
         <v>2025</v>
       </c>
@@ -9333,11 +8905,7 @@
       <c r="E464" t="n">
         <v>198</v>
       </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -9345,11 +8913,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B465" t="inlineStr"/>
       <c r="C465" t="n">
         <v>2025</v>
       </c>
@@ -9359,11 +8923,7 @@
       <c r="E465" t="n">
         <v>197</v>
       </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -9371,11 +8931,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B466" t="inlineStr"/>
       <c r="C466" t="n">
         <v>2025</v>
       </c>
@@ -9385,11 +8941,7 @@
       <c r="E466" t="n">
         <v>153</v>
       </c>
-      <c r="F466" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -9397,11 +8949,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B467" t="inlineStr"/>
       <c r="C467" t="n">
         <v>2025</v>
       </c>
@@ -9411,11 +8959,7 @@
       <c r="E467" t="n">
         <v>107</v>
       </c>
-      <c r="F467" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -9423,11 +8967,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B468" t="inlineStr"/>
       <c r="C468" t="n">
         <v>2026</v>
       </c>
@@ -9437,11 +8977,7 @@
       <c r="E468" t="n">
         <v>217</v>
       </c>
-      <c r="F468" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -9449,11 +8985,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B469" t="inlineStr"/>
       <c r="C469" t="n">
         <v>2026</v>
       </c>
@@ -9463,11 +8995,7 @@
       <c r="E469" t="n">
         <v>123</v>
       </c>
-      <c r="F469" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -9475,11 +9003,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B470" t="inlineStr"/>
       <c r="C470" t="n">
         <v>2026</v>
       </c>
@@ -9489,11 +9013,7 @@
       <c r="E470" t="n">
         <v>125</v>
       </c>
-      <c r="F470" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -9501,11 +9021,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B471" t="inlineStr"/>
       <c r="C471" t="n">
         <v>2026</v>
       </c>
@@ -9515,11 +9031,7 @@
       <c r="E471" t="n">
         <v>111</v>
       </c>
-      <c r="F471" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -9527,11 +9039,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B472" t="inlineStr"/>
       <c r="C472" t="n">
         <v>2026</v>
       </c>
@@ -9541,11 +9049,7 @@
       <c r="E472" t="n">
         <v>100</v>
       </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -9553,11 +9057,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B473" t="inlineStr"/>
       <c r="C473" t="n">
         <v>2026</v>
       </c>
@@ -9567,11 +9067,7 @@
       <c r="E473" t="n">
         <v>79</v>
       </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -9579,11 +9075,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B474" t="inlineStr"/>
       <c r="C474" t="n">
         <v>2026</v>
       </c>
@@ -9593,11 +9085,7 @@
       <c r="E474" t="n">
         <v>119</v>
       </c>
-      <c r="F474" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -9605,11 +9093,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B475" t="inlineStr"/>
       <c r="C475" t="n">
         <v>2026</v>
       </c>
@@ -9619,11 +9103,7 @@
       <c r="E475" t="n">
         <v>115</v>
       </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -9631,11 +9111,7 @@
           <t>Messejana</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Regiao 3</t>
-        </is>
-      </c>
+      <c r="B476" t="inlineStr"/>
       <c r="C476" t="n">
         <v>2026</v>
       </c>
@@ -9645,11 +9121,7 @@
       <c r="E476" t="n">
         <v>93</v>
       </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -9669,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -9683,11 +9155,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B478" t="inlineStr"/>
       <c r="C478" t="n">
         <v>2024</v>
       </c>
@@ -9697,11 +9165,7 @@
       <c r="E478" t="n">
         <v>0</v>
       </c>
-      <c r="F478" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -9709,11 +9173,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B479" t="inlineStr"/>
       <c r="C479" t="n">
         <v>2024</v>
       </c>
@@ -9723,11 +9183,7 @@
       <c r="E479" t="n">
         <v>0</v>
       </c>
-      <c r="F479" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -9735,11 +9191,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B480" t="inlineStr"/>
       <c r="C480" t="n">
         <v>2024</v>
       </c>
@@ -9749,11 +9201,7 @@
       <c r="E480" t="n">
         <v>0</v>
       </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -9761,11 +9209,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B481" t="inlineStr"/>
       <c r="C481" t="n">
         <v>2024</v>
       </c>
@@ -9775,11 +9219,7 @@
       <c r="E481" t="n">
         <v>0</v>
       </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -9787,11 +9227,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B482" t="inlineStr"/>
       <c r="C482" t="n">
         <v>2024</v>
       </c>
@@ -9801,11 +9237,7 @@
       <c r="E482" t="n">
         <v>0</v>
       </c>
-      <c r="F482" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -9813,11 +9245,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B483" t="inlineStr"/>
       <c r="C483" t="n">
         <v>2024</v>
       </c>
@@ -9827,11 +9255,7 @@
       <c r="E483" t="n">
         <v>0</v>
       </c>
-      <c r="F483" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -9839,11 +9263,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B484" t="inlineStr"/>
       <c r="C484" t="n">
         <v>2024</v>
       </c>
@@ -9853,11 +9273,7 @@
       <c r="E484" t="n">
         <v>0</v>
       </c>
-      <c r="F484" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -9865,11 +9281,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B485" t="inlineStr"/>
       <c r="C485" t="n">
         <v>2024</v>
       </c>
@@ -9879,11 +9291,7 @@
       <c r="E485" t="n">
         <v>0</v>
       </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -9891,11 +9299,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B486" t="inlineStr"/>
       <c r="C486" t="n">
         <v>2024</v>
       </c>
@@ -9905,11 +9309,7 @@
       <c r="E486" t="n">
         <v>0</v>
       </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -9917,11 +9317,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B487" t="inlineStr"/>
       <c r="C487" t="n">
         <v>2024</v>
       </c>
@@ -9931,11 +9327,7 @@
       <c r="E487" t="n">
         <v>0</v>
       </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -9943,11 +9335,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B488" t="inlineStr"/>
       <c r="C488" t="n">
         <v>2024</v>
       </c>
@@ -9957,11 +9345,7 @@
       <c r="E488" t="n">
         <v>0</v>
       </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -9969,11 +9353,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B489" t="inlineStr"/>
       <c r="C489" t="n">
         <v>2024</v>
       </c>
@@ -9983,11 +9363,7 @@
       <c r="E489" t="n">
         <v>0</v>
       </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -9995,11 +9371,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B490" t="inlineStr"/>
       <c r="C490" t="n">
         <v>2025</v>
       </c>
@@ -10009,11 +9381,7 @@
       <c r="E490" t="n">
         <v>0</v>
       </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -10021,11 +9389,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B491" t="inlineStr"/>
       <c r="C491" t="n">
         <v>2025</v>
       </c>
@@ -10035,11 +9399,7 @@
       <c r="E491" t="n">
         <v>0</v>
       </c>
-      <c r="F491" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -10047,11 +9407,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B492" t="inlineStr"/>
       <c r="C492" t="n">
         <v>2025</v>
       </c>
@@ -10061,11 +9417,7 @@
       <c r="E492" t="n">
         <v>0</v>
       </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -10073,11 +9425,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B493" t="inlineStr"/>
       <c r="C493" t="n">
         <v>2025</v>
       </c>
@@ -10087,11 +9435,7 @@
       <c r="E493" t="n">
         <v>0</v>
       </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -10099,11 +9443,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B494" t="inlineStr"/>
       <c r="C494" t="n">
         <v>2025</v>
       </c>
@@ -10113,11 +9453,7 @@
       <c r="E494" t="n">
         <v>0</v>
       </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -10125,11 +9461,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B495" t="inlineStr"/>
       <c r="C495" t="n">
         <v>2025</v>
       </c>
@@ -10139,11 +9471,7 @@
       <c r="E495" t="n">
         <v>0</v>
       </c>
-      <c r="F495" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -10151,11 +9479,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B496" t="inlineStr"/>
       <c r="C496" t="n">
         <v>2025</v>
       </c>
@@ -10165,11 +9489,7 @@
       <c r="E496" t="n">
         <v>0</v>
       </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -10177,11 +9497,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B497" t="inlineStr"/>
       <c r="C497" t="n">
         <v>2025</v>
       </c>
@@ -10191,11 +9507,7 @@
       <c r="E497" t="n">
         <v>0</v>
       </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -10203,11 +9515,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B498" t="inlineStr"/>
       <c r="C498" t="n">
         <v>2025</v>
       </c>
@@ -10217,11 +9525,7 @@
       <c r="E498" t="n">
         <v>0</v>
       </c>
-      <c r="F498" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -10229,11 +9533,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B499" t="inlineStr"/>
       <c r="C499" t="n">
         <v>2025</v>
       </c>
@@ -10243,11 +9543,7 @@
       <c r="E499" t="n">
         <v>0</v>
       </c>
-      <c r="F499" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -10255,11 +9551,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B500" t="inlineStr"/>
       <c r="C500" t="n">
         <v>2025</v>
       </c>
@@ -10269,11 +9561,7 @@
       <c r="E500" t="n">
         <v>0</v>
       </c>
-      <c r="F500" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -10281,11 +9569,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B501" t="inlineStr"/>
       <c r="C501" t="n">
         <v>2025</v>
       </c>
@@ -10295,11 +9579,7 @@
       <c r="E501" t="n">
         <v>0</v>
       </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -10307,11 +9587,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B502" t="inlineStr"/>
       <c r="C502" t="n">
         <v>2026</v>
       </c>
@@ -10321,11 +9597,7 @@
       <c r="E502" t="n">
         <v>0</v>
       </c>
-      <c r="F502" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -10333,11 +9605,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B503" t="inlineStr"/>
       <c r="C503" t="n">
         <v>2026</v>
       </c>
@@ -10347,11 +9615,7 @@
       <c r="E503" t="n">
         <v>6</v>
       </c>
-      <c r="F503" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -10359,11 +9623,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B504" t="inlineStr"/>
       <c r="C504" t="n">
         <v>2026</v>
       </c>
@@ -10373,11 +9633,7 @@
       <c r="E504" t="n">
         <v>396</v>
       </c>
-      <c r="F504" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -10385,11 +9641,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B505" t="inlineStr"/>
       <c r="C505" t="n">
         <v>2026</v>
       </c>
@@ -10399,11 +9651,7 @@
       <c r="E505" t="n">
         <v>1460</v>
       </c>
-      <c r="F505" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -10411,11 +9659,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B506" t="inlineStr"/>
       <c r="C506" t="n">
         <v>2026</v>
       </c>
@@ -10425,11 +9669,7 @@
       <c r="E506" t="n">
         <v>273</v>
       </c>
-      <c r="F506" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -10437,11 +9677,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B507" t="inlineStr"/>
       <c r="C507" t="n">
         <v>2026</v>
       </c>
@@ -10451,11 +9687,7 @@
       <c r="E507" t="n">
         <v>104</v>
       </c>
-      <c r="F507" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -10463,11 +9695,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B508" t="inlineStr"/>
       <c r="C508" t="n">
         <v>2026</v>
       </c>
@@ -10477,11 +9705,7 @@
       <c r="E508" t="n">
         <v>324</v>
       </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -10489,11 +9713,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B509" t="inlineStr"/>
       <c r="C509" t="n">
         <v>2026</v>
       </c>
@@ -10503,11 +9723,7 @@
       <c r="E509" t="n">
         <v>478</v>
       </c>
-      <c r="F509" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -10515,11 +9731,7 @@
           <t>Moema</t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B510" t="inlineStr"/>
       <c r="C510" t="n">
         <v>2026</v>
       </c>
@@ -10529,11 +9741,7 @@
       <c r="E510" t="n">
         <v>378</v>
       </c>
-      <c r="F510" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -10553,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -11173,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -11793,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -12413,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -13033,11 +12241,11 @@
         <v>10</v>
       </c>
       <c r="E647" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -13653,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -14273,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -14893,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -15513,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -15527,11 +14735,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B784" t="inlineStr"/>
       <c r="C784" t="n">
         <v>2024</v>
       </c>
@@ -15541,11 +14745,7 @@
       <c r="E784" t="n">
         <v>0</v>
       </c>
-      <c r="F784" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -15553,11 +14753,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B785" t="inlineStr"/>
       <c r="C785" t="n">
         <v>2024</v>
       </c>
@@ -15567,11 +14763,7 @@
       <c r="E785" t="n">
         <v>0</v>
       </c>
-      <c r="F785" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -15579,11 +14771,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B786" t="inlineStr"/>
       <c r="C786" t="n">
         <v>2024</v>
       </c>
@@ -15593,11 +14781,7 @@
       <c r="E786" t="n">
         <v>0</v>
       </c>
-      <c r="F786" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -15605,11 +14789,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B787" t="inlineStr"/>
       <c r="C787" t="n">
         <v>2024</v>
       </c>
@@ -15619,11 +14799,7 @@
       <c r="E787" t="n">
         <v>0</v>
       </c>
-      <c r="F787" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -15631,11 +14807,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B788" t="inlineStr"/>
       <c r="C788" t="n">
         <v>2024</v>
       </c>
@@ -15645,11 +14817,7 @@
       <c r="E788" t="n">
         <v>0</v>
       </c>
-      <c r="F788" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -15657,11 +14825,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B789" t="inlineStr"/>
       <c r="C789" t="n">
         <v>2024</v>
       </c>
@@ -15671,11 +14835,7 @@
       <c r="E789" t="n">
         <v>0</v>
       </c>
-      <c r="F789" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -15683,11 +14843,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B790" t="inlineStr"/>
       <c r="C790" t="n">
         <v>2024</v>
       </c>
@@ -15697,11 +14853,7 @@
       <c r="E790" t="n">
         <v>0</v>
       </c>
-      <c r="F790" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -15709,11 +14861,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B791" t="inlineStr"/>
       <c r="C791" t="n">
         <v>2024</v>
       </c>
@@ -15723,11 +14871,7 @@
       <c r="E791" t="n">
         <v>0</v>
       </c>
-      <c r="F791" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -15735,11 +14879,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B792" t="inlineStr"/>
       <c r="C792" t="n">
         <v>2024</v>
       </c>
@@ -15749,11 +14889,7 @@
       <c r="E792" t="n">
         <v>0</v>
       </c>
-      <c r="F792" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -15761,11 +14897,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B793" t="inlineStr"/>
       <c r="C793" t="n">
         <v>2024</v>
       </c>
@@ -15775,11 +14907,7 @@
       <c r="E793" t="n">
         <v>0</v>
       </c>
-      <c r="F793" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -15787,11 +14915,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B794" t="inlineStr"/>
       <c r="C794" t="n">
         <v>2024</v>
       </c>
@@ -15801,11 +14925,7 @@
       <c r="E794" t="n">
         <v>0</v>
       </c>
-      <c r="F794" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -15813,11 +14933,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B795" t="inlineStr"/>
       <c r="C795" t="n">
         <v>2024</v>
       </c>
@@ -15827,11 +14943,7 @@
       <c r="E795" t="n">
         <v>0</v>
       </c>
-      <c r="F795" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -15839,11 +14951,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B796" t="inlineStr"/>
       <c r="C796" t="n">
         <v>2025</v>
       </c>
@@ -15853,11 +14961,7 @@
       <c r="E796" t="n">
         <v>0</v>
       </c>
-      <c r="F796" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -15865,11 +14969,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B797" t="inlineStr"/>
       <c r="C797" t="n">
         <v>2025</v>
       </c>
@@ -15879,11 +14979,7 @@
       <c r="E797" t="n">
         <v>0</v>
       </c>
-      <c r="F797" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -15891,11 +14987,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B798" t="inlineStr"/>
       <c r="C798" t="n">
         <v>2025</v>
       </c>
@@ -15905,11 +14997,7 @@
       <c r="E798" t="n">
         <v>0</v>
       </c>
-      <c r="F798" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -15917,11 +15005,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B799" t="inlineStr"/>
       <c r="C799" t="n">
         <v>2025</v>
       </c>
@@ -15931,11 +15015,7 @@
       <c r="E799" t="n">
         <v>0</v>
       </c>
-      <c r="F799" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -15943,11 +15023,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B800" t="inlineStr"/>
       <c r="C800" t="n">
         <v>2025</v>
       </c>
@@ -15957,11 +15033,7 @@
       <c r="E800" t="n">
         <v>0</v>
       </c>
-      <c r="F800" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -15969,11 +15041,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B801" t="inlineStr"/>
       <c r="C801" t="n">
         <v>2025</v>
       </c>
@@ -15983,11 +15051,7 @@
       <c r="E801" t="n">
         <v>0</v>
       </c>
-      <c r="F801" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -15995,11 +15059,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B802" t="inlineStr"/>
       <c r="C802" t="n">
         <v>2025</v>
       </c>
@@ -16009,11 +15069,7 @@
       <c r="E802" t="n">
         <v>0</v>
       </c>
-      <c r="F802" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -16021,11 +15077,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B803" t="inlineStr"/>
       <c r="C803" t="n">
         <v>2025</v>
       </c>
@@ -16035,11 +15087,7 @@
       <c r="E803" t="n">
         <v>0</v>
       </c>
-      <c r="F803" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -16047,11 +15095,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B804" t="inlineStr"/>
       <c r="C804" t="n">
         <v>2025</v>
       </c>
@@ -16061,11 +15105,7 @@
       <c r="E804" t="n">
         <v>0</v>
       </c>
-      <c r="F804" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -16073,11 +15113,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B805" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B805" t="inlineStr"/>
       <c r="C805" t="n">
         <v>2025</v>
       </c>
@@ -16087,11 +15123,7 @@
       <c r="E805" t="n">
         <v>0</v>
       </c>
-      <c r="F805" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -16099,11 +15131,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B806" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B806" t="inlineStr"/>
       <c r="C806" t="n">
         <v>2025</v>
       </c>
@@ -16113,11 +15141,7 @@
       <c r="E806" t="n">
         <v>0</v>
       </c>
-      <c r="F806" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -16125,11 +15149,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B807" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B807" t="inlineStr"/>
       <c r="C807" t="n">
         <v>2025</v>
       </c>
@@ -16139,11 +15159,7 @@
       <c r="E807" t="n">
         <v>0</v>
       </c>
-      <c r="F807" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -16151,11 +15167,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B808" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B808" t="inlineStr"/>
       <c r="C808" t="n">
         <v>2026</v>
       </c>
@@ -16165,11 +15177,7 @@
       <c r="E808" t="n">
         <v>0</v>
       </c>
-      <c r="F808" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -16177,11 +15185,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B809" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B809" t="inlineStr"/>
       <c r="C809" t="n">
         <v>2026</v>
       </c>
@@ -16191,11 +15195,7 @@
       <c r="E809" t="n">
         <v>6</v>
       </c>
-      <c r="F809" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -16203,11 +15203,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B810" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B810" t="inlineStr"/>
       <c r="C810" t="n">
         <v>2026</v>
       </c>
@@ -16217,11 +15213,7 @@
       <c r="E810" t="n">
         <v>1061</v>
       </c>
-      <c r="F810" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -16229,11 +15221,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B811" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B811" t="inlineStr"/>
       <c r="C811" t="n">
         <v>2026</v>
       </c>
@@ -16243,11 +15231,7 @@
       <c r="E811" t="n">
         <v>226</v>
       </c>
-      <c r="F811" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -16255,11 +15239,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B812" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B812" t="inlineStr"/>
       <c r="C812" t="n">
         <v>2026</v>
       </c>
@@ -16269,11 +15249,7 @@
       <c r="E812" t="n">
         <v>106</v>
       </c>
-      <c r="F812" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -16281,11 +15257,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B813" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B813" t="inlineStr"/>
       <c r="C813" t="n">
         <v>2026</v>
       </c>
@@ -16295,11 +15267,7 @@
       <c r="E813" t="n">
         <v>41</v>
       </c>
-      <c r="F813" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -16307,11 +15275,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B814" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B814" t="inlineStr"/>
       <c r="C814" t="n">
         <v>2026</v>
       </c>
@@ -16321,11 +15285,7 @@
       <c r="E814" t="n">
         <v>53</v>
       </c>
-      <c r="F814" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -16333,11 +15293,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B815" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B815" t="inlineStr"/>
       <c r="C815" t="n">
         <v>2026</v>
       </c>
@@ -16347,11 +15303,7 @@
       <c r="E815" t="n">
         <v>60</v>
       </c>
-      <c r="F815" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -16359,11 +15311,7 @@
           <t>Tatuape</t>
         </is>
       </c>
-      <c r="B816" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="B816" t="inlineStr"/>
       <c r="C816" t="n">
         <v>2026</v>
       </c>
@@ -16373,11 +15321,7 @@
       <c r="E816" t="n">
         <v>45</v>
       </c>
-      <c r="F816" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:23</t>
-        </is>
-      </c>
+      <c r="F816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -16401,7 +15345,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-26 13:23</t>
+          <t>2026-10-28 13:21</t>
         </is>
       </c>
     </row>
@@ -16739,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>802</v>
+        <v>854</v>
       </c>
     </row>
     <row r="3">
@@ -16848,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>775</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4">
@@ -16858,106 +15802,106 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>473</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5">
@@ -17036,37 +15980,37 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>743</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2519</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2229</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1098</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>854</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>468</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6">
@@ -17175,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2518</v>
+        <v>2724</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -5421,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -7901,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -9761,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -12861,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -15341,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-28 13:21</t>
+          <t>2026-10-29 13:32</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>854</v>
+        <v>890</v>
       </c>
     </row>
     <row r="3">
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>841</v>
+        <v>881</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>523</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2724</v>
+        <v>2843</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C240" t="n">
         <v>2024</v>
       </c>
@@ -4825,7 +4829,11 @@
       <c r="E240" t="n">
         <v>203</v>
       </c>
-      <c r="F240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4833,7 +4841,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C241" t="n">
         <v>2024</v>
       </c>
@@ -4843,7 +4855,11 @@
       <c r="E241" t="n">
         <v>147</v>
       </c>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4851,7 +4867,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C242" t="n">
         <v>2024</v>
       </c>
@@ -4861,7 +4881,11 @@
       <c r="E242" t="n">
         <v>122</v>
       </c>
-      <c r="F242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4869,7 +4893,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C243" t="n">
         <v>2024</v>
       </c>
@@ -4879,7 +4907,11 @@
       <c r="E243" t="n">
         <v>129</v>
       </c>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4887,7 +4919,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C244" t="n">
         <v>2024</v>
       </c>
@@ -4897,7 +4933,11 @@
       <c r="E244" t="n">
         <v>116</v>
       </c>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4905,7 +4945,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C245" t="n">
         <v>2024</v>
       </c>
@@ -4915,7 +4959,11 @@
       <c r="E245" t="n">
         <v>110</v>
       </c>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4923,7 +4971,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C246" t="n">
         <v>2024</v>
       </c>
@@ -4933,7 +4985,11 @@
       <c r="E246" t="n">
         <v>138</v>
       </c>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4941,7 +4997,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C247" t="n">
         <v>2024</v>
       </c>
@@ -4951,7 +5011,11 @@
       <c r="E247" t="n">
         <v>117</v>
       </c>
-      <c r="F247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4959,7 +5023,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C248" t="n">
         <v>2024</v>
       </c>
@@ -4969,7 +5037,11 @@
       <c r="E248" t="n">
         <v>122</v>
       </c>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4977,7 +5049,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C249" t="n">
         <v>2024</v>
       </c>
@@ -4987,7 +5063,11 @@
       <c r="E249" t="n">
         <v>102</v>
       </c>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4995,7 +5075,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C250" t="n">
         <v>2024</v>
       </c>
@@ -5005,7 +5089,11 @@
       <c r="E250" t="n">
         <v>73</v>
       </c>
-      <c r="F250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5013,7 +5101,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C251" t="n">
         <v>2024</v>
       </c>
@@ -5023,7 +5115,11 @@
       <c r="E251" t="n">
         <v>141</v>
       </c>
-      <c r="F251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5031,7 +5127,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C252" t="n">
         <v>2025</v>
       </c>
@@ -5041,7 +5141,11 @@
       <c r="E252" t="n">
         <v>256</v>
       </c>
-      <c r="F252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5049,7 +5153,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C253" t="n">
         <v>2025</v>
       </c>
@@ -5059,7 +5167,11 @@
       <c r="E253" t="n">
         <v>154</v>
       </c>
-      <c r="F253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5067,7 +5179,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C254" t="n">
         <v>2025</v>
       </c>
@@ -5077,7 +5193,11 @@
       <c r="E254" t="n">
         <v>152</v>
       </c>
-      <c r="F254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5085,7 +5205,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C255" t="n">
         <v>2025</v>
       </c>
@@ -5095,7 +5219,11 @@
       <c r="E255" t="n">
         <v>101</v>
       </c>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5103,7 +5231,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C256" t="n">
         <v>2025</v>
       </c>
@@ -5113,7 +5245,11 @@
       <c r="E256" t="n">
         <v>143</v>
       </c>
-      <c r="F256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5121,7 +5257,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C257" t="n">
         <v>2025</v>
       </c>
@@ -5131,7 +5271,11 @@
       <c r="E257" t="n">
         <v>121</v>
       </c>
-      <c r="F257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5139,7 +5283,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C258" t="n">
         <v>2025</v>
       </c>
@@ -5149,7 +5297,11 @@
       <c r="E258" t="n">
         <v>119</v>
       </c>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5157,7 +5309,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C259" t="n">
         <v>2025</v>
       </c>
@@ -5167,7 +5323,11 @@
       <c r="E259" t="n">
         <v>129</v>
       </c>
-      <c r="F259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5175,7 +5335,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C260" t="n">
         <v>2025</v>
       </c>
@@ -5185,7 +5349,11 @@
       <c r="E260" t="n">
         <v>119</v>
       </c>
-      <c r="F260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5193,7 +5361,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C261" t="n">
         <v>2025</v>
       </c>
@@ -5203,7 +5375,11 @@
       <c r="E261" t="n">
         <v>115</v>
       </c>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5211,7 +5387,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C262" t="n">
         <v>2025</v>
       </c>
@@ -5221,7 +5401,11 @@
       <c r="E262" t="n">
         <v>94</v>
       </c>
-      <c r="F262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5229,7 +5413,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C263" t="n">
         <v>2025</v>
       </c>
@@ -5239,7 +5427,11 @@
       <c r="E263" t="n">
         <v>92</v>
       </c>
-      <c r="F263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5247,7 +5439,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C264" t="n">
         <v>2026</v>
       </c>
@@ -5257,7 +5453,11 @@
       <c r="E264" t="n">
         <v>165</v>
       </c>
-      <c r="F264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5265,7 +5465,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C265" t="n">
         <v>2026</v>
       </c>
@@ -5275,7 +5479,11 @@
       <c r="E265" t="n">
         <v>86</v>
       </c>
-      <c r="F265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5283,7 +5491,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C266" t="n">
         <v>2026</v>
       </c>
@@ -5293,7 +5505,11 @@
       <c r="E266" t="n">
         <v>108</v>
       </c>
-      <c r="F266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5301,7 +5517,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C267" t="n">
         <v>2026</v>
       </c>
@@ -5311,7 +5531,11 @@
       <c r="E267" t="n">
         <v>115</v>
       </c>
-      <c r="F267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5319,7 +5543,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C268" t="n">
         <v>2026</v>
       </c>
@@ -5329,7 +5557,11 @@
       <c r="E268" t="n">
         <v>82</v>
       </c>
-      <c r="F268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5337,7 +5569,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C269" t="n">
         <v>2026</v>
       </c>
@@ -5347,7 +5583,11 @@
       <c r="E269" t="n">
         <v>84</v>
       </c>
-      <c r="F269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5355,7 +5595,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C270" t="n">
         <v>2026</v>
       </c>
@@ -5365,7 +5609,11 @@
       <c r="E270" t="n">
         <v>108</v>
       </c>
-      <c r="F270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5373,7 +5621,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C271" t="n">
         <v>2026</v>
       </c>
@@ -5383,7 +5635,11 @@
       <c r="E271" t="n">
         <v>103</v>
       </c>
-      <c r="F271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5391,7 +5647,11 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Regiao 2</t>
+        </is>
+      </c>
       <c r="C272" t="n">
         <v>2026</v>
       </c>
@@ -5401,7 +5661,11 @@
       <c r="E272" t="n">
         <v>94</v>
       </c>
-      <c r="F272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5425,7 +5689,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -6041,11 +6305,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -6661,11 +6925,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -7281,11 +7545,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -7901,11 +8165,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -8521,11 +8785,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9405,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -9761,11 +10025,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10645,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -11001,11 +11265,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11885,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12509,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -12861,11 +13125,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -13481,11 +13745,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -14101,11 +14365,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -14721,11 +14985,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15609,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-29 13:32</t>
+          <t>2026-10-30 13:23</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15947,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3">
@@ -15693,106 +15957,106 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="n">
-        <v>881</v>
+        <v>934</v>
       </c>
     </row>
     <row r="4">
@@ -15901,7 +16165,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>548</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5">
@@ -16010,7 +16274,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>524</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6">
@@ -16119,7 +16383,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2843</v>
+        <v>2977</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1081,11 +1081,11 @@
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1701,11 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3561,11 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -4181,11 +4181,11 @@
         <v>10</v>
       </c>
       <c r="E205" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         <v>10</v>
       </c>
       <c r="E239" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -4815,11 +4815,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
         <v>2024</v>
       </c>
@@ -4829,11 +4825,7 @@
       <c r="E240" t="n">
         <v>203</v>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4841,11 +4833,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
         <v>2024</v>
       </c>
@@ -4855,11 +4843,7 @@
       <c r="E241" t="n">
         <v>147</v>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4867,11 +4851,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
         <v>2024</v>
       </c>
@@ -4881,11 +4861,7 @@
       <c r="E242" t="n">
         <v>122</v>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4893,11 +4869,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="n">
         <v>2024</v>
       </c>
@@ -4907,11 +4879,7 @@
       <c r="E243" t="n">
         <v>129</v>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4919,11 +4887,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
         <v>2024</v>
       </c>
@@ -4933,11 +4897,7 @@
       <c r="E244" t="n">
         <v>116</v>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4945,11 +4905,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
         <v>2024</v>
       </c>
@@ -4959,11 +4915,7 @@
       <c r="E245" t="n">
         <v>110</v>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4971,11 +4923,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
         <v>2024</v>
       </c>
@@ -4985,11 +4933,7 @@
       <c r="E246" t="n">
         <v>138</v>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4997,11 +4941,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
         <v>2024</v>
       </c>
@@ -5011,11 +4951,7 @@
       <c r="E247" t="n">
         <v>117</v>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5023,11 +4959,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
         <v>2024</v>
       </c>
@@ -5037,11 +4969,7 @@
       <c r="E248" t="n">
         <v>122</v>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5049,11 +4977,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
         <v>2024</v>
       </c>
@@ -5063,11 +4987,7 @@
       <c r="E249" t="n">
         <v>102</v>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5075,11 +4995,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
         <v>2024</v>
       </c>
@@ -5089,11 +5005,7 @@
       <c r="E250" t="n">
         <v>73</v>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5101,11 +5013,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="n">
         <v>2024</v>
       </c>
@@ -5115,11 +5023,7 @@
       <c r="E251" t="n">
         <v>141</v>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5127,11 +5031,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
         <v>2025</v>
       </c>
@@ -5141,11 +5041,7 @@
       <c r="E252" t="n">
         <v>256</v>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5153,11 +5049,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="n">
         <v>2025</v>
       </c>
@@ -5167,11 +5059,7 @@
       <c r="E253" t="n">
         <v>154</v>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5179,11 +5067,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="n">
         <v>2025</v>
       </c>
@@ -5193,11 +5077,7 @@
       <c r="E254" t="n">
         <v>152</v>
       </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5205,11 +5085,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
         <v>2025</v>
       </c>
@@ -5219,11 +5095,7 @@
       <c r="E255" t="n">
         <v>101</v>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5231,11 +5103,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
         <v>2025</v>
       </c>
@@ -5245,11 +5113,7 @@
       <c r="E256" t="n">
         <v>143</v>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5257,11 +5121,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B257" t="inlineStr"/>
       <c r="C257" t="n">
         <v>2025</v>
       </c>
@@ -5271,11 +5131,7 @@
       <c r="E257" t="n">
         <v>121</v>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5283,11 +5139,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B258" t="inlineStr"/>
       <c r="C258" t="n">
         <v>2025</v>
       </c>
@@ -5297,11 +5149,7 @@
       <c r="E258" t="n">
         <v>119</v>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5309,11 +5157,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
         <v>2025</v>
       </c>
@@ -5323,11 +5167,7 @@
       <c r="E259" t="n">
         <v>129</v>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5335,11 +5175,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
         <v>2025</v>
       </c>
@@ -5349,11 +5185,7 @@
       <c r="E260" t="n">
         <v>119</v>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5361,11 +5193,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
         <v>2025</v>
       </c>
@@ -5375,11 +5203,7 @@
       <c r="E261" t="n">
         <v>115</v>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5387,11 +5211,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
         <v>2025</v>
       </c>
@@ -5401,11 +5221,7 @@
       <c r="E262" t="n">
         <v>94</v>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5413,11 +5229,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
         <v>2025</v>
       </c>
@@ -5427,11 +5239,7 @@
       <c r="E263" t="n">
         <v>92</v>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5439,11 +5247,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
         <v>2026</v>
       </c>
@@ -5453,11 +5257,7 @@
       <c r="E264" t="n">
         <v>165</v>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5465,11 +5265,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B265" t="inlineStr"/>
       <c r="C265" t="n">
         <v>2026</v>
       </c>
@@ -5479,11 +5275,7 @@
       <c r="E265" t="n">
         <v>86</v>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5491,11 +5283,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
         <v>2026</v>
       </c>
@@ -5505,11 +5293,7 @@
       <c r="E266" t="n">
         <v>108</v>
       </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5517,11 +5301,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
         <v>2026</v>
       </c>
@@ -5531,11 +5311,7 @@
       <c r="E267" t="n">
         <v>115</v>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5543,11 +5319,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B268" t="inlineStr"/>
       <c r="C268" t="n">
         <v>2026</v>
       </c>
@@ -5557,11 +5329,7 @@
       <c r="E268" t="n">
         <v>82</v>
       </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5569,11 +5337,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
         <v>2026</v>
       </c>
@@ -5583,11 +5347,7 @@
       <c r="E269" t="n">
         <v>84</v>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5595,11 +5355,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
         <v>2026</v>
       </c>
@@ -5609,11 +5365,7 @@
       <c r="E270" t="n">
         <v>108</v>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5621,11 +5373,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B271" t="inlineStr"/>
       <c r="C271" t="n">
         <v>2026</v>
       </c>
@@ -5635,11 +5383,7 @@
       <c r="E271" t="n">
         <v>103</v>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5647,11 +5391,7 @@
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Regiao 2</t>
-        </is>
-      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
         <v>2026</v>
       </c>
@@ -5661,11 +5401,7 @@
       <c r="E272" t="n">
         <v>94</v>
       </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>2026-10-30 13:23</t>
-        </is>
-      </c>
+      <c r="F272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5685,11 +5421,11 @@
         <v>10</v>
       </c>
       <c r="E273" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -6305,11 +6041,11 @@
         <v>10</v>
       </c>
       <c r="E307" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -6925,11 +6661,11 @@
         <v>10</v>
       </c>
       <c r="E341" t="n">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -7545,11 +7281,11 @@
         <v>10</v>
       </c>
       <c r="E375" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -8165,11 +7901,11 @@
         <v>10</v>
       </c>
       <c r="E409" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -8785,11 +8521,11 @@
         <v>10</v>
       </c>
       <c r="E443" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -9405,11 +9141,11 @@
         <v>10</v>
       </c>
       <c r="E477" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -10025,11 +9761,11 @@
         <v>10</v>
       </c>
       <c r="E511" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -10645,11 +10381,11 @@
         <v>10</v>
       </c>
       <c r="E545" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -11265,11 +11001,11 @@
         <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -11885,11 +11621,11 @@
         <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12245,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -13125,11 +12861,11 @@
         <v>10</v>
       </c>
       <c r="E681" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -13745,11 +13481,11 @@
         <v>10</v>
       </c>
       <c r="E715" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -14365,11 +14101,11 @@
         <v>10</v>
       </c>
       <c r="E749" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -14985,11 +14721,11 @@
         <v>10</v>
       </c>
       <c r="E783" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -15605,11 +15341,11 @@
         <v>10</v>
       </c>
       <c r="E817" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2026-10-30 13:23</t>
+          <t>2026-10-31 12:35</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>916</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3">
@@ -15957,106 +15693,106 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>934</v>
+        <v>980</v>
       </c>
     </row>
     <row r="4">
@@ -16165,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>589</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5">
@@ -16274,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>538</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6">
@@ -16383,7 +16119,7 @@
         <v>3555</v>
       </c>
       <c r="AI6" t="n">
-        <v>2977</v>
+        <v>3111</v>
       </c>
     </row>
   </sheetData>
